--- a/AAII_Financials/Quarterly/MITSY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MITSY_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="92">
   <si>
     <t>MITSY</t>
   </si>
@@ -656,402 +656,414 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="12" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="31" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="10" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="32" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>21436000</v>
+        <v>24405800</v>
       </c>
       <c r="E8" s="3">
-        <v>20910200</v>
+        <v>21758800</v>
       </c>
       <c r="F8" s="3">
-        <v>21712000</v>
+        <v>21225100</v>
       </c>
       <c r="G8" s="3">
-        <v>23988300</v>
+        <v>22039000</v>
       </c>
       <c r="H8" s="3">
-        <v>24589800</v>
+        <v>24349600</v>
       </c>
       <c r="I8" s="3">
-        <v>24704300</v>
+        <v>24960100</v>
       </c>
       <c r="J8" s="3">
+        <v>25076400</v>
+      </c>
+      <c r="K8" s="3">
         <v>21036400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>21800100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>19886400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>19536500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>23476100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>14920200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>14487100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>15741000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>28986100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>16240900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>16340900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>14959400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>18687200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>16988500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>15394900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>14145800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>11201800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>11381200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>10959900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>10682200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>10539300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>10144100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>8977900</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>19393100</v>
+        <v>21871400</v>
       </c>
       <c r="E9" s="3">
-        <v>18913400</v>
+        <v>19685100</v>
       </c>
       <c r="F9" s="3">
-        <v>19202300</v>
+        <v>19198200</v>
       </c>
       <c r="G9" s="3">
-        <v>21423100</v>
+        <v>19491500</v>
       </c>
       <c r="H9" s="3">
-        <v>22475100</v>
+        <v>21745700</v>
       </c>
       <c r="I9" s="3">
-        <v>22623200</v>
+        <v>22813500</v>
       </c>
       <c r="J9" s="3">
+        <v>22963900</v>
+      </c>
+      <c r="K9" s="3">
         <v>18701800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>19997700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>18017600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>17565000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>21751400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>13451500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>13099400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>14122800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>27233000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>14307400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>14328700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>13042800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>16713400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>15012100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>13487900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>12160100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>9567400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>9519200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>9110700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>8879700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>8666700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>8528400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>7541800</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>2042900</v>
+        <v>2534400</v>
       </c>
       <c r="E10" s="3">
-        <v>1996800</v>
+        <v>2073700</v>
       </c>
       <c r="F10" s="3">
-        <v>2509800</v>
+        <v>2026900</v>
       </c>
       <c r="G10" s="3">
-        <v>2565300</v>
+        <v>2547600</v>
       </c>
       <c r="H10" s="3">
-        <v>2114700</v>
+        <v>2603900</v>
       </c>
       <c r="I10" s="3">
-        <v>2081200</v>
+        <v>2146600</v>
       </c>
       <c r="J10" s="3">
+        <v>2112500</v>
+      </c>
+      <c r="K10" s="3">
         <v>2334500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1802400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1868700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1971500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1724700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1468700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1387600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1618200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1753200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1933500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2012200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1916600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1973800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1976400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1906900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1985700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1634400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1861900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1849100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1802500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1872600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1615700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1436100</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1084,8 +1096,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1176,8 +1189,11 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1268,100 +1284,106 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>9800</v>
+        <v>59100</v>
       </c>
       <c r="E14" s="3">
-        <v>16700</v>
+        <v>9900</v>
       </c>
       <c r="F14" s="3">
-        <v>92200</v>
+        <v>17000</v>
       </c>
       <c r="G14" s="3">
-        <v>35000</v>
+        <v>93600</v>
       </c>
       <c r="H14" s="3">
-        <v>70100</v>
+        <v>35500</v>
       </c>
       <c r="I14" s="3">
+        <v>71100</v>
+      </c>
+      <c r="J14" s="3">
         <v>1800</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>32100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>10800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>163500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-1600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>90700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>262100</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>38700</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>2600</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>874000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>82100</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>8300</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>15500</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>225400</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>20700</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>3800</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>8900</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>59600</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>91800</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>67000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>11600</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>48200</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
-      </c>
       <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1452,8 +1474,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1483,192 +1508,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>20258200</v>
+        <v>23154200</v>
       </c>
       <c r="E17" s="3">
-        <v>19821900</v>
+        <v>20563300</v>
       </c>
       <c r="F17" s="3">
-        <v>20602700</v>
+        <v>20120400</v>
       </c>
       <c r="G17" s="3">
-        <v>22396600</v>
+        <v>20912900</v>
       </c>
       <c r="H17" s="3">
-        <v>23521600</v>
+        <v>22733900</v>
       </c>
       <c r="I17" s="3">
-        <v>23482700</v>
+        <v>23875800</v>
       </c>
       <c r="J17" s="3">
+        <v>23836300</v>
+      </c>
+      <c r="K17" s="3">
         <v>19830800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>20835700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>19119900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>18538500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>22976200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>14945300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>14328800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>15201000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>29074600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>15671900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>15581200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>14210600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>18422900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>16308000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>14800500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>13271100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>11108400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>10721200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>10139700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>9954000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>9794000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>9291500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>8516000</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1177700</v>
+        <v>1251600</v>
       </c>
       <c r="E18" s="3">
-        <v>1088400</v>
+        <v>1195500</v>
       </c>
       <c r="F18" s="3">
-        <v>1109400</v>
+        <v>1104800</v>
       </c>
       <c r="G18" s="3">
-        <v>1591700</v>
+        <v>1126100</v>
       </c>
       <c r="H18" s="3">
-        <v>1068200</v>
+        <v>1615700</v>
       </c>
       <c r="I18" s="3">
-        <v>1221600</v>
+        <v>1084300</v>
       </c>
       <c r="J18" s="3">
+        <v>1240000</v>
+      </c>
+      <c r="K18" s="3">
         <v>1205600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>964400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>766500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>998000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>500000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-25200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>158300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>540000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-88400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>569000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>759700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>748700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>264200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>680500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>594400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>874700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>93400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>660000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>820200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>728200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>745300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>852600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>461900</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1701,468 +1733,484 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>973600</v>
+        <v>1316500</v>
       </c>
       <c r="E20" s="3">
-        <v>1238300</v>
+        <v>988200</v>
       </c>
       <c r="F20" s="3">
-        <v>1361500</v>
+        <v>1257000</v>
       </c>
       <c r="G20" s="3">
-        <v>1132600</v>
+        <v>1382000</v>
       </c>
       <c r="H20" s="3">
-        <v>1342800</v>
+        <v>1149700</v>
       </c>
       <c r="I20" s="3">
-        <v>1197700</v>
+        <v>1363000</v>
       </c>
       <c r="J20" s="3">
+        <v>1215700</v>
+      </c>
+      <c r="K20" s="3">
         <v>1076700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1107600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1367000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>990700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>836800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>762100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>586800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>461600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>822000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>1024200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>799300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1048100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>949200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1042200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>982200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>815900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>682600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>963900</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>765600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>808400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>451900</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>662000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>545900</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>2603200</v>
+        <v>3050400</v>
       </c>
       <c r="E21" s="3">
-        <v>2786900</v>
+        <v>2642400</v>
       </c>
       <c r="F21" s="3">
-        <v>2911600</v>
+        <v>2828900</v>
       </c>
       <c r="G21" s="3">
-        <v>3184400</v>
+        <v>2955400</v>
       </c>
       <c r="H21" s="3">
-        <v>2882700</v>
+        <v>3232300</v>
       </c>
       <c r="I21" s="3">
-        <v>2857600</v>
+        <v>2926100</v>
       </c>
       <c r="J21" s="3">
+        <v>2900600</v>
+      </c>
+      <c r="K21" s="3">
         <v>2756100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2608800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2659900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2531800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1857200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1229100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1290900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1539200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1356700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2193700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2100800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>2351400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1709400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2165200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1987800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>2086700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1189800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>2072700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>2035100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1965600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1607200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1947400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1446600</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>278400</v>
+        <v>278700</v>
       </c>
       <c r="E22" s="3">
-        <v>256200</v>
+        <v>282600</v>
       </c>
       <c r="F22" s="3">
-        <v>276600</v>
+        <v>260100</v>
       </c>
       <c r="G22" s="3">
-        <v>220900</v>
+        <v>280700</v>
       </c>
       <c r="H22" s="3">
-        <v>154400</v>
+        <v>224300</v>
       </c>
       <c r="I22" s="3">
-        <v>108900</v>
+        <v>156700</v>
       </c>
       <c r="J22" s="3">
+        <v>110500</v>
+      </c>
+      <c r="K22" s="3">
         <v>76000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>69100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>82400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>105800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>77600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>92500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>100800</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>131600</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>178400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>205000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>212500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>217600</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>194400</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>191600</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>191700</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>172300</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>149100</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>150300</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>156500</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>145100</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>140900</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>133700</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>118100</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>1872900</v>
+        <v>2289300</v>
       </c>
       <c r="E23" s="3">
-        <v>2070400</v>
+        <v>1901100</v>
       </c>
       <c r="F23" s="3">
-        <v>2194400</v>
+        <v>2101600</v>
       </c>
       <c r="G23" s="3">
-        <v>2503400</v>
+        <v>2227400</v>
       </c>
       <c r="H23" s="3">
-        <v>2256600</v>
+        <v>2541100</v>
       </c>
       <c r="I23" s="3">
-        <v>2310400</v>
+        <v>2290600</v>
       </c>
       <c r="J23" s="3">
+        <v>2345200</v>
+      </c>
+      <c r="K23" s="3">
         <v>2206300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2002900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2051000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1883000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1259100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>644500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>644300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>870000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>555100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1388200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1346500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1579200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1019000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1531100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1384900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1518300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>626900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1473600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1429300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1391500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1056300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1380900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>889700</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>474400</v>
+        <v>443000</v>
       </c>
       <c r="E24" s="3">
-        <v>352900</v>
+        <v>481500</v>
       </c>
       <c r="F24" s="3">
-        <v>253600</v>
+        <v>358300</v>
       </c>
       <c r="G24" s="3">
-        <v>469400</v>
+        <v>257400</v>
       </c>
       <c r="H24" s="3">
-        <v>479200</v>
+        <v>476500</v>
       </c>
       <c r="I24" s="3">
-        <v>395700</v>
+        <v>486500</v>
       </c>
       <c r="J24" s="3">
+        <v>401700</v>
+      </c>
+      <c r="K24" s="3">
         <v>299100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>402700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>482800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>413000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>260700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-32100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>250100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>301300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>88400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>409100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>280700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>343700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>397900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>289000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>367300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>372800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>201200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>158300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>234300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>338000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>320800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>367600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>316000</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2253,192 +2301,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>1398500</v>
+        <v>1846300</v>
       </c>
       <c r="E26" s="3">
-        <v>1717500</v>
+        <v>1419600</v>
       </c>
       <c r="F26" s="3">
-        <v>1940700</v>
+        <v>1743400</v>
       </c>
       <c r="G26" s="3">
-        <v>2033900</v>
+        <v>1970000</v>
       </c>
       <c r="H26" s="3">
-        <v>1777400</v>
+        <v>2064600</v>
       </c>
       <c r="I26" s="3">
-        <v>1914700</v>
+        <v>1804100</v>
       </c>
       <c r="J26" s="3">
+        <v>1943500</v>
+      </c>
+      <c r="K26" s="3">
         <v>1907200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1600200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1568200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1470000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>998400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>676500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>394200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>568600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>466700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>979200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1065800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1235500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>621100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1242100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1017600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1145500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>425700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1315300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1195000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1053500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>735500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1013300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>573700</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>1350600</v>
+        <v>1820800</v>
       </c>
       <c r="E27" s="3">
-        <v>1678900</v>
+        <v>1371000</v>
       </c>
       <c r="F27" s="3">
-        <v>1924600</v>
+        <v>1704200</v>
       </c>
       <c r="G27" s="3">
-        <v>2003200</v>
+        <v>1953500</v>
       </c>
       <c r="H27" s="3">
-        <v>1753700</v>
+        <v>2033300</v>
       </c>
       <c r="I27" s="3">
-        <v>1826000</v>
+        <v>1780100</v>
       </c>
       <c r="J27" s="3">
+        <v>1853500</v>
+      </c>
+      <c r="K27" s="3">
         <v>1868900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1570700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1538400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1405800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>967900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>651700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>369800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>533600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>497200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>919400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1002800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1145300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>616500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1200700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>970400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1076400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>376500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1252300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1153100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1001200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>672400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>961100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>539600</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2529,8 +2586,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2621,8 +2681,11 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2713,8 +2776,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2805,192 +2871,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-973600</v>
+        <v>-1316500</v>
       </c>
       <c r="E32" s="3">
-        <v>-1238300</v>
+        <v>-988200</v>
       </c>
       <c r="F32" s="3">
-        <v>-1361500</v>
+        <v>-1257000</v>
       </c>
       <c r="G32" s="3">
-        <v>-1132600</v>
+        <v>-1382000</v>
       </c>
       <c r="H32" s="3">
-        <v>-1342800</v>
+        <v>-1149700</v>
       </c>
       <c r="I32" s="3">
-        <v>-1197700</v>
+        <v>-1363000</v>
       </c>
       <c r="J32" s="3">
+        <v>-1215700</v>
+      </c>
+      <c r="K32" s="3">
         <v>-1076700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1107600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1367000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-990700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-836800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-762100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-586800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-461600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-822000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-1024200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-799300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1048100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-949200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1042200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-982200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-815900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-682600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-963900</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-765600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-808400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-451900</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-662000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-545900</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>1350600</v>
+        <v>1820800</v>
       </c>
       <c r="E33" s="3">
-        <v>1678900</v>
+        <v>1371000</v>
       </c>
       <c r="F33" s="3">
-        <v>1924600</v>
+        <v>1704200</v>
       </c>
       <c r="G33" s="3">
-        <v>2003200</v>
+        <v>1953500</v>
       </c>
       <c r="H33" s="3">
-        <v>1753700</v>
+        <v>2033300</v>
       </c>
       <c r="I33" s="3">
-        <v>1826000</v>
+        <v>1780100</v>
       </c>
       <c r="J33" s="3">
+        <v>1853500</v>
+      </c>
+      <c r="K33" s="3">
         <v>1868900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1570700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1538400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1405800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>967900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>651700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>369800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>533600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>497200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>919400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1002800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1145300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>616500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1200700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>970400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1076400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>376500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1252300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1153100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1001200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>672400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>961100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>539600</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3081,197 +3156,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>1350600</v>
+        <v>1820800</v>
       </c>
       <c r="E35" s="3">
-        <v>1678900</v>
+        <v>1371000</v>
       </c>
       <c r="F35" s="3">
-        <v>1924600</v>
+        <v>1704200</v>
       </c>
       <c r="G35" s="3">
-        <v>2003200</v>
+        <v>1953500</v>
       </c>
       <c r="H35" s="3">
-        <v>1753700</v>
+        <v>2033300</v>
       </c>
       <c r="I35" s="3">
-        <v>1826000</v>
+        <v>1780100</v>
       </c>
       <c r="J35" s="3">
+        <v>1853500</v>
+      </c>
+      <c r="K35" s="3">
         <v>1868900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1570700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1538400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1405800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>967900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>651700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>369800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>533600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>497200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>919400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1002800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1145300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>616500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1200700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>970400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1076400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>376500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1252300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1153100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1001200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>672400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>961100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>539600</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3304,8 +3388,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3338,836 +3423,864 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>7950100</v>
+        <v>7559700</v>
       </c>
       <c r="E41" s="3">
-        <v>8507900</v>
+        <v>8069800</v>
       </c>
       <c r="F41" s="3">
-        <v>9230500</v>
+        <v>8636000</v>
       </c>
       <c r="G41" s="3">
-        <v>8272200</v>
+        <v>9369500</v>
       </c>
       <c r="H41" s="3">
-        <v>7082300</v>
+        <v>8396800</v>
       </c>
       <c r="I41" s="3">
-        <v>8095100</v>
+        <v>7189000</v>
       </c>
       <c r="J41" s="3">
+        <v>8217000</v>
+      </c>
+      <c r="K41" s="3">
         <v>7489000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5778600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>6202300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>7170000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>7537700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>7172600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>8563400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>8883000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>9327400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>8619900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>10596300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>9047000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>9188200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>8998400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>9253700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>9683800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>10227700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>10936200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>10487600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>14312400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>13338900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>14063500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>13464600</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>6303300</v>
+        <v>6219100</v>
       </c>
       <c r="E42" s="3">
-        <v>6069300</v>
+        <v>6398200</v>
       </c>
       <c r="F42" s="3">
-        <v>5132600</v>
+        <v>6160700</v>
       </c>
       <c r="G42" s="3">
-        <v>6723200</v>
+        <v>5209900</v>
       </c>
       <c r="H42" s="3">
-        <v>8454200</v>
+        <v>6824400</v>
       </c>
       <c r="I42" s="3">
-        <v>7584400</v>
+        <v>8581500</v>
       </c>
       <c r="J42" s="3">
+        <v>7698600</v>
+      </c>
+      <c r="K42" s="3">
         <v>6625800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>6088600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>5687100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>4151400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>3048600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>3152600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>3119600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>3626700</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>4959100</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>3002000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>2707200</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>2753000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>2445800</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>3255400</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>2869100</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>2702600</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>2205000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>3030500</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>2627800</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>2445500</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>2374300</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>3915400</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>3786600</v>
       </c>
     </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>14733900</v>
+        <v>15519100</v>
       </c>
       <c r="E43" s="3">
-        <v>14030000</v>
+        <v>14955800</v>
       </c>
       <c r="F43" s="3">
-        <v>14549400</v>
+        <v>14241200</v>
       </c>
       <c r="G43" s="3">
-        <v>15833100</v>
+        <v>14768600</v>
       </c>
       <c r="H43" s="3">
-        <v>16073800</v>
+        <v>16071500</v>
       </c>
       <c r="I43" s="3">
-        <v>16537300</v>
+        <v>16315800</v>
       </c>
       <c r="J43" s="3">
+        <v>16786300</v>
+      </c>
+      <c r="K43" s="3">
         <v>15292800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>15852800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>13571000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>13780400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>12847000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>12632200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>11204300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>12454600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>14294200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>16566500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>14911000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>15916900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>17338600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>17779600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>16564800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>15649400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>15964800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>17290200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>16461900</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>14971500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>15428500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>15480700</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>13205700</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>6080300</v>
+        <v>6219600</v>
       </c>
       <c r="E44" s="3">
-        <v>6382200</v>
+        <v>6171800</v>
       </c>
       <c r="F44" s="3">
-        <v>6245200</v>
+        <v>6478400</v>
       </c>
       <c r="G44" s="3">
-        <v>6787400</v>
+        <v>6339300</v>
       </c>
       <c r="H44" s="3">
-        <v>6785000</v>
+        <v>6889600</v>
       </c>
       <c r="I44" s="3">
-        <v>6480000</v>
+        <v>6887200</v>
       </c>
       <c r="J44" s="3">
+        <v>6577600</v>
+      </c>
+      <c r="K44" s="3">
         <v>6305800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>6092800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>5348100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>5282900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>4361400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>4413800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>4318400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>4554700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>4879500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>6283100</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>5890100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>5901000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>5839800</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>5950700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>5828600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>5150500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>4978300</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>5689100</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>5718500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>5394500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>5229200</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>5336700</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>4779400</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>3354400</v>
+        <v>3619500</v>
       </c>
       <c r="E45" s="3">
-        <v>3998400</v>
+        <v>3404900</v>
       </c>
       <c r="F45" s="3">
-        <v>2523200</v>
+        <v>4058600</v>
       </c>
       <c r="G45" s="3">
-        <v>2865300</v>
+        <v>2561200</v>
       </c>
       <c r="H45" s="3">
-        <v>2491800</v>
+        <v>2908400</v>
       </c>
       <c r="I45" s="3">
-        <v>2724400</v>
+        <v>2529300</v>
       </c>
       <c r="J45" s="3">
+        <v>2765400</v>
+      </c>
+      <c r="K45" s="3">
         <v>2245300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2327600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2275500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2305600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2036200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2036500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2138300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2623100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2875800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2941600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2909800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>3240200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>3592300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>3707100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>3593900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>3510500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>4828700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>4005100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>3659200</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>3525900</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>3320100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>3359700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>2996000</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>38422000</v>
+        <v>39137000</v>
       </c>
       <c r="E46" s="3">
-        <v>38987800</v>
+        <v>39000600</v>
       </c>
       <c r="F46" s="3">
-        <v>37680900</v>
+        <v>39575000</v>
       </c>
       <c r="G46" s="3">
-        <v>40481100</v>
+        <v>38248400</v>
       </c>
       <c r="H46" s="3">
-        <v>40887100</v>
+        <v>41090800</v>
       </c>
       <c r="I46" s="3">
-        <v>41421100</v>
+        <v>41502800</v>
       </c>
       <c r="J46" s="3">
+        <v>42044900</v>
+      </c>
+      <c r="K46" s="3">
         <v>37958800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>36140400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>33084000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>32690400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>29831000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>29407700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>29344000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>32142100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>36336100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>37413100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>37014400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>36858100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>38404700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>39691200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>38110200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>36696800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>38204500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>40951100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>38955000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>40649900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>39691000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>42156100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>38232400</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>49322000</v>
+        <v>49672500</v>
       </c>
       <c r="E47" s="3">
-        <v>46388400</v>
+        <v>50064800</v>
       </c>
       <c r="F47" s="3">
-        <v>43769600</v>
+        <v>47087000</v>
       </c>
       <c r="G47" s="3">
-        <v>42623600</v>
+        <v>44428700</v>
       </c>
       <c r="H47" s="3">
-        <v>44294100</v>
+        <v>43265600</v>
       </c>
       <c r="I47" s="3">
-        <v>42527500</v>
+        <v>44961200</v>
       </c>
       <c r="J47" s="3">
+        <v>43167900</v>
+      </c>
+      <c r="K47" s="3">
         <v>41318100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>38904100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>40110200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>42558000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>38622100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>37234400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>38999900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>42508800</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>43819300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>50414800</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>49513500</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>50532700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>53209900</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>48784500</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>49446400</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>45792300</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>44126500</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>45878300</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>44160100</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>42595400</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>41700800</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>39980100</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>35285000</v>
       </c>
     </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>18028200</v>
+        <v>17667000</v>
       </c>
       <c r="E48" s="3">
-        <v>18336800</v>
+        <v>18299700</v>
       </c>
       <c r="F48" s="3">
-        <v>17151800</v>
+        <v>18613000</v>
       </c>
       <c r="G48" s="3">
-        <v>16923800</v>
+        <v>17410100</v>
       </c>
       <c r="H48" s="3">
-        <v>17701900</v>
+        <v>17178700</v>
       </c>
       <c r="I48" s="3">
-        <v>17449400</v>
+        <v>17968500</v>
       </c>
       <c r="J48" s="3">
+        <v>17712200</v>
+      </c>
+      <c r="K48" s="3">
         <v>16662900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>16691900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>17196100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>17942800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>17369900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>17576200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>18818600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>20573600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>20908000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>22359200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>21602500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>21397900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>20646900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>20363100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>19807500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>18394900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>17346400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>17820100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>18003700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>17903900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>17769100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>18403400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>16888800</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>2951400</v>
+        <v>2996600</v>
       </c>
       <c r="E49" s="3">
-        <v>2875700</v>
+        <v>2995800</v>
       </c>
       <c r="F49" s="3">
-        <v>1841400</v>
+        <v>2919000</v>
       </c>
       <c r="G49" s="3">
-        <v>1875100</v>
+        <v>1869100</v>
       </c>
       <c r="H49" s="3">
-        <v>1965200</v>
+        <v>1903300</v>
       </c>
       <c r="I49" s="3">
-        <v>1870500</v>
+        <v>1994800</v>
       </c>
       <c r="J49" s="3">
+        <v>1898700</v>
+      </c>
+      <c r="K49" s="3">
         <v>1680200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1568100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1529500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1604900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1336900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1365200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1507700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1644000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1720500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>2151300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>2186600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>2230100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1673000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1743600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1607100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1552500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1565800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1572800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1615000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1568500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1496200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1434400</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1274500</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4258,8 +4371,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4350,100 +4466,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1796600</v>
+        <v>1662300</v>
       </c>
       <c r="E52" s="3">
-        <v>1718900</v>
+        <v>1823600</v>
       </c>
       <c r="F52" s="3">
-        <v>1685700</v>
+        <v>1744800</v>
       </c>
       <c r="G52" s="3">
-        <v>1474400</v>
+        <v>1711000</v>
       </c>
       <c r="H52" s="3">
-        <v>1642400</v>
+        <v>1496600</v>
       </c>
       <c r="I52" s="3">
-        <v>1554900</v>
+        <v>1667200</v>
       </c>
       <c r="J52" s="3">
+        <v>1578300</v>
+      </c>
+      <c r="K52" s="3">
         <v>1470700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1415900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1479100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1529400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1577500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1215900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>984000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1107500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1229500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>850800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>851500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>819700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>864500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1064200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1091400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1002900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>969100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1006800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1169300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1357900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1356900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1432200</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1287300</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4534,100 +4656,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>110520000</v>
+        <v>111135400</v>
       </c>
       <c r="E54" s="3">
-        <v>108307500</v>
+        <v>112184500</v>
       </c>
       <c r="F54" s="3">
-        <v>102129300</v>
+        <v>109938700</v>
       </c>
       <c r="G54" s="3">
-        <v>103378100</v>
+        <v>103667400</v>
       </c>
       <c r="H54" s="3">
-        <v>106490700</v>
+        <v>104935000</v>
       </c>
       <c r="I54" s="3">
-        <v>104823300</v>
+        <v>108094400</v>
       </c>
       <c r="J54" s="3">
+        <v>106402000</v>
+      </c>
+      <c r="K54" s="3">
         <v>99090600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>94720400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>93398900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>96325500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>88737300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>86799500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>89654300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>97976000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>104013400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>113189100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>111168500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>111838500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>114798900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>111646700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>110062600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>103439500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>102212200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>107229100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>103903100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>104075500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>102014000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>103406200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>92968100</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4660,8 +4788,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4694,560 +4823,579 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>10729400</v>
+        <v>11706600</v>
       </c>
       <c r="E57" s="3">
-        <v>10638000</v>
+        <v>10891000</v>
       </c>
       <c r="F57" s="3">
-        <v>10029000</v>
+        <v>10798300</v>
       </c>
       <c r="G57" s="3">
-        <v>11719300</v>
+        <v>10180000</v>
       </c>
       <c r="H57" s="3">
-        <v>11412700</v>
+        <v>11895800</v>
       </c>
       <c r="I57" s="3">
-        <v>12358600</v>
+        <v>11584600</v>
       </c>
       <c r="J57" s="3">
+        <v>12544700</v>
+      </c>
+      <c r="K57" s="3">
         <v>11547900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>11758900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>10074300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>10382200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>9311600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>8737600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>8288800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>8744100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>10012600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>11770300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>10845800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>11551100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>12707100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>13217100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>12028200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>11694800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>11429100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>12147200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>11328200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>10649200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>10676900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>10787700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>8887300</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>7131500</v>
+        <v>7030500</v>
       </c>
       <c r="E58" s="3">
-        <v>6222000</v>
+        <v>7238900</v>
       </c>
       <c r="F58" s="3">
-        <v>8255100</v>
+        <v>6315700</v>
       </c>
       <c r="G58" s="3">
-        <v>8285800</v>
+        <v>8379400</v>
       </c>
       <c r="H58" s="3">
-        <v>8614200</v>
+        <v>8410600</v>
       </c>
       <c r="I58" s="3">
-        <v>7636000</v>
+        <v>8743900</v>
       </c>
       <c r="J58" s="3">
+        <v>7751000</v>
+      </c>
+      <c r="K58" s="3">
         <v>4595500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>5029900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>5764700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>5962600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>5327600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>5047300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>5228200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>6306000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>6143800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>6544700</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>7261900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>8192800</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>7845800</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>7553600</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>6959600</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>6294800</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>6184300</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>5829800</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>5542100</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>6488500</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>6146100</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>7075800</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>6388700</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>8108300</v>
+        <v>7627400</v>
       </c>
       <c r="E59" s="3">
-        <v>8372300</v>
+        <v>8230400</v>
       </c>
       <c r="F59" s="3">
-        <v>6726400</v>
+        <v>8498400</v>
       </c>
       <c r="G59" s="3">
-        <v>7631200</v>
+        <v>6827700</v>
       </c>
       <c r="H59" s="3">
-        <v>10732500</v>
+        <v>7746100</v>
       </c>
       <c r="I59" s="3">
-        <v>10650300</v>
+        <v>10894200</v>
       </c>
       <c r="J59" s="3">
+        <v>10810700</v>
+      </c>
+      <c r="K59" s="3">
         <v>9145900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>6802800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>6487000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>5634600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4516000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4513900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4330200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4931400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>7640400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>6186700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>5577100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>5804100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>5781200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>6905100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>6461800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>6059700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>6783400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>6711400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>5826600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>5765000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>5564600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>5821700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>4722300</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>25969200</v>
+        <v>26364400</v>
       </c>
       <c r="E60" s="3">
-        <v>25232400</v>
+        <v>26360300</v>
       </c>
       <c r="F60" s="3">
-        <v>25010500</v>
+        <v>25612400</v>
       </c>
       <c r="G60" s="3">
-        <v>27636400</v>
+        <v>25387100</v>
       </c>
       <c r="H60" s="3">
-        <v>30759500</v>
+        <v>28052600</v>
       </c>
       <c r="I60" s="3">
-        <v>30644900</v>
+        <v>31222700</v>
       </c>
       <c r="J60" s="3">
+        <v>31106500</v>
+      </c>
+      <c r="K60" s="3">
         <v>25289300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>23591600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>22326000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>21979400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>19155200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>18298800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>17847200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>19981500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>23796800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>24501800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>23684800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>25548000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>26334000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>27675800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>25449500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>24049300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>24396900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>24688500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>22697000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>22902800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>22387600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>23685200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>19998200</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>26599800</v>
+        <v>25952900</v>
       </c>
       <c r="E61" s="3">
-        <v>27587400</v>
+        <v>27000400</v>
       </c>
       <c r="F61" s="3">
-        <v>25214300</v>
+        <v>28002900</v>
       </c>
       <c r="G61" s="3">
-        <v>25708000</v>
+        <v>25594000</v>
       </c>
       <c r="H61" s="3">
-        <v>26080400</v>
+        <v>26095200</v>
       </c>
       <c r="I61" s="3">
-        <v>26873500</v>
+        <v>26473200</v>
       </c>
       <c r="J61" s="3">
+        <v>27278200</v>
+      </c>
+      <c r="K61" s="3">
         <v>27790900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>28115400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>27947800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>29338200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>28326800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>30052900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>32828400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>35839200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>37259400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>38486000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>38586200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>37173100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>36605000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>33965600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>33739000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>32441500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>32027200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>34920400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>35699100</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>37405600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>37431100</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>38250500</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>36521200</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>9602800</v>
+        <v>9449300</v>
       </c>
       <c r="E62" s="3">
-        <v>9012000</v>
+        <v>9747400</v>
       </c>
       <c r="F62" s="3">
-        <v>8312000</v>
+        <v>9147700</v>
       </c>
       <c r="G62" s="3">
-        <v>8022700</v>
+        <v>8437200</v>
       </c>
       <c r="H62" s="3">
-        <v>8070600</v>
+        <v>8143500</v>
       </c>
       <c r="I62" s="3">
-        <v>7593200</v>
+        <v>8192100</v>
       </c>
       <c r="J62" s="3">
+        <v>7707600</v>
+      </c>
+      <c r="K62" s="3">
         <v>7528900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>6977600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>7137200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>7774600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>7061100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>6336400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>6416800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>6975900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>7180400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>8188900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>7779100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>7906600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>8323600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>8124200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>8671300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>7800000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>7656300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>7269000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>7278500</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>7072300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>6802600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>6766700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>5977300</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5338,8 +5486,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5430,8 +5581,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5522,100 +5676,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>63631400</v>
+        <v>63276700</v>
       </c>
       <c r="E66" s="3">
-        <v>63260700</v>
+        <v>64589700</v>
       </c>
       <c r="F66" s="3">
-        <v>59847400</v>
+        <v>64213400</v>
       </c>
       <c r="G66" s="3">
-        <v>62738400</v>
+        <v>60748700</v>
       </c>
       <c r="H66" s="3">
-        <v>66350000</v>
+        <v>63683300</v>
       </c>
       <c r="I66" s="3">
-        <v>66504400</v>
+        <v>67349200</v>
       </c>
       <c r="J66" s="3">
+        <v>67506000</v>
+      </c>
+      <c r="K66" s="3">
         <v>61872100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>60471700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>59233700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>60973500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>56333100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>56483400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>59007300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>64958700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>70379700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>73667400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>72465300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>73055600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>73829900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>72239100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>70300400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>66567400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>66280800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>69332300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>68053100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>69759100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>68909600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>71093200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>64647500</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5648,8 +5808,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5740,8 +5901,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5832,8 +5996,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5924,8 +6091,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6016,100 +6186,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>33804400</v>
+        <v>35324900</v>
       </c>
       <c r="E72" s="3">
-        <v>33059200</v>
+        <v>34313500</v>
       </c>
       <c r="F72" s="3">
-        <v>32141000</v>
+        <v>33557100</v>
       </c>
       <c r="G72" s="3">
-        <v>31238800</v>
+        <v>32625000</v>
       </c>
       <c r="H72" s="3">
-        <v>29730700</v>
+        <v>31709300</v>
       </c>
       <c r="I72" s="3">
-        <v>28869800</v>
+        <v>30178500</v>
       </c>
       <c r="J72" s="3">
+        <v>29304600</v>
+      </c>
+      <c r="K72" s="3">
         <v>27662000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>26560900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>26825200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>26541400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>25153800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>24743600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>26163700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>28238800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>29621800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>30109600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>30037200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>28668100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>29585900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>28566200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>22079200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>25998200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>26247000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>25531600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>24759700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>23601500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>22619600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>21765100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>21151000</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6200,8 +6376,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6292,8 +6471,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6384,100 +6566,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>46888600</v>
+        <v>47858700</v>
       </c>
       <c r="E76" s="3">
-        <v>45046800</v>
+        <v>47594700</v>
       </c>
       <c r="F76" s="3">
-        <v>42281900</v>
+        <v>45725200</v>
       </c>
       <c r="G76" s="3">
-        <v>40639600</v>
+        <v>42918600</v>
       </c>
       <c r="H76" s="3">
-        <v>40140700</v>
+        <v>41251700</v>
       </c>
       <c r="I76" s="3">
-        <v>38319000</v>
+        <v>40745200</v>
       </c>
       <c r="J76" s="3">
+        <v>38896000</v>
+      </c>
+      <c r="K76" s="3">
         <v>37218600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>34248700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>34165100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>35352000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>32404300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>30316100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>30647000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>33017300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>33633700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>39521800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>38703100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>38782900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>40969000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>39407500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>39762100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>36872200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>35931400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>37896800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>35850000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>34316500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>33104400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>32312900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>28320500</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6568,197 +6756,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>1350600</v>
+        <v>1820800</v>
       </c>
       <c r="E81" s="3">
-        <v>1678900</v>
+        <v>1371000</v>
       </c>
       <c r="F81" s="3">
-        <v>1924600</v>
+        <v>1704200</v>
       </c>
       <c r="G81" s="3">
-        <v>2003200</v>
+        <v>1953500</v>
       </c>
       <c r="H81" s="3">
-        <v>1753700</v>
+        <v>2033300</v>
       </c>
       <c r="I81" s="3">
-        <v>1826000</v>
+        <v>1780100</v>
       </c>
       <c r="J81" s="3">
+        <v>1853500</v>
+      </c>
+      <c r="K81" s="3">
         <v>1868900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1570700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1538400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1405800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>967900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>651700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>369800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>533600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>497200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>919400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1002800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1145300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>616500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1200700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>970400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1076400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>376500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1252300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1153100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1001200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>672400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>961100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>539600</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6791,100 +6988,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>451900</v>
+        <v>482300</v>
       </c>
       <c r="E83" s="3">
-        <v>460200</v>
+        <v>458700</v>
       </c>
       <c r="F83" s="3">
-        <v>440600</v>
+        <v>467100</v>
       </c>
       <c r="G83" s="3">
-        <v>460100</v>
+        <v>447300</v>
       </c>
       <c r="H83" s="3">
-        <v>471700</v>
+        <v>467000</v>
       </c>
       <c r="I83" s="3">
-        <v>438300</v>
+        <v>478800</v>
       </c>
       <c r="J83" s="3">
+        <v>444900</v>
+      </c>
+      <c r="K83" s="3">
         <v>473800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>536800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>526500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>543100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>520500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>492200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>545800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>537500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>623100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>600400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>541700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>554500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>496000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>442500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>411100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>396100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>413800</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>448800</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>449300</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>429100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>410100</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>432800</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>438700</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6975,8 +7176,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7067,8 +7271,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7159,8 +7366,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7251,8 +7461,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7343,100 +7556,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>675200</v>
+        <v>1449800</v>
       </c>
       <c r="E89" s="3">
-        <v>2422400</v>
+        <v>685300</v>
       </c>
       <c r="F89" s="3">
-        <v>2972300</v>
+        <v>2458800</v>
       </c>
       <c r="G89" s="3">
-        <v>1922500</v>
+        <v>3017100</v>
       </c>
       <c r="H89" s="3">
-        <v>195400</v>
+        <v>1951400</v>
       </c>
       <c r="I89" s="3">
-        <v>1865400</v>
+        <v>198400</v>
       </c>
       <c r="J89" s="3">
+        <v>1893500</v>
+      </c>
+      <c r="K89" s="3">
         <v>2973900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>356300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>921800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1317900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1916000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>891400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1688800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1399300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1229000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>548400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1827000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1171400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>472800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1886300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>251200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1223700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1352500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>2182700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-372700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1833000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1624300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1312000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>298600</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7469,100 +7688,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-80828000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-78404000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-63111000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-52536000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-66573000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-54756000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-54200000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-44019000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-50278000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-44762000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-341500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-275500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-358300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-357300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-700100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-669200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-792800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-579100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-566500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-717000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-868800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-680800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-616300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>707600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-337700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-384300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-196300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-458100</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-338400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-537000</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7653,8 +7876,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7745,100 +7971,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-679000</v>
+        <v>-184000</v>
       </c>
       <c r="E94" s="3">
-        <v>-1289900</v>
+        <v>-689300</v>
       </c>
       <c r="F94" s="3">
-        <v>-344900</v>
+        <v>-1309300</v>
       </c>
       <c r="G94" s="3">
-        <v>37200</v>
+        <v>-350100</v>
       </c>
       <c r="H94" s="3">
-        <v>-135400</v>
+        <v>37700</v>
       </c>
       <c r="I94" s="3">
-        <v>-741100</v>
+        <v>-137500</v>
       </c>
       <c r="J94" s="3">
+        <v>-752200</v>
+      </c>
+      <c r="K94" s="3">
         <v>61100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-286000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-405500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-680000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-98800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-618100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-901100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-925800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>186300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-718500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-156200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1012200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-2595500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1897000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1369400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-914400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-579400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-717100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-761300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-186100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-967700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-474900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-603200</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7871,100 +8103,104 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>-863000</v>
       </c>
       <c r="E96" s="3">
-        <v>-759100</v>
+        <v>0</v>
       </c>
       <c r="F96" s="3">
-        <v>0</v>
+        <v>-770600</v>
       </c>
       <c r="G96" s="3">
-        <v>-677400</v>
+        <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>0</v>
+        <v>-687600</v>
       </c>
       <c r="I96" s="3">
-        <v>-637800</v>
+        <v>0</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>-647400</v>
       </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>-502400</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>-551900</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>-492400</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>-582600</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-633600</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-636800</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-656300</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-631900</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-478400</v>
       </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-478400</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-397500</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8055,8 +8291,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8147,8 +8386,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8239,280 +8481,292 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-608600</v>
+        <v>-1659500</v>
       </c>
       <c r="E100" s="3">
-        <v>-2251600</v>
+        <v>-617800</v>
       </c>
       <c r="F100" s="3">
-        <v>-1706700</v>
+        <v>-2285500</v>
       </c>
       <c r="G100" s="3">
-        <v>-462800</v>
+        <v>-1732400</v>
       </c>
       <c r="H100" s="3">
-        <v>-1183000</v>
+        <v>-469800</v>
       </c>
       <c r="I100" s="3">
-        <v>-861800</v>
+        <v>-1200800</v>
       </c>
       <c r="J100" s="3">
+        <v>-874800</v>
+      </c>
+      <c r="K100" s="3">
         <v>-1439500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-322200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1286200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1266100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1451100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1099300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-343300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-752700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-130100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1862200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-68800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>202500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>2126800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-385900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>482800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-954700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1145700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-1020400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-2791000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-939700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1316100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-841900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>217200</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>54700</v>
+        <v>-116400</v>
       </c>
       <c r="E101" s="3">
-        <v>396500</v>
+        <v>55500</v>
       </c>
       <c r="F101" s="3">
-        <v>37400</v>
+        <v>402500</v>
       </c>
       <c r="G101" s="3">
-        <v>-306900</v>
+        <v>38000</v>
       </c>
       <c r="H101" s="3">
-        <v>110200</v>
+        <v>-311500</v>
       </c>
       <c r="I101" s="3">
-        <v>343500</v>
+        <v>111900</v>
       </c>
       <c r="J101" s="3">
+        <v>348700</v>
+      </c>
+      <c r="K101" s="3">
         <v>308400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>120700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-61400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-15900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>233800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-59100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>6600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>131300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-293800</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>148200</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-82300</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-72700</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>23700</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-142100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>124000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>45000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-335900</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>3300</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>100100</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>10700</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-65200</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>603600</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-59700</v>
       </c>
     </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-557900</v>
+        <v>-510100</v>
       </c>
       <c r="E102" s="3">
-        <v>-722600</v>
+        <v>-566300</v>
       </c>
       <c r="F102" s="3">
-        <v>958200</v>
+        <v>-733400</v>
       </c>
       <c r="G102" s="3">
-        <v>1189900</v>
+        <v>972700</v>
       </c>
       <c r="H102" s="3">
-        <v>-1012800</v>
+        <v>1207900</v>
       </c>
       <c r="I102" s="3">
-        <v>606000</v>
+        <v>-1028000</v>
       </c>
       <c r="J102" s="3">
+        <v>615100</v>
+      </c>
+      <c r="K102" s="3">
         <v>1903900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-131200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-831200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-644100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>600000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-885100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>451000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-148000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>991400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1884100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1519700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>289000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>27700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-404700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-643100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-600500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-708500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>448600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-3824900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>717900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-724700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>598900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-147200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MITSY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MITSY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="92">
   <si>
     <t>MITSY</t>
   </si>
@@ -656,414 +656,428 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="32" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="7" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="14" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="33" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>24405800</v>
+        <v>21222900</v>
       </c>
       <c r="E8" s="3">
-        <v>21758800</v>
+        <v>23102200</v>
       </c>
       <c r="F8" s="3">
-        <v>21225100</v>
+        <v>20596600</v>
       </c>
       <c r="G8" s="3">
-        <v>22039000</v>
+        <v>20091500</v>
       </c>
       <c r="H8" s="3">
-        <v>24349600</v>
+        <v>20861900</v>
       </c>
       <c r="I8" s="3">
-        <v>24960100</v>
+        <v>23049000</v>
       </c>
       <c r="J8" s="3">
+        <v>23627000</v>
+      </c>
+      <c r="K8" s="3">
         <v>25076400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>21036400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>21800100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>19886400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>19536500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>23476100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>14920200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>14487100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>15741000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>28986100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>16240900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>16340900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>14959400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>18687200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>16988500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>15394900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>14145800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>11201800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>11381200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>10959900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>10682200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>10539300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>10144100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>8977900</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>21871400</v>
+        <v>19083700</v>
       </c>
       <c r="E9" s="3">
-        <v>19685100</v>
+        <v>20703200</v>
       </c>
       <c r="F9" s="3">
-        <v>19198200</v>
+        <v>18633700</v>
       </c>
       <c r="G9" s="3">
-        <v>19491500</v>
+        <v>18172800</v>
       </c>
       <c r="H9" s="3">
-        <v>21745700</v>
+        <v>18450400</v>
       </c>
       <c r="I9" s="3">
-        <v>22813500</v>
+        <v>20584200</v>
       </c>
       <c r="J9" s="3">
+        <v>21595000</v>
+      </c>
+      <c r="K9" s="3">
         <v>22963900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>18701800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>19997700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>18017600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>17565000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>21751400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>13451500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>13099400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>14122800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>27233000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>14307400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>14328700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>13042800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>16713400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>15012100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>13487900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>12160100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>9567400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>9519200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>9110700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>8879700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>8666700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>8528400</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>7541800</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>2534400</v>
+        <v>2139200</v>
       </c>
       <c r="E10" s="3">
-        <v>2073700</v>
+        <v>2399000</v>
       </c>
       <c r="F10" s="3">
-        <v>2026900</v>
+        <v>1962900</v>
       </c>
       <c r="G10" s="3">
-        <v>2547600</v>
+        <v>1918700</v>
       </c>
       <c r="H10" s="3">
-        <v>2603900</v>
+        <v>2411500</v>
       </c>
       <c r="I10" s="3">
-        <v>2146600</v>
+        <v>2464800</v>
       </c>
       <c r="J10" s="3">
+        <v>2031900</v>
+      </c>
+      <c r="K10" s="3">
         <v>2112500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2334500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1802400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1868700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1971500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1724700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1468700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1387600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1618200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1753200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1933500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2012200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1916600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1973800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1976400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1906900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1985700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1634400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1861900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1849100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1802500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1872600</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1615700</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1436100</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1097,8 +1111,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1192,8 +1207,11 @@
       <c r="AG12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1287,103 +1305,109 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>59100</v>
+        <v>346300</v>
       </c>
       <c r="E14" s="3">
-        <v>9900</v>
+        <v>56000</v>
       </c>
       <c r="F14" s="3">
-        <v>17000</v>
+        <v>9400</v>
       </c>
       <c r="G14" s="3">
-        <v>93600</v>
+        <v>16100</v>
       </c>
       <c r="H14" s="3">
-        <v>35500</v>
+        <v>88600</v>
       </c>
       <c r="I14" s="3">
-        <v>71100</v>
+        <v>33600</v>
       </c>
       <c r="J14" s="3">
+        <v>67300</v>
+      </c>
+      <c r="K14" s="3">
         <v>1800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>32100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>10800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>163500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-1600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>90700</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>262100</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>38700</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>2600</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>874000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>82100</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>8300</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>15500</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>225400</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>20700</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>3800</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>8900</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>59600</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>91800</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>67000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>11600</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>48200</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
-      </c>
       <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1477,8 +1501,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1509,198 +1536,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>23154200</v>
+        <v>20094000</v>
       </c>
       <c r="E17" s="3">
-        <v>20563300</v>
+        <v>21917500</v>
       </c>
       <c r="F17" s="3">
-        <v>20120400</v>
+        <v>19465000</v>
       </c>
       <c r="G17" s="3">
-        <v>20912900</v>
+        <v>19045700</v>
       </c>
       <c r="H17" s="3">
-        <v>22733900</v>
+        <v>19795900</v>
       </c>
       <c r="I17" s="3">
-        <v>23875800</v>
+        <v>21519700</v>
       </c>
       <c r="J17" s="3">
+        <v>22600500</v>
+      </c>
+      <c r="K17" s="3">
         <v>23836300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>19830800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>20835700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>19119900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>18538500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>22976200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>14945300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>14328800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>15201000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>29074600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>15671900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>15581200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>14210600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>18422900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>16308000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>14800500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>13271100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>11108400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>10721200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>10139700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>9954000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>9794000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>9291500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>8516000</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1251600</v>
+        <v>1128900</v>
       </c>
       <c r="E18" s="3">
-        <v>1195500</v>
+        <v>1184700</v>
       </c>
       <c r="F18" s="3">
-        <v>1104800</v>
+        <v>1131600</v>
       </c>
       <c r="G18" s="3">
-        <v>1126100</v>
+        <v>1045800</v>
       </c>
       <c r="H18" s="3">
-        <v>1615700</v>
+        <v>1066000</v>
       </c>
       <c r="I18" s="3">
-        <v>1084300</v>
+        <v>1529400</v>
       </c>
       <c r="J18" s="3">
+        <v>1026400</v>
+      </c>
+      <c r="K18" s="3">
         <v>1240000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1205600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>964400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>766500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>998000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>500000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-25200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>158300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>540000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-88400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>569000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>759700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>748700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>264200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>680500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>594400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>874700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>93400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>660000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>820200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>728200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>745300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>852600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>461900</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1734,483 +1768,499 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>1316500</v>
+        <v>1519100</v>
       </c>
       <c r="E20" s="3">
-        <v>988200</v>
+        <v>1246100</v>
       </c>
       <c r="F20" s="3">
-        <v>1257000</v>
+        <v>935400</v>
       </c>
       <c r="G20" s="3">
-        <v>1382000</v>
+        <v>1189800</v>
       </c>
       <c r="H20" s="3">
-        <v>1149700</v>
+        <v>1308200</v>
       </c>
       <c r="I20" s="3">
-        <v>1363000</v>
+        <v>1088300</v>
       </c>
       <c r="J20" s="3">
+        <v>1290200</v>
+      </c>
+      <c r="K20" s="3">
         <v>1215700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1076700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1107600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1367000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>990700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>836800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>762100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>586800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>461600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>822000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1024200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>799300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1048100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>949200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>1042200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>982200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>815900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>682600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>963900</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>765600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>808400</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>451900</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>662000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>545900</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>3050400</v>
+        <v>3188000</v>
       </c>
       <c r="E21" s="3">
-        <v>2642400</v>
+        <v>2887500</v>
       </c>
       <c r="F21" s="3">
-        <v>2828900</v>
+        <v>2501300</v>
       </c>
       <c r="G21" s="3">
-        <v>2955400</v>
+        <v>2677800</v>
       </c>
       <c r="H21" s="3">
-        <v>3232300</v>
+        <v>2797600</v>
       </c>
       <c r="I21" s="3">
-        <v>2926100</v>
+        <v>3059700</v>
       </c>
       <c r="J21" s="3">
+        <v>2769800</v>
+      </c>
+      <c r="K21" s="3">
         <v>2900600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2756100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2608800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2659900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2531800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1857200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1229100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1290900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1539200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1356700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2193700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>2100800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>2351400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1709400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>2165200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1987800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>2086700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1189800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>2072700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>2035100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1965600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1607200</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1947400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1446600</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>278700</v>
+        <v>294700</v>
       </c>
       <c r="E22" s="3">
-        <v>282600</v>
+        <v>263900</v>
       </c>
       <c r="F22" s="3">
-        <v>260100</v>
+        <v>267500</v>
       </c>
       <c r="G22" s="3">
-        <v>280700</v>
+        <v>246200</v>
       </c>
       <c r="H22" s="3">
-        <v>224300</v>
+        <v>265700</v>
       </c>
       <c r="I22" s="3">
-        <v>156700</v>
+        <v>212300</v>
       </c>
       <c r="J22" s="3">
+        <v>148400</v>
+      </c>
+      <c r="K22" s="3">
         <v>110500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>76000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>69100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>82400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>105800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>77600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>92500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>100800</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>131600</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>178400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>205000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>212500</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>217600</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>194400</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>191600</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>191700</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>172300</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>149100</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>150300</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>156500</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>145100</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>140900</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>133700</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>118100</v>
       </c>
     </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>2289300</v>
+        <v>2353300</v>
       </c>
       <c r="E23" s="3">
-        <v>1901100</v>
+        <v>2167000</v>
       </c>
       <c r="F23" s="3">
-        <v>2101600</v>
+        <v>1799600</v>
       </c>
       <c r="G23" s="3">
-        <v>2227400</v>
+        <v>1989400</v>
       </c>
       <c r="H23" s="3">
-        <v>2541100</v>
+        <v>2108400</v>
       </c>
       <c r="I23" s="3">
-        <v>2290600</v>
+        <v>2405300</v>
       </c>
       <c r="J23" s="3">
+        <v>2168200</v>
+      </c>
+      <c r="K23" s="3">
         <v>2345200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2206300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2002900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2051000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1883000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1259100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>644500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>644300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>870000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>555100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1388200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1346500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1579200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1019000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1531100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1384900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1518300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>626900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1473600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1429300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1391500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1056300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1380900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>889700</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>443000</v>
+        <v>201500</v>
       </c>
       <c r="E24" s="3">
-        <v>481500</v>
+        <v>419400</v>
       </c>
       <c r="F24" s="3">
-        <v>358300</v>
+        <v>455800</v>
       </c>
       <c r="G24" s="3">
-        <v>257400</v>
+        <v>339100</v>
       </c>
       <c r="H24" s="3">
-        <v>476500</v>
+        <v>243700</v>
       </c>
       <c r="I24" s="3">
-        <v>486500</v>
+        <v>451100</v>
       </c>
       <c r="J24" s="3">
+        <v>460500</v>
+      </c>
+      <c r="K24" s="3">
         <v>401700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>299100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>402700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>482800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>413000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>260700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-32100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>250100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>301300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>88400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>409100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>280700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>343700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>397900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>289000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>367300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>372800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>201200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>158300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>234300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>338000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>320800</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>367600</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>316000</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2304,198 +2354,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>1846300</v>
+        <v>2151800</v>
       </c>
       <c r="E26" s="3">
-        <v>1419600</v>
+        <v>1747700</v>
       </c>
       <c r="F26" s="3">
-        <v>1743400</v>
+        <v>1343800</v>
       </c>
       <c r="G26" s="3">
-        <v>1970000</v>
+        <v>1650200</v>
       </c>
       <c r="H26" s="3">
-        <v>2064600</v>
+        <v>1864700</v>
       </c>
       <c r="I26" s="3">
-        <v>1804100</v>
+        <v>1954300</v>
       </c>
       <c r="J26" s="3">
+        <v>1707800</v>
+      </c>
+      <c r="K26" s="3">
         <v>1943500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1907200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1600200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1568200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1470000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>998400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>676500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>394200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>568600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>466700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>979200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1065800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1235500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>621100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1242100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1017600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1145500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>425700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1315300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1195000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1053500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>735500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1013300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>573700</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>1820800</v>
+        <v>2151800</v>
       </c>
       <c r="E27" s="3">
-        <v>1371000</v>
+        <v>1723500</v>
       </c>
       <c r="F27" s="3">
-        <v>1704200</v>
+        <v>1297800</v>
       </c>
       <c r="G27" s="3">
-        <v>1953500</v>
+        <v>1613200</v>
       </c>
       <c r="H27" s="3">
-        <v>2033300</v>
+        <v>1849200</v>
       </c>
       <c r="I27" s="3">
-        <v>1780100</v>
+        <v>1924700</v>
       </c>
       <c r="J27" s="3">
+        <v>1685000</v>
+      </c>
+      <c r="K27" s="3">
         <v>1853500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1868900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1570700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1538400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1405800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>967900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>651700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>369800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>533600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>497200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>919400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1002800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1145300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>616500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1200700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>970400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1076400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>376500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1252300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1153100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1001200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>672400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>961100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>539600</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2589,8 +2648,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2684,8 +2746,11 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2779,8 +2844,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2874,198 +2942,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-1316500</v>
+        <v>-1519100</v>
       </c>
       <c r="E32" s="3">
-        <v>-988200</v>
+        <v>-1246100</v>
       </c>
       <c r="F32" s="3">
-        <v>-1257000</v>
+        <v>-935400</v>
       </c>
       <c r="G32" s="3">
-        <v>-1382000</v>
+        <v>-1189800</v>
       </c>
       <c r="H32" s="3">
-        <v>-1149700</v>
+        <v>-1308200</v>
       </c>
       <c r="I32" s="3">
-        <v>-1363000</v>
+        <v>-1088300</v>
       </c>
       <c r="J32" s="3">
+        <v>-1290200</v>
+      </c>
+      <c r="K32" s="3">
         <v>-1215700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1076700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1107600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1367000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-990700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-836800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-762100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-586800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-461600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-822000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1024200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-799300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1048100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-949200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-1042200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-982200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-815900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-682600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-963900</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-765600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-808400</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-451900</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-662000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-545900</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>1820800</v>
+        <v>2151800</v>
       </c>
       <c r="E33" s="3">
-        <v>1371000</v>
+        <v>1723500</v>
       </c>
       <c r="F33" s="3">
-        <v>1704200</v>
+        <v>1297800</v>
       </c>
       <c r="G33" s="3">
-        <v>1953500</v>
+        <v>1613200</v>
       </c>
       <c r="H33" s="3">
-        <v>2033300</v>
+        <v>1849200</v>
       </c>
       <c r="I33" s="3">
-        <v>1780100</v>
+        <v>1924700</v>
       </c>
       <c r="J33" s="3">
+        <v>1685000</v>
+      </c>
+      <c r="K33" s="3">
         <v>1853500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1868900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1570700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1538400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1405800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>967900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>651700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>369800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>533600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>497200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>919400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1002800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1145300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>616500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1200700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>970400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1076400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>376500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1252300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1153100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1001200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>672400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>961100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>539600</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3159,203 +3236,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>1820800</v>
+        <v>2151800</v>
       </c>
       <c r="E35" s="3">
-        <v>1371000</v>
+        <v>1723500</v>
       </c>
       <c r="F35" s="3">
-        <v>1704200</v>
+        <v>1297800</v>
       </c>
       <c r="G35" s="3">
-        <v>1953500</v>
+        <v>1613200</v>
       </c>
       <c r="H35" s="3">
-        <v>2033300</v>
+        <v>1849200</v>
       </c>
       <c r="I35" s="3">
-        <v>1780100</v>
+        <v>1924700</v>
       </c>
       <c r="J35" s="3">
+        <v>1685000</v>
+      </c>
+      <c r="K35" s="3">
         <v>1853500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1868900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1570700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1538400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1405800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>967900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>651700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>369800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>533600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>497200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>919400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1002800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1145300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>616500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1200700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>970400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1076400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>376500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1252300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1153100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1001200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>672400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>961100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>539600</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3389,8 +3475,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3424,863 +3511,891 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>7559700</v>
+        <v>5730500</v>
       </c>
       <c r="E41" s="3">
-        <v>8069800</v>
+        <v>7155900</v>
       </c>
       <c r="F41" s="3">
-        <v>8636000</v>
+        <v>7638800</v>
       </c>
       <c r="G41" s="3">
-        <v>9369500</v>
+        <v>8174800</v>
       </c>
       <c r="H41" s="3">
-        <v>8396800</v>
+        <v>8869000</v>
       </c>
       <c r="I41" s="3">
-        <v>7189000</v>
+        <v>7948300</v>
       </c>
       <c r="J41" s="3">
+        <v>6805000</v>
+      </c>
+      <c r="K41" s="3">
         <v>8217000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>7489000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5778600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>6202300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>7170000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>7537700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>7172600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>8563400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>8883000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>9327400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>8619900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>10596300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>9047000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>9188200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>8998400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>9253700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>9683800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>10227700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>10936200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>10487600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>14312400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>13338900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>14063500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>13464600</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>6219100</v>
+        <v>7274000</v>
       </c>
       <c r="E42" s="3">
-        <v>6398200</v>
+        <v>5886900</v>
       </c>
       <c r="F42" s="3">
-        <v>6160700</v>
+        <v>6056500</v>
       </c>
       <c r="G42" s="3">
-        <v>5209900</v>
+        <v>5831700</v>
       </c>
       <c r="H42" s="3">
-        <v>6824400</v>
+        <v>4931600</v>
       </c>
       <c r="I42" s="3">
-        <v>8581500</v>
+        <v>6459900</v>
       </c>
       <c r="J42" s="3">
+        <v>8123200</v>
+      </c>
+      <c r="K42" s="3">
         <v>7698600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>6625800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>6088600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>5687100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>4151400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>3048600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>3152600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>3119600</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>3626700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>4959100</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>3002000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>2707200</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>2753000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>2445800</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>3255400</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>2869100</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>2702600</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>2205000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>3030500</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>2627800</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>2445500</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>2374300</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>3915400</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>3786600</v>
       </c>
     </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>15519100</v>
+        <v>14458000</v>
       </c>
       <c r="E43" s="3">
-        <v>14955800</v>
+        <v>14690200</v>
       </c>
       <c r="F43" s="3">
-        <v>14241200</v>
+        <v>14157000</v>
       </c>
       <c r="G43" s="3">
-        <v>14768600</v>
+        <v>13480600</v>
       </c>
       <c r="H43" s="3">
-        <v>16071500</v>
+        <v>13979700</v>
       </c>
       <c r="I43" s="3">
-        <v>16315800</v>
+        <v>15213100</v>
       </c>
       <c r="J43" s="3">
+        <v>15444400</v>
+      </c>
+      <c r="K43" s="3">
         <v>16786300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>15292800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>15852800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>13571000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>13780400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>12847000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>12632200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>11204300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>12454600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>14294200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>16566500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>14911000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>15916900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>17338600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>17779600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>16564800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>15649400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>15964800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>17290200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>16461900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>14971500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>15428500</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>15480700</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>13205700</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>6219600</v>
+        <v>6161300</v>
       </c>
       <c r="E44" s="3">
-        <v>6171800</v>
+        <v>5887400</v>
       </c>
       <c r="F44" s="3">
-        <v>6478400</v>
+        <v>5842200</v>
       </c>
       <c r="G44" s="3">
-        <v>6339300</v>
+        <v>6132300</v>
       </c>
       <c r="H44" s="3">
-        <v>6889600</v>
+        <v>6000700</v>
       </c>
       <c r="I44" s="3">
-        <v>6887200</v>
+        <v>6521600</v>
       </c>
       <c r="J44" s="3">
+        <v>6519300</v>
+      </c>
+      <c r="K44" s="3">
         <v>6577600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>6305800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>6092800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>5348100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>5282900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>4361400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>4413800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>4318400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>4554700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>4879500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>6283100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>5890100</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>5901000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>5839800</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>5950700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>5828600</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>5150500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>4978300</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>5689100</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>5718500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>5394500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>5229200</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>5336700</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>4779400</v>
       </c>
     </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>3619500</v>
+        <v>3176900</v>
       </c>
       <c r="E45" s="3">
-        <v>3404900</v>
+        <v>3426200</v>
       </c>
       <c r="F45" s="3">
-        <v>4058600</v>
+        <v>3223100</v>
       </c>
       <c r="G45" s="3">
-        <v>2561200</v>
+        <v>3841800</v>
       </c>
       <c r="H45" s="3">
-        <v>2908400</v>
+        <v>2424400</v>
       </c>
       <c r="I45" s="3">
-        <v>2529300</v>
+        <v>2753100</v>
       </c>
       <c r="J45" s="3">
+        <v>2394200</v>
+      </c>
+      <c r="K45" s="3">
         <v>2765400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2245300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2327600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2275500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2305600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2036200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2036500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2138300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2623100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2875800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2941600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2909800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>3240200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>3592300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>3707100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>3593900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>3510500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>4828700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>4005100</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>3659200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>3525900</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>3320100</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>3359700</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>2996000</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>39137000</v>
+        <v>36800800</v>
       </c>
       <c r="E46" s="3">
-        <v>39000600</v>
+        <v>37046600</v>
       </c>
       <c r="F46" s="3">
-        <v>39575000</v>
+        <v>36917500</v>
       </c>
       <c r="G46" s="3">
-        <v>38248400</v>
+        <v>37461200</v>
       </c>
       <c r="H46" s="3">
-        <v>41090800</v>
+        <v>36205400</v>
       </c>
       <c r="I46" s="3">
-        <v>41502800</v>
+        <v>38896000</v>
       </c>
       <c r="J46" s="3">
+        <v>39286100</v>
+      </c>
+      <c r="K46" s="3">
         <v>42044900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>37958800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>36140400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>33084000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>32690400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>29831000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>29407700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>29344000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>32142100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>36336100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>37413100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>37014400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>36858100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>38404700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>39691200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>38110200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>36696800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>38204500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>40951100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>38955000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>40649900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>39691000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>42156100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>38232400</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>49672500</v>
+        <v>49044500</v>
       </c>
       <c r="E47" s="3">
-        <v>50064800</v>
+        <v>47019300</v>
       </c>
       <c r="F47" s="3">
-        <v>47087000</v>
+        <v>47390700</v>
       </c>
       <c r="G47" s="3">
-        <v>44428700</v>
+        <v>44572000</v>
       </c>
       <c r="H47" s="3">
-        <v>43265600</v>
+        <v>42055700</v>
       </c>
       <c r="I47" s="3">
-        <v>44961200</v>
+        <v>40954600</v>
       </c>
       <c r="J47" s="3">
+        <v>42559700</v>
+      </c>
+      <c r="K47" s="3">
         <v>43167900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>41318100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>38904100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>40110200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>42558000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>38622100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>37234400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>38999900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>42508800</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>43819300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>50414800</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>49513500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>50532700</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>53209900</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>48784500</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>49446400</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>45792300</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>44126500</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>45878300</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>44160100</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>42595400</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>41700800</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>39980100</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>35285000</v>
       </c>
     </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>17667000</v>
+        <v>17122300</v>
       </c>
       <c r="E48" s="3">
-        <v>18299700</v>
+        <v>16723400</v>
       </c>
       <c r="F48" s="3">
-        <v>18613000</v>
+        <v>17322300</v>
       </c>
       <c r="G48" s="3">
-        <v>17410100</v>
+        <v>17618800</v>
       </c>
       <c r="H48" s="3">
-        <v>17178700</v>
+        <v>16480200</v>
       </c>
       <c r="I48" s="3">
-        <v>17968500</v>
+        <v>16261100</v>
       </c>
       <c r="J48" s="3">
+        <v>17008700</v>
+      </c>
+      <c r="K48" s="3">
         <v>17712200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>16662900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>16691900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>17196100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>17942800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>17369900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>17576200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>18818600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>20573600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>20908000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>22359200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>21602500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>21397900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>20646900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>20363100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>19807500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>18394900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>17346400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>17820100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>18003700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>17903900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>17769100</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>18403400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>16888800</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>2996600</v>
+        <v>2923600</v>
       </c>
       <c r="E49" s="3">
-        <v>2995800</v>
+        <v>2836600</v>
       </c>
       <c r="F49" s="3">
-        <v>2919000</v>
+        <v>2835800</v>
       </c>
       <c r="G49" s="3">
-        <v>1869100</v>
+        <v>2763100</v>
       </c>
       <c r="H49" s="3">
-        <v>1903300</v>
+        <v>1769300</v>
       </c>
       <c r="I49" s="3">
-        <v>1994800</v>
+        <v>1801600</v>
       </c>
       <c r="J49" s="3">
+        <v>1888200</v>
+      </c>
+      <c r="K49" s="3">
         <v>1898700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1680200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1568100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1529500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1604900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1336900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1365200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1507700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1644000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1720500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>2151300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>2186600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>2230100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1673000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1743600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1607100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1552500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1565800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1572800</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1615000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1568500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1496200</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1434400</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1274500</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4374,8 +4489,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4469,103 +4587,109 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1662300</v>
+        <v>1927600</v>
       </c>
       <c r="E52" s="3">
-        <v>1823600</v>
+        <v>1573500</v>
       </c>
       <c r="F52" s="3">
-        <v>1744800</v>
+        <v>1726200</v>
       </c>
       <c r="G52" s="3">
-        <v>1711000</v>
+        <v>1651600</v>
       </c>
       <c r="H52" s="3">
-        <v>1496600</v>
+        <v>1619600</v>
       </c>
       <c r="I52" s="3">
-        <v>1667200</v>
+        <v>1416700</v>
       </c>
       <c r="J52" s="3">
+        <v>1578100</v>
+      </c>
+      <c r="K52" s="3">
         <v>1578300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1470700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1415900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1479100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1529400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1577500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1215900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>984000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1107500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1229500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>850800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>851500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>819700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>864500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1064200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1091400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1002900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>969100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1006800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1169300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1357900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1356900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1432200</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1287300</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4659,103 +4783,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>111135400</v>
+        <v>107818800</v>
       </c>
       <c r="E54" s="3">
-        <v>112184500</v>
+        <v>105199400</v>
       </c>
       <c r="F54" s="3">
-        <v>109938700</v>
+        <v>106192400</v>
       </c>
       <c r="G54" s="3">
-        <v>103667400</v>
+        <v>104066600</v>
       </c>
       <c r="H54" s="3">
-        <v>104935000</v>
+        <v>98130200</v>
       </c>
       <c r="I54" s="3">
-        <v>108094400</v>
+        <v>99330100</v>
       </c>
       <c r="J54" s="3">
+        <v>102320900</v>
+      </c>
+      <c r="K54" s="3">
         <v>106402000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>99090600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>94720400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>93398900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>96325500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>88737300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>86799500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>89654300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>97976000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>104013400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>113189100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>111168500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>111838500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>114798900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>111646700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>110062600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>103439500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>102212200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>107229100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>103903100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>104075500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>102014000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>103406200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>92968100</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4789,8 +4919,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4824,578 +4955,597 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>11706600</v>
+        <v>10508000</v>
       </c>
       <c r="E57" s="3">
-        <v>10891000</v>
+        <v>11081300</v>
       </c>
       <c r="F57" s="3">
-        <v>10798300</v>
+        <v>10309300</v>
       </c>
       <c r="G57" s="3">
-        <v>10180000</v>
+        <v>10221500</v>
       </c>
       <c r="H57" s="3">
-        <v>11895800</v>
+        <v>9636300</v>
       </c>
       <c r="I57" s="3">
-        <v>11584600</v>
+        <v>11260500</v>
       </c>
       <c r="J57" s="3">
+        <v>10965800</v>
+      </c>
+      <c r="K57" s="3">
         <v>12544700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>11547900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>11758900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>10074300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>10382200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>9311600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>8737600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>8288800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>8744100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>10012600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>11770300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>10845800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>11551100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>12707100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>13217100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>12028200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>11694800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>11429100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>12147200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>11328200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>10649200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>10676900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>10787700</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>8887300</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>7030500</v>
+        <v>6169700</v>
       </c>
       <c r="E58" s="3">
-        <v>7238900</v>
+        <v>6655000</v>
       </c>
       <c r="F58" s="3">
-        <v>6315700</v>
+        <v>6852300</v>
       </c>
       <c r="G58" s="3">
-        <v>8379400</v>
+        <v>5978400</v>
       </c>
       <c r="H58" s="3">
-        <v>8410600</v>
+        <v>7931800</v>
       </c>
       <c r="I58" s="3">
-        <v>8743900</v>
+        <v>7961400</v>
       </c>
       <c r="J58" s="3">
+        <v>8276900</v>
+      </c>
+      <c r="K58" s="3">
         <v>7751000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>4595500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>5029900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>5764700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>5962600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>5327600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>5047300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>5228200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>6306000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>6143800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>6544700</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>7261900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>8192800</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>7845800</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>7553600</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>6959600</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>6294800</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>6184300</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>5829800</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>5542100</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>6488500</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>6146100</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>7075800</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>6388700</v>
       </c>
     </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>7627400</v>
+        <v>8150200</v>
       </c>
       <c r="E59" s="3">
-        <v>8230400</v>
+        <v>7220000</v>
       </c>
       <c r="F59" s="3">
-        <v>8498400</v>
+        <v>7790800</v>
       </c>
       <c r="G59" s="3">
-        <v>6827700</v>
+        <v>8044500</v>
       </c>
       <c r="H59" s="3">
-        <v>7746100</v>
+        <v>6463000</v>
       </c>
       <c r="I59" s="3">
-        <v>10894200</v>
+        <v>7332400</v>
       </c>
       <c r="J59" s="3">
+        <v>10312300</v>
+      </c>
+      <c r="K59" s="3">
         <v>10810700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>9145900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>6802800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>6487000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>5634600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4516000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4513900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4330200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>4931400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>7640400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>6186700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>5577100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>5804100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>5781200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>6905100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>6461800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>6059700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>6783400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>6711400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>5826600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>5765000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>5564600</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>5821700</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>4722300</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>26364400</v>
+        <v>24828000</v>
       </c>
       <c r="E60" s="3">
-        <v>26360300</v>
+        <v>24956300</v>
       </c>
       <c r="F60" s="3">
-        <v>25612400</v>
+        <v>24952400</v>
       </c>
       <c r="G60" s="3">
-        <v>25387100</v>
+        <v>24244400</v>
       </c>
       <c r="H60" s="3">
-        <v>28052600</v>
+        <v>24031100</v>
       </c>
       <c r="I60" s="3">
-        <v>31222700</v>
+        <v>26554200</v>
       </c>
       <c r="J60" s="3">
+        <v>29555000</v>
+      </c>
+      <c r="K60" s="3">
         <v>31106500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>25289300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>23591600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>22326000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>21979400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>19155200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>18298800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>17847200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>19981500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>23796800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>24501800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>23684800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>25548000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>26334000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>27675800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>25449500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>24049300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>24396900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>24688500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>22697000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>22902800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>22387600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>23685200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>19998200</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>25952900</v>
+        <v>24301500</v>
       </c>
       <c r="E61" s="3">
-        <v>27000400</v>
+        <v>24566700</v>
       </c>
       <c r="F61" s="3">
-        <v>28002900</v>
+        <v>25558300</v>
       </c>
       <c r="G61" s="3">
-        <v>25594000</v>
+        <v>26507200</v>
       </c>
       <c r="H61" s="3">
-        <v>26095200</v>
+        <v>24227000</v>
       </c>
       <c r="I61" s="3">
-        <v>26473200</v>
+        <v>24701400</v>
       </c>
       <c r="J61" s="3">
+        <v>25059200</v>
+      </c>
+      <c r="K61" s="3">
         <v>27278200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>27790900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>28115400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>27947800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>29338200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>28326800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>30052900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>32828400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>35839200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>37259400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>38486000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>38586200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>37173100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>36605000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>33965600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>33739000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>32441500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>32027200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>34920400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>35699100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>37405600</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>37431100</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>38250500</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>36521200</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>9449300</v>
+        <v>9117100</v>
       </c>
       <c r="E62" s="3">
-        <v>9747400</v>
+        <v>8944600</v>
       </c>
       <c r="F62" s="3">
-        <v>9147700</v>
+        <v>9226800</v>
       </c>
       <c r="G62" s="3">
-        <v>8437200</v>
+        <v>8659100</v>
       </c>
       <c r="H62" s="3">
-        <v>8143500</v>
+        <v>7986500</v>
       </c>
       <c r="I62" s="3">
-        <v>8192100</v>
+        <v>7708500</v>
       </c>
       <c r="J62" s="3">
+        <v>7754600</v>
+      </c>
+      <c r="K62" s="3">
         <v>7707600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>7528900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>6977600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>7137200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>7774600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>7061100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>6336400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>6416800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>6975900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>7180400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>8188900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>7779100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>7906600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>8323600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>8124200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>8671300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>7800000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>7656300</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>7269000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>7278500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>7072300</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>6802600</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>6766700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>5977300</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5489,8 +5639,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5584,8 +5737,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5679,103 +5835,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>63276700</v>
+        <v>59701800</v>
       </c>
       <c r="E66" s="3">
-        <v>64589700</v>
+        <v>59896900</v>
       </c>
       <c r="F66" s="3">
-        <v>64213400</v>
+        <v>61139800</v>
       </c>
       <c r="G66" s="3">
-        <v>60748700</v>
+        <v>60783600</v>
       </c>
       <c r="H66" s="3">
-        <v>63683300</v>
+        <v>57504000</v>
       </c>
       <c r="I66" s="3">
-        <v>67349200</v>
+        <v>60281800</v>
       </c>
       <c r="J66" s="3">
+        <v>63752000</v>
+      </c>
+      <c r="K66" s="3">
         <v>67506000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>61872100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>60471700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>59233700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>60973500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>56333100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>56483400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>59007300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>64958700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>70379700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>73667400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>72465300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>73055600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>73829900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>72239100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>70300400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>66567400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>66280800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>69332300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>68053100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>69759100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>68909600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>71093200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>64647500</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5809,8 +5971,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5904,8 +6067,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5999,8 +6165,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6094,8 +6263,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6189,103 +6361,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>35324900</v>
+        <v>35420100</v>
       </c>
       <c r="E72" s="3">
-        <v>34313500</v>
+        <v>33438100</v>
       </c>
       <c r="F72" s="3">
-        <v>33557100</v>
+        <v>32480700</v>
       </c>
       <c r="G72" s="3">
-        <v>32625000</v>
+        <v>31764700</v>
       </c>
       <c r="H72" s="3">
-        <v>31709300</v>
+        <v>30882500</v>
       </c>
       <c r="I72" s="3">
-        <v>30178500</v>
+        <v>30015600</v>
       </c>
       <c r="J72" s="3">
+        <v>28566600</v>
+      </c>
+      <c r="K72" s="3">
         <v>29304600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>27662000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>26560900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>26825200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>26541400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>25153800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>24743600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>26163700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>28238800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>29621800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>30109600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>30037200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>28668100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>29585900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>28566200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>22079200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>25998200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>26247000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>25531600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>24759700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>23601500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>22619600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>21765100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>21151000</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6379,8 +6557,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6474,8 +6655,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6569,103 +6753,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>47858700</v>
+        <v>48117000</v>
       </c>
       <c r="E76" s="3">
-        <v>47594700</v>
+        <v>45302400</v>
       </c>
       <c r="F76" s="3">
-        <v>45725200</v>
+        <v>45052600</v>
       </c>
       <c r="G76" s="3">
-        <v>42918600</v>
+        <v>43282900</v>
       </c>
       <c r="H76" s="3">
-        <v>41251700</v>
+        <v>40626200</v>
       </c>
       <c r="I76" s="3">
-        <v>40745200</v>
+        <v>39048300</v>
       </c>
       <c r="J76" s="3">
+        <v>38568900</v>
+      </c>
+      <c r="K76" s="3">
         <v>38896000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>37218600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>34248700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>34165100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>35352000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>32404300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>30316100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>30647000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>33017300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>33633700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>39521800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>38703100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>38782900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>40969000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>39407500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>39762100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>36872200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>35931400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>37896800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>35850000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>34316500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>33104400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>32312900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>28320500</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6759,203 +6949,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>1820800</v>
+        <v>2151800</v>
       </c>
       <c r="E81" s="3">
-        <v>1371000</v>
+        <v>1723500</v>
       </c>
       <c r="F81" s="3">
-        <v>1704200</v>
+        <v>1297800</v>
       </c>
       <c r="G81" s="3">
-        <v>1953500</v>
+        <v>1613200</v>
       </c>
       <c r="H81" s="3">
-        <v>2033300</v>
+        <v>1849200</v>
       </c>
       <c r="I81" s="3">
-        <v>1780100</v>
+        <v>1924700</v>
       </c>
       <c r="J81" s="3">
+        <v>1685000</v>
+      </c>
+      <c r="K81" s="3">
         <v>1853500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1868900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1570700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1538400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1405800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>967900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>651700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>369800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>533600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>497200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>919400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1002800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1145300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>616500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1200700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>970400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1076400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>376500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1252300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1153100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1001200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>672400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>961100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>539600</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6989,103 +7188,107 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>482300</v>
+        <v>540000</v>
       </c>
       <c r="E83" s="3">
-        <v>458700</v>
+        <v>456600</v>
       </c>
       <c r="F83" s="3">
-        <v>467100</v>
+        <v>434200</v>
       </c>
       <c r="G83" s="3">
-        <v>447300</v>
+        <v>442200</v>
       </c>
       <c r="H83" s="3">
-        <v>467000</v>
+        <v>423400</v>
       </c>
       <c r="I83" s="3">
-        <v>478800</v>
+        <v>442100</v>
       </c>
       <c r="J83" s="3">
+        <v>453200</v>
+      </c>
+      <c r="K83" s="3">
         <v>444900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>473800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>536800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>526500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>543100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>520500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>492200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>545800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>537500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>623100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>600400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>541700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>554500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>496000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>442500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>411100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>396100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>413800</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>448800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>449300</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>429100</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>410100</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>432800</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>438700</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7179,8 +7382,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7274,8 +7480,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7369,8 +7578,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7464,8 +7676,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7559,103 +7774,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>1449800</v>
+        <v>1166400</v>
       </c>
       <c r="E89" s="3">
-        <v>685300</v>
+        <v>1372400</v>
       </c>
       <c r="F89" s="3">
-        <v>2458800</v>
+        <v>648700</v>
       </c>
       <c r="G89" s="3">
-        <v>3017100</v>
+        <v>2327500</v>
       </c>
       <c r="H89" s="3">
-        <v>1951400</v>
+        <v>2855900</v>
       </c>
       <c r="I89" s="3">
-        <v>198400</v>
+        <v>1847200</v>
       </c>
       <c r="J89" s="3">
+        <v>187800</v>
+      </c>
+      <c r="K89" s="3">
         <v>1893500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2973900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>356300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>921800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1317900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1916000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>891400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1688800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1399300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1229000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>548400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1827000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1171400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>472800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1886300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>251200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1223700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1352500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>2182700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-372700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1833000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1624300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1312000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>298600</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7689,103 +7910,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-58680000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-80828000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-78404000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-63111000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-52536000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-66573000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-54756000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-54200000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-44019000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-50278000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-44762000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-341500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-275500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-358300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-357300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-700100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-669200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-792800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-579100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-566500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-717000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-868800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-680800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-616300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>707600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-337700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-384300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-196300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-458100</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-338400</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-537000</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7879,8 +8104,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7974,103 +8202,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-184000</v>
+        <v>-661700</v>
       </c>
       <c r="E94" s="3">
-        <v>-689300</v>
+        <v>-174200</v>
       </c>
       <c r="F94" s="3">
-        <v>-1309300</v>
+        <v>-652400</v>
       </c>
       <c r="G94" s="3">
-        <v>-350100</v>
+        <v>-1239300</v>
       </c>
       <c r="H94" s="3">
-        <v>37700</v>
+        <v>-331400</v>
       </c>
       <c r="I94" s="3">
-        <v>-137500</v>
+        <v>35700</v>
       </c>
       <c r="J94" s="3">
+        <v>-130100</v>
+      </c>
+      <c r="K94" s="3">
         <v>-752200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>61100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-286000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-405500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-680000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-98800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-618100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-901100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-925800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>186300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-718500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-156200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1012200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-2595500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1897000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1369400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-914400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-579400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-717100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-761300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-186100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-967700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-474900</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-603200</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8104,103 +8338,107 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-863000</v>
+        <v>0</v>
       </c>
       <c r="E96" s="3">
-        <v>0</v>
+        <v>-816900</v>
       </c>
       <c r="F96" s="3">
-        <v>-770600</v>
+        <v>0</v>
       </c>
       <c r="G96" s="3">
-        <v>0</v>
+        <v>-729400</v>
       </c>
       <c r="H96" s="3">
-        <v>-687600</v>
+        <v>0</v>
       </c>
       <c r="I96" s="3">
-        <v>0</v>
+        <v>-650900</v>
       </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>-647400</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>-502400</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>-551900</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-492400</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
         <v>-582600</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
       <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
         <v>-633600</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
       <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
         <v>-636800</v>
       </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
       <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-656300</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
       <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-631900</v>
       </c>
-      <c r="AA96" s="3">
-        <v>0</v>
-      </c>
       <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-478400</v>
       </c>
-      <c r="AC96" s="3">
-        <v>0</v>
-      </c>
       <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-478400</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
       <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-397500</v>
       </c>
-      <c r="AG96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8294,8 +8532,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8389,8 +8630,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8484,289 +8728,301 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-1659500</v>
+        <v>-2144300</v>
       </c>
       <c r="E100" s="3">
-        <v>-617800</v>
+        <v>-1570800</v>
       </c>
       <c r="F100" s="3">
-        <v>-2285500</v>
+        <v>-584800</v>
       </c>
       <c r="G100" s="3">
-        <v>-1732400</v>
+        <v>-2163400</v>
       </c>
       <c r="H100" s="3">
-        <v>-469800</v>
+        <v>-1639900</v>
       </c>
       <c r="I100" s="3">
-        <v>-1200800</v>
+        <v>-444700</v>
       </c>
       <c r="J100" s="3">
+        <v>-1136700</v>
+      </c>
+      <c r="K100" s="3">
         <v>-874800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1439500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-322200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1286200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1266100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1451100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1099300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-343300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-752700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-130100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1862200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-68800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>202500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>2126800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-385900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>482800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-954700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-1145700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1020400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-2791000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-939700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1316100</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-841900</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>217200</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-116400</v>
+        <v>214400</v>
       </c>
       <c r="E101" s="3">
-        <v>55500</v>
+        <v>-110200</v>
       </c>
       <c r="F101" s="3">
-        <v>402500</v>
+        <v>52500</v>
       </c>
       <c r="G101" s="3">
-        <v>38000</v>
+        <v>381000</v>
       </c>
       <c r="H101" s="3">
-        <v>-311500</v>
+        <v>36000</v>
       </c>
       <c r="I101" s="3">
-        <v>111900</v>
+        <v>-294900</v>
       </c>
       <c r="J101" s="3">
+        <v>105900</v>
+      </c>
+      <c r="K101" s="3">
         <v>348700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>308400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>120700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-61400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-15900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>233800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-59100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>6600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>131300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-293800</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>148200</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-82300</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-72700</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>23700</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-142100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>124000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>45000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-335900</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>3300</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>100100</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>10700</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-65200</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>603600</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-59700</v>
       </c>
     </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-510100</v>
+        <v>-1425300</v>
       </c>
       <c r="E102" s="3">
-        <v>-566300</v>
+        <v>-482900</v>
       </c>
       <c r="F102" s="3">
-        <v>-733400</v>
+        <v>-536000</v>
       </c>
       <c r="G102" s="3">
-        <v>972700</v>
+        <v>-694300</v>
       </c>
       <c r="H102" s="3">
-        <v>1207900</v>
+        <v>920700</v>
       </c>
       <c r="I102" s="3">
-        <v>-1028000</v>
+        <v>1143300</v>
       </c>
       <c r="J102" s="3">
+        <v>-973100</v>
+      </c>
+      <c r="K102" s="3">
         <v>615100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1903900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-131200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-831200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-644100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>600000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-885100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>451000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-148000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>991400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-1884100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1519700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>289000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>27700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-404700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-643100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-600500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-708500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>448600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-3824900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>717900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-724700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>598900</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-147200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MITSY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MITSY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="92">
   <si>
     <t>MITSY</t>
   </si>
@@ -656,428 +656,438 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="14" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="33" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="12" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="34" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>21222900</v>
+        <v>27263400</v>
       </c>
       <c r="E8" s="3">
-        <v>23102200</v>
+        <v>23617900</v>
       </c>
       <c r="F8" s="3">
-        <v>20596600</v>
+        <v>25709300</v>
       </c>
       <c r="G8" s="3">
-        <v>20091500</v>
+        <v>22921000</v>
       </c>
       <c r="H8" s="3">
-        <v>20861900</v>
+        <v>22358800</v>
       </c>
       <c r="I8" s="3">
-        <v>23049000</v>
+        <v>23216200</v>
       </c>
       <c r="J8" s="3">
+        <v>25650200</v>
+      </c>
+      <c r="K8" s="3">
         <v>23627000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>25076400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>21036400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>21800100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>19886400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>19536500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>23476100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>14920200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>14487100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>15741000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>28986100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>16240900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>16340900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>14959400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>18687200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>16988500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>15394900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>14145800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>11201800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>11381200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>10959900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>10682200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>10539300</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>10144100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>8977900</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>19083700</v>
+        <v>24900700</v>
       </c>
       <c r="E9" s="3">
-        <v>20703200</v>
+        <v>21237300</v>
       </c>
       <c r="F9" s="3">
-        <v>18633700</v>
+        <v>23039600</v>
       </c>
       <c r="G9" s="3">
-        <v>18172800</v>
+        <v>20736600</v>
       </c>
       <c r="H9" s="3">
-        <v>18450400</v>
+        <v>20223600</v>
       </c>
       <c r="I9" s="3">
-        <v>20584200</v>
+        <v>20532500</v>
       </c>
       <c r="J9" s="3">
+        <v>22907200</v>
+      </c>
+      <c r="K9" s="3">
         <v>21595000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>22963900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>18701800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>19997700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>18017600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>17565000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>21751400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>13451500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>13099400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>14122800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>27233000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>14307400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>14328700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>13042800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>16713400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>15012100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>13487900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>12160100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>9567400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>9519200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>9110700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>8879700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>8666700</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>8528400</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>7541800</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>2139200</v>
+        <v>2362700</v>
       </c>
       <c r="E10" s="3">
-        <v>2399000</v>
+        <v>2380600</v>
       </c>
       <c r="F10" s="3">
-        <v>1962900</v>
+        <v>2669700</v>
       </c>
       <c r="G10" s="3">
-        <v>1918700</v>
+        <v>2184400</v>
       </c>
       <c r="H10" s="3">
-        <v>2411500</v>
+        <v>2135200</v>
       </c>
       <c r="I10" s="3">
-        <v>2464800</v>
+        <v>2683700</v>
       </c>
       <c r="J10" s="3">
+        <v>2743000</v>
+      </c>
+      <c r="K10" s="3">
         <v>2031900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2112500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2334500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1802400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1868700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1971500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1724700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1468700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1387600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1618200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1753200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1933500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2012200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1916600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1973800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1976400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1906900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1985700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1634400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1861900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1849100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1802500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1872600</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1615700</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1436100</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1112,8 +1122,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1210,8 +1221,11 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1308,106 +1322,112 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>346300</v>
+        <v>24600</v>
       </c>
       <c r="E14" s="3">
-        <v>56000</v>
+        <v>385300</v>
       </c>
       <c r="F14" s="3">
-        <v>9400</v>
+        <v>62300</v>
       </c>
       <c r="G14" s="3">
-        <v>16100</v>
+        <v>10400</v>
       </c>
       <c r="H14" s="3">
-        <v>88600</v>
+        <v>17900</v>
       </c>
       <c r="I14" s="3">
-        <v>33600</v>
+        <v>98600</v>
       </c>
       <c r="J14" s="3">
+        <v>37400</v>
+      </c>
+      <c r="K14" s="3">
         <v>67300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>32100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>10800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>163500</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-1600</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>90700</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>262100</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>38700</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>2600</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>874000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>82100</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>8300</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>15500</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>225400</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>20700</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>3800</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>8900</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>59600</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>91800</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>67000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>11600</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>48200</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
-      </c>
       <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1504,8 +1524,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1537,204 +1560,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>20094000</v>
+        <v>25758200</v>
       </c>
       <c r="E17" s="3">
-        <v>21917500</v>
+        <v>22361600</v>
       </c>
       <c r="F17" s="3">
-        <v>19465000</v>
+        <v>24390900</v>
       </c>
       <c r="G17" s="3">
-        <v>19045700</v>
+        <v>21661700</v>
       </c>
       <c r="H17" s="3">
-        <v>19795900</v>
+        <v>21195100</v>
       </c>
       <c r="I17" s="3">
-        <v>21519700</v>
+        <v>22030000</v>
       </c>
       <c r="J17" s="3">
+        <v>23948200</v>
+      </c>
+      <c r="K17" s="3">
         <v>22600500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>23836300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>19830800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>20835700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>19119900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>18538500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>22976200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>14945300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>14328800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>15201000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>29074600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>15671900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>15581200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>14210600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>18422900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>16308000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>14800500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>13271100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>11108400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>10721200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>10139700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>9954000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>9794000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>9291500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>8516000</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1128900</v>
+        <v>1505200</v>
       </c>
       <c r="E18" s="3">
-        <v>1184700</v>
+        <v>1256300</v>
       </c>
       <c r="F18" s="3">
-        <v>1131600</v>
+        <v>1318400</v>
       </c>
       <c r="G18" s="3">
-        <v>1045800</v>
+        <v>1259300</v>
       </c>
       <c r="H18" s="3">
-        <v>1066000</v>
+        <v>1163800</v>
       </c>
       <c r="I18" s="3">
-        <v>1529400</v>
+        <v>1186200</v>
       </c>
       <c r="J18" s="3">
+        <v>1701900</v>
+      </c>
+      <c r="K18" s="3">
         <v>1026400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1240000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1205600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>964400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>766500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>998000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>500000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-25200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>158300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>540000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-88400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>569000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>759700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>748700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>264200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>680500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>594400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>874700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>93400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>660000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>820200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>728200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>745300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>852600</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>461900</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1769,498 +1799,514 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>1519100</v>
+        <v>1278300</v>
       </c>
       <c r="E20" s="3">
-        <v>1246100</v>
+        <v>1690500</v>
       </c>
       <c r="F20" s="3">
-        <v>935400</v>
+        <v>1386800</v>
       </c>
       <c r="G20" s="3">
-        <v>1189800</v>
+        <v>1041000</v>
       </c>
       <c r="H20" s="3">
-        <v>1308200</v>
+        <v>1324100</v>
       </c>
       <c r="I20" s="3">
-        <v>1088300</v>
+        <v>1455900</v>
       </c>
       <c r="J20" s="3">
+        <v>1211100</v>
+      </c>
+      <c r="K20" s="3">
         <v>1290200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1215700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1076700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1107600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1367000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>990700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>836800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>762100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>586800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>461600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>822000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1024200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>799300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1048100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>949200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>1042200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>982200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>815900</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>682600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>963900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>765600</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>808400</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>451900</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>662000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>545900</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>3188000</v>
+        <v>3332600</v>
       </c>
       <c r="E21" s="3">
-        <v>2887500</v>
+        <v>3547700</v>
       </c>
       <c r="F21" s="3">
-        <v>2501300</v>
+        <v>3213300</v>
       </c>
       <c r="G21" s="3">
-        <v>2677800</v>
+        <v>2783600</v>
       </c>
       <c r="H21" s="3">
-        <v>2797600</v>
+        <v>2980000</v>
       </c>
       <c r="I21" s="3">
-        <v>3059700</v>
+        <v>3113300</v>
       </c>
       <c r="J21" s="3">
+        <v>3405000</v>
+      </c>
+      <c r="K21" s="3">
         <v>2769800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2900600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2756100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2608800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2659900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2531800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1857200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1229100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1290900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1539200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1356700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>2193700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>2100800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2351400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1709400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>2165200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1987800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>2086700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1189800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>2072700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>2035100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1965600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1607200</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1947400</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1446600</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>294700</v>
+        <v>314900</v>
       </c>
       <c r="E22" s="3">
-        <v>263900</v>
+        <v>327900</v>
       </c>
       <c r="F22" s="3">
-        <v>267500</v>
+        <v>293600</v>
       </c>
       <c r="G22" s="3">
-        <v>246200</v>
+        <v>297700</v>
       </c>
       <c r="H22" s="3">
-        <v>265700</v>
+        <v>274000</v>
       </c>
       <c r="I22" s="3">
-        <v>212300</v>
+        <v>295700</v>
       </c>
       <c r="J22" s="3">
+        <v>236200</v>
+      </c>
+      <c r="K22" s="3">
         <v>148400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>110500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>76000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>69100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>82400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>105800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>77600</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>92500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>100800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>131600</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>178400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>205000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>212500</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>217600</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>194400</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>191600</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>191700</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>172300</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>149100</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>150300</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>156500</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>145100</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>140900</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>133700</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>118100</v>
       </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>2353300</v>
+        <v>2468600</v>
       </c>
       <c r="E23" s="3">
-        <v>2167000</v>
+        <v>2618900</v>
       </c>
       <c r="F23" s="3">
-        <v>1799600</v>
+        <v>2411600</v>
       </c>
       <c r="G23" s="3">
-        <v>1989400</v>
+        <v>2002600</v>
       </c>
       <c r="H23" s="3">
-        <v>2108400</v>
+        <v>2213900</v>
       </c>
       <c r="I23" s="3">
-        <v>2405300</v>
+        <v>2346400</v>
       </c>
       <c r="J23" s="3">
+        <v>2676800</v>
+      </c>
+      <c r="K23" s="3">
         <v>2168200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2345200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2206300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2002900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2051000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1883000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1259100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>644500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>644300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>870000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>555100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1388200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1346500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1579200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1019000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1531100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1384900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1518300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>626900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1473600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1429300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1391500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1056300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1380900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>889700</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>201500</v>
+        <v>463900</v>
       </c>
       <c r="E24" s="3">
-        <v>419400</v>
+        <v>224300</v>
       </c>
       <c r="F24" s="3">
-        <v>455800</v>
+        <v>466700</v>
       </c>
       <c r="G24" s="3">
-        <v>339100</v>
+        <v>507200</v>
       </c>
       <c r="H24" s="3">
-        <v>243700</v>
+        <v>377400</v>
       </c>
       <c r="I24" s="3">
-        <v>451100</v>
+        <v>271200</v>
       </c>
       <c r="J24" s="3">
+        <v>502000</v>
+      </c>
+      <c r="K24" s="3">
         <v>460500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>401700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>299100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>402700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>482800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>413000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>260700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-32100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>250100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>301300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>88400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>409100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>280700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>343700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>397900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>289000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>367300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>372800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>201200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>158300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>234300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>338000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>320800</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>367600</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>316000</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2357,204 +2403,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>2151800</v>
+        <v>2004700</v>
       </c>
       <c r="E26" s="3">
-        <v>1747700</v>
+        <v>2394600</v>
       </c>
       <c r="F26" s="3">
-        <v>1343800</v>
+        <v>1944900</v>
       </c>
       <c r="G26" s="3">
-        <v>1650200</v>
+        <v>1495400</v>
       </c>
       <c r="H26" s="3">
-        <v>1864700</v>
+        <v>1836500</v>
       </c>
       <c r="I26" s="3">
-        <v>1954300</v>
+        <v>2075200</v>
       </c>
       <c r="J26" s="3">
+        <v>2174800</v>
+      </c>
+      <c r="K26" s="3">
         <v>1707800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1943500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1907200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1600200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1568200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1470000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>998400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>676500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>394200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>568600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>466700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>979200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1065800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1235500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>621100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1242100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1017600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1145500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>425700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1315300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1195000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1053500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>735500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>1013300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>573700</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>2151800</v>
+        <v>1960400</v>
       </c>
       <c r="E27" s="3">
-        <v>1723500</v>
+        <v>2394700</v>
       </c>
       <c r="F27" s="3">
-        <v>1297800</v>
+        <v>1918000</v>
       </c>
       <c r="G27" s="3">
-        <v>1613200</v>
+        <v>1444200</v>
       </c>
       <c r="H27" s="3">
-        <v>1849200</v>
+        <v>1795200</v>
       </c>
       <c r="I27" s="3">
-        <v>1924700</v>
+        <v>2057900</v>
       </c>
       <c r="J27" s="3">
+        <v>2141900</v>
+      </c>
+      <c r="K27" s="3">
         <v>1685000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1853500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1868900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1570700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1538400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1405800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>967900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>651700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>369800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>533600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>497200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>919400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1002800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1145300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>616500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1200700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>970400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1076400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>376500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1252300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1153100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1001200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>672400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>961100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>539600</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2651,8 +2706,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2749,8 +2807,11 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2847,8 +2908,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2945,204 +3009,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-1519100</v>
+        <v>-1278300</v>
       </c>
       <c r="E32" s="3">
-        <v>-1246100</v>
+        <v>-1690500</v>
       </c>
       <c r="F32" s="3">
-        <v>-935400</v>
+        <v>-1386800</v>
       </c>
       <c r="G32" s="3">
-        <v>-1189800</v>
+        <v>-1041000</v>
       </c>
       <c r="H32" s="3">
-        <v>-1308200</v>
+        <v>-1324100</v>
       </c>
       <c r="I32" s="3">
-        <v>-1088300</v>
+        <v>-1455900</v>
       </c>
       <c r="J32" s="3">
+        <v>-1211100</v>
+      </c>
+      <c r="K32" s="3">
         <v>-1290200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1215700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1076700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1107600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1367000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-990700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-836800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-762100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-586800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-461600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-822000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1024200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-799300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1048100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-949200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-1042200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-982200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-815900</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-682600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-963900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-765600</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-808400</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-451900</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-662000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-545900</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>2151800</v>
+        <v>1960400</v>
       </c>
       <c r="E33" s="3">
-        <v>1723500</v>
+        <v>2394700</v>
       </c>
       <c r="F33" s="3">
-        <v>1297800</v>
+        <v>1918000</v>
       </c>
       <c r="G33" s="3">
-        <v>1613200</v>
+        <v>1444200</v>
       </c>
       <c r="H33" s="3">
-        <v>1849200</v>
+        <v>1795200</v>
       </c>
       <c r="I33" s="3">
-        <v>1924700</v>
+        <v>2057900</v>
       </c>
       <c r="J33" s="3">
+        <v>2141900</v>
+      </c>
+      <c r="K33" s="3">
         <v>1685000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1853500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1868900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1570700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1538400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1405800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>967900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>651700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>369800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>533600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>497200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>919400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1002800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1145300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>616500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1200700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>970400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1076400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>376500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1252300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1153100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1001200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>672400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>961100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>539600</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3239,209 +3312,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>2151800</v>
+        <v>1960400</v>
       </c>
       <c r="E35" s="3">
-        <v>1723500</v>
+        <v>2394700</v>
       </c>
       <c r="F35" s="3">
-        <v>1297800</v>
+        <v>1918000</v>
       </c>
       <c r="G35" s="3">
-        <v>1613200</v>
+        <v>1444200</v>
       </c>
       <c r="H35" s="3">
-        <v>1849200</v>
+        <v>1795200</v>
       </c>
       <c r="I35" s="3">
-        <v>1924700</v>
+        <v>2057900</v>
       </c>
       <c r="J35" s="3">
+        <v>2141900</v>
+      </c>
+      <c r="K35" s="3">
         <v>1685000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1853500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1868900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1570700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1538400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1405800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>967900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>651700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>369800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>533600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>497200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>919400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1002800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1145300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>616500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1200700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>970400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1076400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>376500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1252300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1153100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1001200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>672400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>961100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>539600</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3476,8 +3558,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3512,890 +3595,918 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>5730500</v>
+        <v>7352400</v>
       </c>
       <c r="E41" s="3">
-        <v>7155900</v>
+        <v>6377200</v>
       </c>
       <c r="F41" s="3">
-        <v>7638800</v>
+        <v>7963400</v>
       </c>
       <c r="G41" s="3">
-        <v>8174800</v>
+        <v>8500800</v>
       </c>
       <c r="H41" s="3">
-        <v>8869000</v>
+        <v>9097300</v>
       </c>
       <c r="I41" s="3">
-        <v>7948300</v>
+        <v>9869900</v>
       </c>
       <c r="J41" s="3">
+        <v>8845300</v>
+      </c>
+      <c r="K41" s="3">
         <v>6805000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>8217000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>7489000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>5778600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>6202300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>7170000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>7537700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>7172600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>8563400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>8883000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>9327400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>8619900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>10596300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>9047000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>9188200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>8998400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>9253700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>9683800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>10227700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>10936200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>10487600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>14312400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>13338900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>14063500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>13464600</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>7274000</v>
+        <v>9228400</v>
       </c>
       <c r="E42" s="3">
-        <v>5886900</v>
+        <v>8094900</v>
       </c>
       <c r="F42" s="3">
-        <v>6056500</v>
+        <v>6551300</v>
       </c>
       <c r="G42" s="3">
-        <v>5831700</v>
+        <v>6740000</v>
       </c>
       <c r="H42" s="3">
-        <v>4931600</v>
+        <v>6489800</v>
       </c>
       <c r="I42" s="3">
-        <v>6459900</v>
+        <v>5488200</v>
       </c>
       <c r="J42" s="3">
+        <v>7188900</v>
+      </c>
+      <c r="K42" s="3">
         <v>8123200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>7698600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>6625800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>6088600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>5687100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>4151400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>3048600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>3152600</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>3119600</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>3626700</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>4959100</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>3002000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>2707200</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>2753000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>2445800</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>3255400</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>2869100</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>2702600</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>2205000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>3030500</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>2627800</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>2445500</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>2374300</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>3915400</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>3786600</v>
       </c>
     </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>14458000</v>
+        <v>17515300</v>
       </c>
       <c r="E43" s="3">
-        <v>14690200</v>
+        <v>16089700</v>
       </c>
       <c r="F43" s="3">
-        <v>14157000</v>
+        <v>16348000</v>
       </c>
       <c r="G43" s="3">
-        <v>13480600</v>
+        <v>15754600</v>
       </c>
       <c r="H43" s="3">
-        <v>13979700</v>
+        <v>15001900</v>
       </c>
       <c r="I43" s="3">
-        <v>15213100</v>
+        <v>15557400</v>
       </c>
       <c r="J43" s="3">
+        <v>16929900</v>
+      </c>
+      <c r="K43" s="3">
         <v>15444400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>16786300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>15292800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>15852800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>13571000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>13780400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>12847000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>12632200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>11204300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>12454600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>14294200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>16566500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>14911000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>15916900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>17338600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>17779600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>16564800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>15649400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>15964800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>17290200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>16461900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>14971500</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>15428500</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>15480700</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>13205700</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>6161300</v>
+        <v>7034200</v>
       </c>
       <c r="E44" s="3">
-        <v>5887400</v>
+        <v>6856600</v>
       </c>
       <c r="F44" s="3">
-        <v>5842200</v>
+        <v>6551800</v>
       </c>
       <c r="G44" s="3">
-        <v>6132300</v>
+        <v>6501500</v>
       </c>
       <c r="H44" s="3">
-        <v>6000700</v>
+        <v>6824400</v>
       </c>
       <c r="I44" s="3">
-        <v>6521600</v>
+        <v>6677900</v>
       </c>
       <c r="J44" s="3">
+        <v>7257600</v>
+      </c>
+      <c r="K44" s="3">
         <v>6519300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>6577600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>6305800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>6092800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>5348100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>5282900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>4361400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>4413800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>4318400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>4554700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>4879500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>6283100</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>5890100</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>5901000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>5839800</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>5950700</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>5828600</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>5150500</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>4978300</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>5689100</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>5718500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>5394500</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>5229200</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>5336700</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>4779400</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>3176900</v>
+        <v>3745000</v>
       </c>
       <c r="E45" s="3">
-        <v>3426200</v>
+        <v>3535500</v>
       </c>
       <c r="F45" s="3">
-        <v>3223100</v>
+        <v>3812900</v>
       </c>
       <c r="G45" s="3">
-        <v>3841800</v>
+        <v>3586800</v>
       </c>
       <c r="H45" s="3">
-        <v>2424400</v>
+        <v>4275400</v>
       </c>
       <c r="I45" s="3">
-        <v>2753100</v>
+        <v>2698000</v>
       </c>
       <c r="J45" s="3">
+        <v>3063800</v>
+      </c>
+      <c r="K45" s="3">
         <v>2394200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2765400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2245300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2327600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2275500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2305600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2036200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2036500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2138300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2623100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2875800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2941600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2909800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>3240200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>3592300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>3707100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>3593900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>3510500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>4828700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>4005100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>3659200</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>3525900</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>3320100</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>3359700</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>2996000</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>36800800</v>
+        <v>44875300</v>
       </c>
       <c r="E46" s="3">
-        <v>37046600</v>
+        <v>40953900</v>
       </c>
       <c r="F46" s="3">
-        <v>36917500</v>
+        <v>41227400</v>
       </c>
       <c r="G46" s="3">
-        <v>37461200</v>
+        <v>41083700</v>
       </c>
       <c r="H46" s="3">
-        <v>36205400</v>
+        <v>41688800</v>
       </c>
       <c r="I46" s="3">
-        <v>38896000</v>
+        <v>40291300</v>
       </c>
       <c r="J46" s="3">
+        <v>43285600</v>
+      </c>
+      <c r="K46" s="3">
         <v>39286100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>42044900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>37958800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>36140400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>33084000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>32690400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>29831000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>29407700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>29344000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>32142100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>36336100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>37413100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>37014400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>36858100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>38404700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>39691200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>38110200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>36696800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>38204500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>40951100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>38955000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>40649900</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>39691000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>42156100</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>38232400</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>49044500</v>
+        <v>56558400</v>
       </c>
       <c r="E47" s="3">
-        <v>47019300</v>
+        <v>54579300</v>
       </c>
       <c r="F47" s="3">
-        <v>47390700</v>
+        <v>52325600</v>
       </c>
       <c r="G47" s="3">
-        <v>44572000</v>
+        <v>52738800</v>
       </c>
       <c r="H47" s="3">
-        <v>42055700</v>
+        <v>49602000</v>
       </c>
       <c r="I47" s="3">
-        <v>40954600</v>
+        <v>46801800</v>
       </c>
       <c r="J47" s="3">
+        <v>45576500</v>
+      </c>
+      <c r="K47" s="3">
         <v>42559700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>43167900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>41318100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>38904100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>40110200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>42558000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>38622100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>37234400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>38999900</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>42508800</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>43819300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>50414800</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>49513500</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>50532700</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>53209900</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>48784500</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>49446400</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>45792300</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>44126500</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>45878300</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>44160100</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>42595400</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>41700800</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>39980100</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>35285000</v>
       </c>
     </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>17122300</v>
+        <v>20295400</v>
       </c>
       <c r="E48" s="3">
-        <v>16723400</v>
+        <v>19054600</v>
       </c>
       <c r="F48" s="3">
-        <v>17322300</v>
+        <v>18610700</v>
       </c>
       <c r="G48" s="3">
-        <v>17618800</v>
+        <v>19277100</v>
       </c>
       <c r="H48" s="3">
-        <v>16480200</v>
+        <v>19607100</v>
       </c>
       <c r="I48" s="3">
-        <v>16261100</v>
+        <v>18340000</v>
       </c>
       <c r="J48" s="3">
+        <v>18096300</v>
+      </c>
+      <c r="K48" s="3">
         <v>17008700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>17712200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>16662900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>16691900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>17196100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>17942800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>17369900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>17576200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>18818600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>20573600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>20908000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>22359200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>21602500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>21397900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>20646900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>20363100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>19807500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>18394900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>17346400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>17820100</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>18003700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>17903900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>17769100</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>18403400</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>16888800</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>2923600</v>
+        <v>3604500</v>
       </c>
       <c r="E49" s="3">
-        <v>2836600</v>
+        <v>3253500</v>
       </c>
       <c r="F49" s="3">
-        <v>2835800</v>
+        <v>3156700</v>
       </c>
       <c r="G49" s="3">
-        <v>2763100</v>
+        <v>3155800</v>
       </c>
       <c r="H49" s="3">
-        <v>1769300</v>
+        <v>3074900</v>
       </c>
       <c r="I49" s="3">
-        <v>1801600</v>
+        <v>1968900</v>
       </c>
       <c r="J49" s="3">
+        <v>2005000</v>
+      </c>
+      <c r="K49" s="3">
         <v>1888200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1898700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1680200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1568100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1529500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1604900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1336900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1365200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1507700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1644000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1720500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>2151300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>2186600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>2230100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1673000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1743600</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1607100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1552500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1565800</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1572800</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1615000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1568500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1496200</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1434400</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>1274500</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4492,8 +4603,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4590,106 +4704,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1927600</v>
+        <v>2323900</v>
       </c>
       <c r="E52" s="3">
-        <v>1573500</v>
+        <v>2145200</v>
       </c>
       <c r="F52" s="3">
-        <v>1726200</v>
+        <v>1751100</v>
       </c>
       <c r="G52" s="3">
-        <v>1651600</v>
+        <v>1921000</v>
       </c>
       <c r="H52" s="3">
-        <v>1619600</v>
+        <v>1838000</v>
       </c>
       <c r="I52" s="3">
-        <v>1416700</v>
+        <v>1802400</v>
       </c>
       <c r="J52" s="3">
+        <v>1576500</v>
+      </c>
+      <c r="K52" s="3">
         <v>1578100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1578300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1470700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1415900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1479100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1529400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1577500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1215900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>984000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1107500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1229500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>850800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>851500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>819700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>864500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1064200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1091400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1002900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>969100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1006800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1169300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1357900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1356900</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1432200</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1287300</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4786,106 +4906,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>107818800</v>
+        <v>127657400</v>
       </c>
       <c r="E54" s="3">
-        <v>105199400</v>
+        <v>119986500</v>
       </c>
       <c r="F54" s="3">
-        <v>106192400</v>
+        <v>117071400</v>
       </c>
       <c r="G54" s="3">
-        <v>104066600</v>
+        <v>118176500</v>
       </c>
       <c r="H54" s="3">
-        <v>98130200</v>
+        <v>115810800</v>
       </c>
       <c r="I54" s="3">
-        <v>99330100</v>
+        <v>109204500</v>
       </c>
       <c r="J54" s="3">
+        <v>110539800</v>
+      </c>
+      <c r="K54" s="3">
         <v>102320900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>106402000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>99090600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>94720400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>93398900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>96325500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>88737300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>86799500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>89654300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>97976000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>104013400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>113189100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>111168500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>111838500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>114798900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>111646700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>110062600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>103439500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>102212200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>107229100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>103903100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>104075500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>102014000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>103406200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>92968100</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4920,8 +5046,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4956,596 +5083,615 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>10508000</v>
+        <v>12892700</v>
       </c>
       <c r="E57" s="3">
-        <v>11081300</v>
+        <v>11693900</v>
       </c>
       <c r="F57" s="3">
-        <v>10309300</v>
+        <v>12331800</v>
       </c>
       <c r="G57" s="3">
-        <v>10221500</v>
+        <v>11472700</v>
       </c>
       <c r="H57" s="3">
-        <v>9636300</v>
+        <v>11375000</v>
       </c>
       <c r="I57" s="3">
-        <v>11260500</v>
+        <v>10723800</v>
       </c>
       <c r="J57" s="3">
+        <v>12531200</v>
+      </c>
+      <c r="K57" s="3">
         <v>10965800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>12544700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>11547900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>11758900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>10074300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>10382200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>9311600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>8737600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>8288800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>8744100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>10012600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>11770300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>10845800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>11551100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>12707100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>13217100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>12028200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>11694800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>11429100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>12147200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>11328200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>10649200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>10676900</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>10787700</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>8887300</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>6169700</v>
+        <v>8453500</v>
       </c>
       <c r="E58" s="3">
-        <v>6655000</v>
+        <v>6866000</v>
       </c>
       <c r="F58" s="3">
-        <v>6852300</v>
+        <v>7406000</v>
       </c>
       <c r="G58" s="3">
-        <v>5978400</v>
+        <v>7625600</v>
       </c>
       <c r="H58" s="3">
-        <v>7931800</v>
+        <v>6653100</v>
       </c>
       <c r="I58" s="3">
-        <v>7961400</v>
+        <v>8826900</v>
       </c>
       <c r="J58" s="3">
+        <v>8859900</v>
+      </c>
+      <c r="K58" s="3">
         <v>8276900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>7751000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>4595500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>5029900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>5764700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>5962600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>5327600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>5047300</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>5228200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>6306000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>6143800</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>6544700</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>7261900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>8192800</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>7845800</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>7553600</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>6959600</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>6294800</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>6184300</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>5829800</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>5542100</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>6488500</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>6146100</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>7075800</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>6388700</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>8150200</v>
+        <v>10238100</v>
       </c>
       <c r="E59" s="3">
-        <v>7220000</v>
+        <v>9070000</v>
       </c>
       <c r="F59" s="3">
-        <v>7790800</v>
+        <v>8034800</v>
       </c>
       <c r="G59" s="3">
-        <v>8044500</v>
+        <v>8670000</v>
       </c>
       <c r="H59" s="3">
-        <v>6463000</v>
+        <v>8952300</v>
       </c>
       <c r="I59" s="3">
-        <v>7332400</v>
+        <v>7192400</v>
       </c>
       <c r="J59" s="3">
+        <v>8159800</v>
+      </c>
+      <c r="K59" s="3">
         <v>10312300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>10810700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>9145900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>6802800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>6487000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>5634600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4516000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4513900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>4330200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>4931400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>7640400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>6186700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>5577100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>5804100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>5781200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>6905100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>6461800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>6059700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>6783400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>6711400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>5826600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>5765000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>5564600</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>5821700</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>4722300</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>24828000</v>
+        <v>31584300</v>
       </c>
       <c r="E60" s="3">
-        <v>24956300</v>
+        <v>27629900</v>
       </c>
       <c r="F60" s="3">
-        <v>24952400</v>
+        <v>27772600</v>
       </c>
       <c r="G60" s="3">
-        <v>24244400</v>
+        <v>27768300</v>
       </c>
       <c r="H60" s="3">
-        <v>24031100</v>
+        <v>26980400</v>
       </c>
       <c r="I60" s="3">
-        <v>26554200</v>
+        <v>26743100</v>
       </c>
       <c r="J60" s="3">
+        <v>29550900</v>
+      </c>
+      <c r="K60" s="3">
         <v>29555000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>31106500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>25289300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>23591600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>22326000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>21979400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>19155200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>18298800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>17847200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>19981500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>23796800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>24501800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>23684800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>25548000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>26334000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>27675800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>25449500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>24049300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>24396900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>24688500</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>22697000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>22902800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>22387600</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>23685200</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>19998200</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>24301500</v>
+        <v>27144000</v>
       </c>
       <c r="E61" s="3">
-        <v>24566700</v>
+        <v>27044000</v>
       </c>
       <c r="F61" s="3">
-        <v>25558300</v>
+        <v>27339100</v>
       </c>
       <c r="G61" s="3">
-        <v>26507200</v>
+        <v>28442600</v>
       </c>
       <c r="H61" s="3">
-        <v>24227000</v>
+        <v>29498600</v>
       </c>
       <c r="I61" s="3">
-        <v>24701400</v>
+        <v>26961000</v>
       </c>
       <c r="J61" s="3">
+        <v>27489000</v>
+      </c>
+      <c r="K61" s="3">
         <v>25059200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>27278200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>27790900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>28115400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>27947800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>29338200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>28326800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>30052900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>32828400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>35839200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>37259400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>38486000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>38586200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>37173100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>36605000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>33965600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>33739000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>32441500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>32027200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>34920400</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>35699100</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>37405600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>37431100</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>38250500</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>36521200</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>9117100</v>
+        <v>11015500</v>
       </c>
       <c r="E62" s="3">
-        <v>8944600</v>
+        <v>10146000</v>
       </c>
       <c r="F62" s="3">
-        <v>9226800</v>
+        <v>9954000</v>
       </c>
       <c r="G62" s="3">
-        <v>8659100</v>
+        <v>10268100</v>
       </c>
       <c r="H62" s="3">
-        <v>7986500</v>
+        <v>9636300</v>
       </c>
       <c r="I62" s="3">
-        <v>7708500</v>
+        <v>8887800</v>
       </c>
       <c r="J62" s="3">
+        <v>8578500</v>
+      </c>
+      <c r="K62" s="3">
         <v>7754600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>7707600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>7528900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>6977600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>7137200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>7774600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>7061100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>6336400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>6416800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>6975900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>7180400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>8188900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>7779100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>7906600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>8323600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>8124200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>8671300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>7800000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>7656300</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>7269000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>7278500</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>7072300</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>6802600</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>6766700</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>5977300</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5642,8 +5788,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5740,8 +5889,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5838,106 +5990,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>59701800</v>
+        <v>71412500</v>
       </c>
       <c r="E66" s="3">
-        <v>59896900</v>
+        <v>66439300</v>
       </c>
       <c r="F66" s="3">
-        <v>61139800</v>
+        <v>66656500</v>
       </c>
       <c r="G66" s="3">
-        <v>60783600</v>
+        <v>68039600</v>
       </c>
       <c r="H66" s="3">
-        <v>57504000</v>
+        <v>67643200</v>
       </c>
       <c r="I66" s="3">
-        <v>60281800</v>
+        <v>63993500</v>
       </c>
       <c r="J66" s="3">
+        <v>67084800</v>
+      </c>
+      <c r="K66" s="3">
         <v>63752000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>67506000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>61872100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>60471700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>59233700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>60973500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>56333100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>56483400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>59007300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>64958700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>70379700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>73667400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>72465300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>73055600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>73829900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>72239100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>70300400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>66567400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>66280800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>69332300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>68053100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>69759100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>68909600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>71093200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>64647500</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5972,8 +6130,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6070,8 +6229,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6168,8 +6330,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6266,8 +6431,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6364,106 +6532,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>35420100</v>
+        <v>40651700</v>
       </c>
       <c r="E72" s="3">
-        <v>33438100</v>
+        <v>39417300</v>
       </c>
       <c r="F72" s="3">
-        <v>32480700</v>
+        <v>37211600</v>
       </c>
       <c r="G72" s="3">
-        <v>31764700</v>
+        <v>36146300</v>
       </c>
       <c r="H72" s="3">
-        <v>30882500</v>
+        <v>35349400</v>
       </c>
       <c r="I72" s="3">
-        <v>30015600</v>
+        <v>34367600</v>
       </c>
       <c r="J72" s="3">
+        <v>33403000</v>
+      </c>
+      <c r="K72" s="3">
         <v>28566600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>29304600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>27662000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>26560900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>26825200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>26541400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>25153800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>24743600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>26163700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>28238800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>29621800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>30109600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>30037200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>28668100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>29585900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>28566200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>22079200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>25998200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>26247000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>25531600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>24759700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>23601500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>22619600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>21765100</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>21151000</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6560,8 +6734,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6658,8 +6835,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6756,106 +6936,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>48117000</v>
+        <v>56244800</v>
       </c>
       <c r="E76" s="3">
-        <v>45302400</v>
+        <v>53547100</v>
       </c>
       <c r="F76" s="3">
-        <v>45052600</v>
+        <v>50414900</v>
       </c>
       <c r="G76" s="3">
-        <v>43282900</v>
+        <v>50136900</v>
       </c>
       <c r="H76" s="3">
-        <v>40626200</v>
+        <v>48167500</v>
       </c>
       <c r="I76" s="3">
-        <v>39048300</v>
+        <v>45211000</v>
       </c>
       <c r="J76" s="3">
+        <v>43455000</v>
+      </c>
+      <c r="K76" s="3">
         <v>38568900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>38896000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>37218600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>34248700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>34165100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>35352000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>32404300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>30316100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>30647000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>33017300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>33633700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>39521800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>38703100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>38782900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>40969000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>39407500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>39762100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>36872200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>35931400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>37896800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>35850000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>34316500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>33104400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>32312900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>28320500</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6952,209 +7138,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>2151800</v>
+        <v>1960400</v>
       </c>
       <c r="E81" s="3">
-        <v>1723500</v>
+        <v>2394700</v>
       </c>
       <c r="F81" s="3">
-        <v>1297800</v>
+        <v>1918000</v>
       </c>
       <c r="G81" s="3">
-        <v>1613200</v>
+        <v>1444200</v>
       </c>
       <c r="H81" s="3">
-        <v>1849200</v>
+        <v>1795200</v>
       </c>
       <c r="I81" s="3">
-        <v>1924700</v>
+        <v>2057900</v>
       </c>
       <c r="J81" s="3">
+        <v>2141900</v>
+      </c>
+      <c r="K81" s="3">
         <v>1685000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1853500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1868900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1570700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1538400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1405800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>967900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>651700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>369800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>533600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>497200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>919400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1002800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1145300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>616500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1200700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>970400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1076400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>376500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1252300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1153100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1001200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>672400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>961100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>539600</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7189,106 +7384,110 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>540000</v>
+        <v>549200</v>
       </c>
       <c r="E83" s="3">
-        <v>456600</v>
+        <v>600900</v>
       </c>
       <c r="F83" s="3">
-        <v>434200</v>
+        <v>508100</v>
       </c>
       <c r="G83" s="3">
-        <v>442200</v>
+        <v>483200</v>
       </c>
       <c r="H83" s="3">
-        <v>423400</v>
+        <v>492100</v>
       </c>
       <c r="I83" s="3">
-        <v>442100</v>
+        <v>471200</v>
       </c>
       <c r="J83" s="3">
+        <v>492000</v>
+      </c>
+      <c r="K83" s="3">
         <v>453200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>444900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>473800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>536800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>526500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>543100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>520500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>492200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>545800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>537500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>623100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>600400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>541700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>554500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>496000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>442500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>411100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>396100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>413800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>448800</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>449300</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>429100</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>410100</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>432800</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>438700</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7385,8 +7584,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7483,8 +7685,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7581,8 +7786,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7679,8 +7887,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7777,106 +7988,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>1166400</v>
+        <v>2026500</v>
       </c>
       <c r="E89" s="3">
-        <v>1372400</v>
+        <v>1298000</v>
       </c>
       <c r="F89" s="3">
-        <v>648700</v>
+        <v>1527300</v>
       </c>
       <c r="G89" s="3">
-        <v>2327500</v>
+        <v>721900</v>
       </c>
       <c r="H89" s="3">
-        <v>2855900</v>
+        <v>2590200</v>
       </c>
       <c r="I89" s="3">
-        <v>1847200</v>
+        <v>3178300</v>
       </c>
       <c r="J89" s="3">
+        <v>2055600</v>
+      </c>
+      <c r="K89" s="3">
         <v>187800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1893500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2973900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>356300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>921800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1317900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1916000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>891400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1688800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1399300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1229000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>548400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1827000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1171400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>472800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1886300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>251200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1223700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1352500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>2182700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-372700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1833000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1624300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1312000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>298600</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7911,106 +8128,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-58680000</v>
+        <v>-96241000</v>
       </c>
       <c r="E91" s="3">
+        <v>-72428000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-80828000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-78404000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-63111000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-52536000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-66573000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-54756000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-54200000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-44019000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-50278000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-44762000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-341500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-275500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-358300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-357300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-700100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-669200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-792800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-579100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-566500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-717000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-868800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-680800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-616300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>707600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-337700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-384300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-196300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-458100</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-338400</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-537000</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8107,8 +8328,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8205,106 +8429,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-661700</v>
+        <v>-174400</v>
       </c>
       <c r="E94" s="3">
-        <v>-174200</v>
+        <v>-736400</v>
       </c>
       <c r="F94" s="3">
-        <v>-652400</v>
+        <v>-193900</v>
       </c>
       <c r="G94" s="3">
-        <v>-1239300</v>
+        <v>-726100</v>
       </c>
       <c r="H94" s="3">
-        <v>-331400</v>
+        <v>-1379200</v>
       </c>
       <c r="I94" s="3">
-        <v>35700</v>
+        <v>-368800</v>
       </c>
       <c r="J94" s="3">
+        <v>39800</v>
+      </c>
+      <c r="K94" s="3">
         <v>-130100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-752200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>61100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-286000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-405500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-680000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-98800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-618100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-901100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-925800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>186300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-718500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-156200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1012200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-2595500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1897000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1369400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-914400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-579400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-717100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-761300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-186100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-967700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-474900</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-603200</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8339,106 +8569,110 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>-903700</v>
       </c>
       <c r="E96" s="3">
-        <v>-816900</v>
+        <v>0</v>
       </c>
       <c r="F96" s="3">
-        <v>0</v>
+        <v>-909100</v>
       </c>
       <c r="G96" s="3">
-        <v>-729400</v>
+        <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>0</v>
+        <v>-811700</v>
       </c>
       <c r="I96" s="3">
-        <v>-650900</v>
+        <v>0</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>-724400</v>
       </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>-647400</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>-502400</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>-551900</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>-492400</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-582600</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-633600</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-636800</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-656300</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-631900</v>
       </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-478400</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-478400</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
       <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-397500</v>
       </c>
-      <c r="AH96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8535,8 +8769,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8633,8 +8870,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8731,298 +8971,310 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-2144300</v>
+        <v>-1115500</v>
       </c>
       <c r="E100" s="3">
-        <v>-1570800</v>
+        <v>-2386300</v>
       </c>
       <c r="F100" s="3">
-        <v>-584800</v>
+        <v>-1748100</v>
       </c>
       <c r="G100" s="3">
-        <v>-2163400</v>
+        <v>-650800</v>
       </c>
       <c r="H100" s="3">
-        <v>-1639900</v>
+        <v>-2407600</v>
       </c>
       <c r="I100" s="3">
-        <v>-444700</v>
+        <v>-1824900</v>
       </c>
       <c r="J100" s="3">
+        <v>-494900</v>
+      </c>
+      <c r="K100" s="3">
         <v>-1136700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-874800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1439500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-322200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1286200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1266100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1451100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1099300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-343300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-752700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-130100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1862200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-68800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>202500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>2126800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-385900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>482800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-954700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1145700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1020400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-2791000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-939700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-1316100</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-841900</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>217200</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>214400</v>
+        <v>238500</v>
       </c>
       <c r="E101" s="3">
-        <v>-110200</v>
+        <v>238600</v>
       </c>
       <c r="F101" s="3">
-        <v>52500</v>
+        <v>-122700</v>
       </c>
       <c r="G101" s="3">
-        <v>381000</v>
+        <v>58400</v>
       </c>
       <c r="H101" s="3">
-        <v>36000</v>
+        <v>424000</v>
       </c>
       <c r="I101" s="3">
-        <v>-294900</v>
+        <v>40000</v>
       </c>
       <c r="J101" s="3">
+        <v>-328200</v>
+      </c>
+      <c r="K101" s="3">
         <v>105900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>348700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>308400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>120700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-61400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-15900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>233800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-59100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>6600</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>131300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-293800</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>148200</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-82300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-72700</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>23700</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-142100</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>124000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>45000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-335900</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>3300</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>100100</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>10700</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-65200</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>603600</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-59700</v>
       </c>
     </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-1425300</v>
+        <v>975200</v>
       </c>
       <c r="E102" s="3">
-        <v>-482900</v>
+        <v>-1586200</v>
       </c>
       <c r="F102" s="3">
-        <v>-536000</v>
+        <v>-537400</v>
       </c>
       <c r="G102" s="3">
-        <v>-694300</v>
+        <v>-596500</v>
       </c>
       <c r="H102" s="3">
-        <v>920700</v>
+        <v>-772600</v>
       </c>
       <c r="I102" s="3">
-        <v>1143300</v>
+        <v>1024600</v>
       </c>
       <c r="J102" s="3">
+        <v>1272400</v>
+      </c>
+      <c r="K102" s="3">
         <v>-973100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>615100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1903900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-131200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-831200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-644100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>600000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-885100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>451000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-148000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>991400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-1884100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1519700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>289000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>27700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-404700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-643100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-600500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-708500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>448600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-3824900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>717900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-724700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>598900</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-147200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MITSY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MITSY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="92">
   <si>
     <t>MITSY</t>
   </si>
@@ -656,438 +656,450 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="15" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="34" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="13" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="35" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
-        <v>27263400</v>
-      </c>
-      <c r="E8" s="3">
-        <v>23617900</v>
-      </c>
-      <c r="F8" s="3">
-        <v>25709300</v>
-      </c>
-      <c r="G8" s="3">
-        <v>22921000</v>
-      </c>
-      <c r="H8" s="3">
-        <v>22358800</v>
-      </c>
-      <c r="I8" s="3">
-        <v>23216200</v>
-      </c>
-      <c r="J8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K8" s="3">
         <v>25650200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>23627000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>25076400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>21036400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>21800100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>19886400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>19536500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>23476100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>14920200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>14487100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>15741000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>28986100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>16240900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>16340900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>14959400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>18687200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>16988500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>15394900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>14145800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>11201800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>11381200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>10959900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>10682200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>10539300</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>10144100</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>8977900</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3">
-        <v>24900700</v>
-      </c>
-      <c r="E9" s="3">
-        <v>21237300</v>
-      </c>
-      <c r="F9" s="3">
-        <v>23039600</v>
-      </c>
-      <c r="G9" s="3">
-        <v>20736600</v>
-      </c>
-      <c r="H9" s="3">
-        <v>20223600</v>
-      </c>
-      <c r="I9" s="3">
-        <v>20532500</v>
-      </c>
-      <c r="J9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K9" s="3">
         <v>22907200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>21595000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>22963900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>18701800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>19997700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>18017600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>17565000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>21751400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>13451500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>13099400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>14122800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>27233000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>14307400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>14328700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>13042800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>16713400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>15012100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>13487900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>12160100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>9567400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>9519200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>9110700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>8879700</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>8666700</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>8528400</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>7541800</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="3">
-        <v>2362700</v>
-      </c>
-      <c r="E10" s="3">
-        <v>2380600</v>
-      </c>
-      <c r="F10" s="3">
-        <v>2669700</v>
-      </c>
-      <c r="G10" s="3">
-        <v>2184400</v>
-      </c>
-      <c r="H10" s="3">
-        <v>2135200</v>
-      </c>
-      <c r="I10" s="3">
-        <v>2683700</v>
-      </c>
-      <c r="J10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K10" s="3">
         <v>2743000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2031900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2112500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2334500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1802400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1868700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1971500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1724700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1468700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1387600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1618200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1753200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1933500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2012200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1916600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1973800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1976400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1906900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1985700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1634400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1861900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1849100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1802500</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1872600</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1615700</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1436100</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1123,8 +1135,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1224,8 +1237,11 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1325,132 +1341,138 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>24600</v>
-      </c>
-      <c r="E14" s="3">
-        <v>385300</v>
-      </c>
-      <c r="F14" s="3">
-        <v>62300</v>
-      </c>
-      <c r="G14" s="3">
-        <v>10400</v>
-      </c>
-      <c r="H14" s="3">
-        <v>17900</v>
-      </c>
-      <c r="I14" s="3">
-        <v>98600</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="3">
         <v>37400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>67300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>32100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>10800</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>163500</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>90700</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>262100</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>38700</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>2600</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>874000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>82100</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>8300</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>15500</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>225400</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>20700</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>3800</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>8900</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>59600</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>91800</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>67000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>11600</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>48200</v>
       </c>
-      <c r="AH14" s="3">
-        <v>0</v>
-      </c>
       <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3">
-        <v>0</v>
-      </c>
-      <c r="E15" s="3">
-        <v>0</v>
-      </c>
-      <c r="F15" s="3">
-        <v>0</v>
-      </c>
-      <c r="G15" s="3">
-        <v>0</v>
-      </c>
-      <c r="H15" s="3">
-        <v>0</v>
-      </c>
-      <c r="I15" s="3">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3">
-        <v>0</v>
+      <c r="D15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1527,8 +1549,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1561,210 +1586,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
-        <v>25758200</v>
-      </c>
-      <c r="E17" s="3">
-        <v>22361600</v>
-      </c>
-      <c r="F17" s="3">
-        <v>24390900</v>
-      </c>
-      <c r="G17" s="3">
-        <v>21661700</v>
-      </c>
-      <c r="H17" s="3">
-        <v>21195100</v>
-      </c>
-      <c r="I17" s="3">
-        <v>22030000</v>
-      </c>
-      <c r="J17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K17" s="3">
         <v>23948200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>22600500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>23836300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>19830800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>20835700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>19119900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>18538500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>22976200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>14945300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>14328800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>15201000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>29074600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>15671900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>15581200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>14210600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>18422900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>16308000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>14800500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>13271100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>11108400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>10721200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>10139700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>9954000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>9794000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>9291500</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>8516000</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
-        <v>1505200</v>
-      </c>
-      <c r="E18" s="3">
-        <v>1256300</v>
-      </c>
-      <c r="F18" s="3">
-        <v>1318400</v>
-      </c>
-      <c r="G18" s="3">
-        <v>1259300</v>
-      </c>
-      <c r="H18" s="3">
-        <v>1163800</v>
-      </c>
-      <c r="I18" s="3">
-        <v>1186200</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K18" s="3">
         <v>1701900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1026400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1240000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1205600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>964400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>766500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>998000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>500000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-25200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>158300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>540000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-88400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>569000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>759700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>748700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>264200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>680500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>594400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>874700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>93400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>660000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>820200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>728200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>745300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>852600</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>461900</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1800,513 +1832,529 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>1278300</v>
-      </c>
-      <c r="E20" s="3">
-        <v>1690500</v>
-      </c>
-      <c r="F20" s="3">
-        <v>1386800</v>
-      </c>
-      <c r="G20" s="3">
-        <v>1041000</v>
-      </c>
-      <c r="H20" s="3">
-        <v>1324100</v>
-      </c>
-      <c r="I20" s="3">
-        <v>1455900</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K20" s="3">
         <v>1211100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1290200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1215700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1076700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1107600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1367000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>990700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>836800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>762100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>586800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>461600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>822000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1024200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>799300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>1048100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>949200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>1042200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>982200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>815900</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>682600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>963900</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>765600</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>808400</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>451900</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>662000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>545900</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
-        <v>3332600</v>
-      </c>
-      <c r="E21" s="3">
-        <v>3547700</v>
-      </c>
-      <c r="F21" s="3">
-        <v>3213300</v>
-      </c>
-      <c r="G21" s="3">
-        <v>2783600</v>
-      </c>
-      <c r="H21" s="3">
-        <v>2980000</v>
-      </c>
-      <c r="I21" s="3">
-        <v>3113300</v>
-      </c>
-      <c r="J21" s="3">
+      <c r="D21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K21" s="3">
         <v>3405000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2769800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2900600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2756100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2608800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2659900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2531800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1857200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1229100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1290900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1539200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1356700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>2193700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2100800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>2351400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1709400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>2165200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1987800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>2086700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1189800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>2072700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>2035100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1965600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1607200</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1947400</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1446600</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>314900</v>
-      </c>
-      <c r="E22" s="3">
-        <v>327900</v>
-      </c>
-      <c r="F22" s="3">
-        <v>293600</v>
-      </c>
-      <c r="G22" s="3">
-        <v>297700</v>
-      </c>
-      <c r="H22" s="3">
-        <v>274000</v>
-      </c>
-      <c r="I22" s="3">
-        <v>295700</v>
-      </c>
-      <c r="J22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K22" s="3">
         <v>236200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>148400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>110500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>76000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>69100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>82400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>105800</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>77600</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>92500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>100800</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>131600</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>178400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>205000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>212500</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>217600</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>194400</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>191600</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>191700</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>172300</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>149100</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>150300</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>156500</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>145100</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>140900</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>133700</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>118100</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
-        <v>2468600</v>
-      </c>
-      <c r="E23" s="3">
-        <v>2618900</v>
-      </c>
-      <c r="F23" s="3">
-        <v>2411600</v>
-      </c>
-      <c r="G23" s="3">
-        <v>2002600</v>
-      </c>
-      <c r="H23" s="3">
-        <v>2213900</v>
-      </c>
-      <c r="I23" s="3">
-        <v>2346400</v>
-      </c>
-      <c r="J23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K23" s="3">
         <v>2676800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2168200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2345200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2206300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2002900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2051000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1883000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1259100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>644500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>644300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>870000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>555100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1388200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1346500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1579200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1019000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1531100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1384900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1518300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>626900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1473600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1429300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1391500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1056300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1380900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>889700</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>463900</v>
-      </c>
-      <c r="E24" s="3">
-        <v>224300</v>
-      </c>
-      <c r="F24" s="3">
-        <v>466700</v>
-      </c>
-      <c r="G24" s="3">
-        <v>507200</v>
-      </c>
-      <c r="H24" s="3">
-        <v>377400</v>
-      </c>
-      <c r="I24" s="3">
-        <v>271200</v>
-      </c>
-      <c r="J24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K24" s="3">
         <v>502000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>460500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>401700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>299100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>402700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>482800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>413000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>260700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-32100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>250100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>301300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>88400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>409100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>280700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>343700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>397900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>289000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>367300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>372800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>201200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>158300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>234300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>338000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>320800</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>367600</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>316000</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2406,210 +2454,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
-        <v>2004700</v>
-      </c>
-      <c r="E26" s="3">
-        <v>2394600</v>
-      </c>
-      <c r="F26" s="3">
-        <v>1944900</v>
-      </c>
-      <c r="G26" s="3">
-        <v>1495400</v>
-      </c>
-      <c r="H26" s="3">
-        <v>1836500</v>
-      </c>
-      <c r="I26" s="3">
-        <v>2075200</v>
-      </c>
-      <c r="J26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K26" s="3">
         <v>2174800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1707800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1943500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1907200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1600200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1568200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1470000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>998400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>676500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>394200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>568600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>466700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>979200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1065800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1235500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>621100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1242100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1017600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1145500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>425700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1315300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1195000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1053500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>735500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1013300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>573700</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
-        <v>1960400</v>
-      </c>
-      <c r="E27" s="3">
-        <v>2394700</v>
-      </c>
-      <c r="F27" s="3">
-        <v>1918000</v>
-      </c>
-      <c r="G27" s="3">
-        <v>1444200</v>
-      </c>
-      <c r="H27" s="3">
-        <v>1795200</v>
-      </c>
-      <c r="I27" s="3">
-        <v>2057900</v>
-      </c>
-      <c r="J27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K27" s="3">
         <v>2141900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1685000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1853500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1868900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1570700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1538400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1405800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>967900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>651700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>369800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>533600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>497200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>919400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1002800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1145300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>616500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1200700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>970400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1076400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>376500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1252300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1153100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1001200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>672400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>961100</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>539600</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2709,31 +2766,34 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3">
-        <v>0</v>
-      </c>
-      <c r="E29" s="3">
-        <v>0</v>
-      </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
-      <c r="H29" s="3">
-        <v>0</v>
-      </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3">
-        <v>0</v>
+      <c r="D29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K29" s="3">
         <v>0</v>
@@ -2810,8 +2870,11 @@
       <c r="AI29" s="3">
         <v>0</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2911,8 +2974,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3012,210 +3078,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>-1278300</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-1690500</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-1386800</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-1041000</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-1324100</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-1455900</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K32" s="3">
         <v>-1211100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1290200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1215700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1076700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1107600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1367000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-990700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-836800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-762100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-586800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-461600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-822000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1024200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-799300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-1048100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-949200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-1042200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-982200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-815900</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-682600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-963900</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-765600</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-808400</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-451900</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-662000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-545900</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
-        <v>1960400</v>
-      </c>
-      <c r="E33" s="3">
-        <v>2394700</v>
-      </c>
-      <c r="F33" s="3">
-        <v>1918000</v>
-      </c>
-      <c r="G33" s="3">
-        <v>1444200</v>
-      </c>
-      <c r="H33" s="3">
-        <v>1795200</v>
-      </c>
-      <c r="I33" s="3">
-        <v>2057900</v>
-      </c>
-      <c r="J33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K33" s="3">
         <v>2141900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1685000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1853500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1868900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1570700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1538400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1405800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>967900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>651700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>369800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>533600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>497200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>919400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1002800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1145300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>616500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1200700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>970400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1076400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>376500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1252300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1153100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1001200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>672400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>961100</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>539600</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3315,215 +3390,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
-        <v>1960400</v>
-      </c>
-      <c r="E35" s="3">
-        <v>2394700</v>
-      </c>
-      <c r="F35" s="3">
-        <v>1918000</v>
-      </c>
-      <c r="G35" s="3">
-        <v>1444200</v>
-      </c>
-      <c r="H35" s="3">
-        <v>1795200</v>
-      </c>
-      <c r="I35" s="3">
-        <v>2057900</v>
-      </c>
-      <c r="J35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K35" s="3">
         <v>2141900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1685000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1853500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1868900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1570700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1538400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1405800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>967900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>651700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>369800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>533600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>497200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>919400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1002800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1145300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>616500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1200700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>970400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1076400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>376500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1252300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1153100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1001200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>672400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>961100</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>539600</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3559,8 +3643,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3596,917 +3681,945 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>7352400</v>
+        <v>5983900</v>
       </c>
       <c r="E41" s="3">
-        <v>6377200</v>
+        <v>6437400</v>
       </c>
       <c r="F41" s="3">
-        <v>7963400</v>
+        <v>5938300</v>
       </c>
       <c r="G41" s="3">
-        <v>8500800</v>
+        <v>7956800</v>
       </c>
       <c r="H41" s="3">
-        <v>9097300</v>
+        <v>8016100</v>
       </c>
       <c r="I41" s="3">
-        <v>9869900</v>
+        <v>8862000</v>
       </c>
       <c r="J41" s="3">
+        <v>10457300</v>
+      </c>
+      <c r="K41" s="3">
         <v>8845300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6805000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>8217000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>7489000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5778600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>6202300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>7170000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>7537700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>7172600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>8563400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>8883000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>9327400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>8619900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>10596300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>9047000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>9188200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>8998400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>9253700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>9683800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>10227700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>10936200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>10487600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>14312400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>13338900</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>14063500</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>13464600</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>9228400</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>8094900</v>
+        <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>6551300</v>
+        <v>29900</v>
       </c>
       <c r="G42" s="3">
-        <v>6740000</v>
+        <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>6489800</v>
+        <v>0</v>
       </c>
       <c r="I42" s="3">
-        <v>5488200</v>
+        <v>0</v>
       </c>
       <c r="J42" s="3">
+        <v>50300</v>
+      </c>
+      <c r="K42" s="3">
         <v>7188900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>8123200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>7698600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>6625800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>6088600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>5687100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>4151400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>3048600</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>3152600</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>3119600</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>3626700</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>4959100</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>3002000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>2707200</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>2753000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>2445800</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>3255400</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>2869100</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>2702600</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>2205000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>3030500</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>2627800</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>2445500</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>2374300</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>3915400</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>3786600</v>
       </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>17515300</v>
+        <v>15610800</v>
       </c>
       <c r="E43" s="3">
-        <v>16089700</v>
+        <v>15335400</v>
       </c>
       <c r="F43" s="3">
-        <v>16348000</v>
+        <v>17120500</v>
       </c>
       <c r="G43" s="3">
-        <v>15754600</v>
+        <v>16334400</v>
       </c>
       <c r="H43" s="3">
-        <v>15001900</v>
+        <v>14856300</v>
       </c>
       <c r="I43" s="3">
-        <v>15557400</v>
+        <v>14613900</v>
       </c>
       <c r="J43" s="3">
+        <v>17991700</v>
+      </c>
+      <c r="K43" s="3">
         <v>16929900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>15444400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>16786300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>15292800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>15852800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>13571000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>13780400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>12847000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>12632200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>11204300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>12454600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>14294200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>16566500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>14911000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>15916900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>17338600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>17779600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>16564800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>15649400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>15964800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>17290200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>16461900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>14971500</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>15428500</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>15480700</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>13205700</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>7034200</v>
+        <v>6684200</v>
       </c>
       <c r="E44" s="3">
-        <v>6856600</v>
+        <v>6158700</v>
       </c>
       <c r="F44" s="3">
-        <v>6551800</v>
+        <v>6384700</v>
       </c>
       <c r="G44" s="3">
-        <v>6501500</v>
+        <v>6546400</v>
       </c>
       <c r="H44" s="3">
-        <v>6824400</v>
+        <v>6130800</v>
       </c>
       <c r="I44" s="3">
-        <v>6677900</v>
+        <v>6647900</v>
       </c>
       <c r="J44" s="3">
+        <v>7075300</v>
+      </c>
+      <c r="K44" s="3">
         <v>7257600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>6519300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>6577600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>6305800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>6092800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>5348100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>5282900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>4361400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>4413800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>4318400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>4554700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>4879500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>6283100</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>5890100</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>5901000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>5839800</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>5950700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>5828600</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>5150500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>4978300</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>5689100</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>5718500</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>5394500</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>5229200</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>5336700</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>4779400</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>3745000</v>
+        <v>9926400</v>
       </c>
       <c r="E45" s="3">
-        <v>3535500</v>
+        <v>11358800</v>
       </c>
       <c r="F45" s="3">
-        <v>3812900</v>
+        <v>8661800</v>
       </c>
       <c r="G45" s="3">
-        <v>3586800</v>
+        <v>10355500</v>
       </c>
       <c r="H45" s="3">
-        <v>4275400</v>
+        <v>9737900</v>
       </c>
       <c r="I45" s="3">
-        <v>2698000</v>
+        <v>10486700</v>
       </c>
       <c r="J45" s="3">
+        <v>7114500</v>
+      </c>
+      <c r="K45" s="3">
         <v>3063800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2394200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2765400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2245300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2327600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2275500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2305600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2036200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2036500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2138300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2623100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2875800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2941600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2909800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>3240200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>3592300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>3707100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>3593900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>3510500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>4828700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>4005100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>3659200</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>3525900</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>3320100</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>3359700</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>2996000</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>44875300</v>
+        <v>38205300</v>
       </c>
       <c r="E46" s="3">
-        <v>40953900</v>
+        <v>39290200</v>
       </c>
       <c r="F46" s="3">
-        <v>41227400</v>
+        <v>38135300</v>
       </c>
       <c r="G46" s="3">
-        <v>41083700</v>
+        <v>41193200</v>
       </c>
       <c r="H46" s="3">
-        <v>41688800</v>
+        <v>38741100</v>
       </c>
       <c r="I46" s="3">
-        <v>40291300</v>
+        <v>40610400</v>
       </c>
       <c r="J46" s="3">
+        <v>42689100</v>
+      </c>
+      <c r="K46" s="3">
         <v>43285600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>39286100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>42044900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>37958800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>36140400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>33084000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>32690400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>29831000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>29407700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>29344000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>32142100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>36336100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>37413100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>37014400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>36858100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>38404700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>39691200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>38110200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>36696800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>38204500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>40951100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>38955000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>40649900</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>39691000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>42156100</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>38232400</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>56558400</v>
+        <v>48591000</v>
       </c>
       <c r="E47" s="3">
-        <v>54579300</v>
+        <v>46012800</v>
       </c>
       <c r="F47" s="3">
-        <v>52325600</v>
+        <v>47546900</v>
       </c>
       <c r="G47" s="3">
-        <v>52738800</v>
+        <v>49006300</v>
       </c>
       <c r="H47" s="3">
-        <v>49602000</v>
+        <v>46203000</v>
       </c>
       <c r="I47" s="3">
-        <v>46801800</v>
+        <v>44651900</v>
       </c>
       <c r="J47" s="3">
+        <v>45632700</v>
+      </c>
+      <c r="K47" s="3">
         <v>45576500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>42559700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>43167900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>41318100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>38904100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>40110200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>42558000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>38622100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>37234400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>38999900</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>42508800</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>43819300</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>50414800</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>49513500</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>50532700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>53209900</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>48784500</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>49446400</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>45792300</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>44126500</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>45878300</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>44160100</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>42595400</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>41700800</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>39980100</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>35285000</v>
       </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>20295400</v>
+        <v>16766200</v>
       </c>
       <c r="E48" s="3">
-        <v>19054600</v>
+        <v>15999900</v>
       </c>
       <c r="F48" s="3">
-        <v>18610700</v>
+        <v>15877100</v>
       </c>
       <c r="G48" s="3">
-        <v>19277100</v>
+        <v>16660800</v>
       </c>
       <c r="H48" s="3">
-        <v>19607100</v>
+        <v>16273300</v>
       </c>
       <c r="I48" s="3">
-        <v>18340000</v>
+        <v>17114800</v>
       </c>
       <c r="J48" s="3">
+        <v>17306400</v>
+      </c>
+      <c r="K48" s="3">
         <v>18096300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>17008700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>17712200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>16662900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>16691900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>17196100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>17942800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>17369900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>17576200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>18818600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>20573600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>20908000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>22359200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>21602500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>21397900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>20646900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>20363100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>19807500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>18394900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>17346400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>17820100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>18003700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>17903900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>17769100</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>18403400</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>16888800</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>3604500</v>
+        <v>3268000</v>
       </c>
       <c r="E49" s="3">
-        <v>3253500</v>
+        <v>3155900</v>
       </c>
       <c r="F49" s="3">
-        <v>3156700</v>
+        <v>3029600</v>
       </c>
       <c r="G49" s="3">
-        <v>3155800</v>
+        <v>3154100</v>
       </c>
       <c r="H49" s="3">
-        <v>3074900</v>
+        <v>2975900</v>
       </c>
       <c r="I49" s="3">
-        <v>1968900</v>
+        <v>2995300</v>
       </c>
       <c r="J49" s="3">
+        <v>2086100</v>
+      </c>
+      <c r="K49" s="3">
         <v>2005000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1888200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1898700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1680200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1568100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1529500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1604900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1336900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1365200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1507700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1644000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1720500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>2151300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>2186600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>2230100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1673000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1743600</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1607100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1552500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1565800</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1572800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1615000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1568500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1496200</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>1434400</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>1274500</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4606,8 +4719,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4707,109 +4823,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>2323900</v>
+        <v>4411800</v>
       </c>
       <c r="E52" s="3">
-        <v>2145200</v>
+        <v>4789800</v>
       </c>
       <c r="F52" s="3">
-        <v>1751100</v>
+        <v>4761800</v>
       </c>
       <c r="G52" s="3">
-        <v>1921000</v>
+        <v>4201200</v>
       </c>
       <c r="H52" s="3">
-        <v>1838000</v>
+        <v>4469200</v>
       </c>
       <c r="I52" s="3">
-        <v>1802400</v>
+        <v>4569800</v>
       </c>
       <c r="J52" s="3">
+        <v>5022900</v>
+      </c>
+      <c r="K52" s="3">
         <v>1576500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1578100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1578300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1470700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1415900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1479100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1529400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1577500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1215900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>984000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1107500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1229500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>850800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>851500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>819700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>864500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1064200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1091400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1002900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>969100</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1006800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1169300</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1357900</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1356900</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1432200</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1287300</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4909,109 +5031,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>127657400</v>
+        <v>113744000</v>
       </c>
       <c r="E54" s="3">
-        <v>119986500</v>
+        <v>111769500</v>
       </c>
       <c r="F54" s="3">
-        <v>117071400</v>
+        <v>111728600</v>
       </c>
       <c r="G54" s="3">
-        <v>118176500</v>
+        <v>116974300</v>
       </c>
       <c r="H54" s="3">
-        <v>115810800</v>
+        <v>111437900</v>
       </c>
       <c r="I54" s="3">
-        <v>109204500</v>
+        <v>112815100</v>
       </c>
       <c r="J54" s="3">
+        <v>115703400</v>
+      </c>
+      <c r="K54" s="3">
         <v>110539800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>102320900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>106402000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>99090600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>94720400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>93398900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>96325500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>88737300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>86799500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>89654300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>97976000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>104013400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>113189100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>111168500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>111838500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>114798900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>111646700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>110062600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>103439500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>102212200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>107229100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>103903100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>104075500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>102014000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>103406200</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>92968100</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5047,8 +5175,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5084,614 +5213,633 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>12892700</v>
+        <v>11222400</v>
       </c>
       <c r="E57" s="3">
-        <v>11693900</v>
+        <v>11288100</v>
       </c>
       <c r="F57" s="3">
-        <v>12331800</v>
+        <v>9498000</v>
       </c>
       <c r="G57" s="3">
-        <v>11472700</v>
+        <v>12321600</v>
       </c>
       <c r="H57" s="3">
-        <v>11375000</v>
+        <v>10818500</v>
       </c>
       <c r="I57" s="3">
-        <v>10723800</v>
+        <v>11080800</v>
       </c>
       <c r="J57" s="3">
+        <v>10059000</v>
+      </c>
+      <c r="K57" s="3">
         <v>12531200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>10965800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>12544700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>11547900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>11758900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>10074300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>10382200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>9311600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>8737600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>8288800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>8744100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>10012600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>11770300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>10845800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>11551100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>12707100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>13217100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>12028200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>11694800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>11429100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>12147200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>11328200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>10649200</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>10676900</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>10787700</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>8887300</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>8453500</v>
+        <v>5812800</v>
       </c>
       <c r="E58" s="3">
-        <v>6866000</v>
+        <v>7401400</v>
       </c>
       <c r="F58" s="3">
-        <v>7406000</v>
+        <v>6393500</v>
       </c>
       <c r="G58" s="3">
-        <v>7625600</v>
+        <v>7399900</v>
       </c>
       <c r="H58" s="3">
-        <v>6653100</v>
+        <v>7190800</v>
       </c>
       <c r="I58" s="3">
-        <v>8826900</v>
+        <v>6481000</v>
       </c>
       <c r="J58" s="3">
+        <v>9352200</v>
+      </c>
+      <c r="K58" s="3">
         <v>8859900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>8276900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>7751000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>4595500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>5029900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>5764700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>5962600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>5327600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>5047300</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>5228200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>6306000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>6143800</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>6544700</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>7261900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>8192800</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>7845800</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>7553600</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>6959600</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>6294800</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>6184300</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>5829800</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>5542100</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>6488500</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>6146100</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>7075800</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>6388700</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>10238100</v>
+        <v>8096000</v>
       </c>
       <c r="E59" s="3">
-        <v>9070000</v>
+        <v>8963900</v>
       </c>
       <c r="F59" s="3">
-        <v>8034800</v>
+        <v>8445800</v>
       </c>
       <c r="G59" s="3">
-        <v>8670000</v>
+        <v>8028100</v>
       </c>
       <c r="H59" s="3">
-        <v>8952300</v>
+        <v>8175600</v>
       </c>
       <c r="I59" s="3">
-        <v>7192400</v>
+        <v>8720800</v>
       </c>
       <c r="J59" s="3">
+        <v>7620400</v>
+      </c>
+      <c r="K59" s="3">
         <v>8159800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>10312300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>10810700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>9145900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>6802800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>6487000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>5634600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4516000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>4513900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>4330200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>4931400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>7640400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>6186700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>5577100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>5804100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>5781200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>6905100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>6461800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>6059700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>6783400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>6711400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>5826600</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>5765000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>5564600</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>5821700</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>4722300</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>31584300</v>
+        <v>25131200</v>
       </c>
       <c r="E60" s="3">
-        <v>27629900</v>
+        <v>27653400</v>
       </c>
       <c r="F60" s="3">
-        <v>27772600</v>
+        <v>25728300</v>
       </c>
       <c r="G60" s="3">
-        <v>27768300</v>
+        <v>27749600</v>
       </c>
       <c r="H60" s="3">
-        <v>26980400</v>
+        <v>26184900</v>
       </c>
       <c r="I60" s="3">
-        <v>26743100</v>
+        <v>26282500</v>
       </c>
       <c r="J60" s="3">
+        <v>28334600</v>
+      </c>
+      <c r="K60" s="3">
         <v>29550900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>29555000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>31106500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>25289300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>23591600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>22326000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>21979400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>19155200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>18298800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>17847200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>19981500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>23796800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>24501800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>23684800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>25548000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>26334000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>27675800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>25449500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>24049300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>24396900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>24688500</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>22697000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>22902800</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>22387600</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>23685200</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>19998200</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>27144000</v>
+        <v>25551400</v>
       </c>
       <c r="E61" s="3">
-        <v>27044000</v>
+        <v>23765800</v>
       </c>
       <c r="F61" s="3">
-        <v>27339100</v>
+        <v>25182700</v>
       </c>
       <c r="G61" s="3">
-        <v>28442600</v>
+        <v>27316400</v>
       </c>
       <c r="H61" s="3">
-        <v>29498600</v>
+        <v>26820700</v>
       </c>
       <c r="I61" s="3">
-        <v>26961000</v>
+        <v>28735500</v>
       </c>
       <c r="J61" s="3">
+        <v>28565500</v>
+      </c>
+      <c r="K61" s="3">
         <v>27489000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>25059200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>27278200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>27790900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>28115400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>27947800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>29338200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>28326800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>30052900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>32828400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>35839200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>37259400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>38486000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>38586200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>37173100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>36605000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>33965600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>33739000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>32441500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>32027200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>34920400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>35699100</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>37405600</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>37431100</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>38250500</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>36521200</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>11015500</v>
+        <v>4035000</v>
       </c>
       <c r="E62" s="3">
-        <v>10146000</v>
+        <v>4657400</v>
       </c>
       <c r="F62" s="3">
-        <v>9954000</v>
+        <v>4226200</v>
       </c>
       <c r="G62" s="3">
-        <v>10268100</v>
+        <v>4199900</v>
       </c>
       <c r="H62" s="3">
-        <v>9636300</v>
+        <v>4520300</v>
       </c>
       <c r="I62" s="3">
-        <v>8887800</v>
+        <v>4351100</v>
       </c>
       <c r="J62" s="3">
+        <v>4261800</v>
+      </c>
+      <c r="K62" s="3">
         <v>8578500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>7754600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>7707600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>7528900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>6977600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>7137200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>7774600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>7061100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>6336400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>6416800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>6975900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>7180400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>8188900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>7779100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>7906600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>8323600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>8124200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>8671300</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>7800000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>7656300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>7269000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>7278500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>7072300</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>6802600</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>6766700</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>5977300</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5791,8 +5939,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5892,8 +6043,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5993,109 +6147,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>71412500</v>
+        <v>60132700</v>
       </c>
       <c r="E66" s="3">
-        <v>66439300</v>
+        <v>61063700</v>
       </c>
       <c r="F66" s="3">
-        <v>66656500</v>
+        <v>60358700</v>
       </c>
       <c r="G66" s="3">
-        <v>68039600</v>
+        <v>65011800</v>
       </c>
       <c r="H66" s="3">
-        <v>67643200</v>
+        <v>62688200</v>
       </c>
       <c r="I66" s="3">
-        <v>63993500</v>
+        <v>64405100</v>
       </c>
       <c r="J66" s="3">
+        <v>66316900</v>
+      </c>
+      <c r="K66" s="3">
         <v>67084800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>63752000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>67506000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>61872100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>60471700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>59233700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>60973500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>56333100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>56483400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>59007300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>64958700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>70379700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>73667400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>72465300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>73055600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>73829900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>72239100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>70300400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>66567400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>66280800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>69332300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>68053100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>69759100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>68909600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>71093200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>64647500</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6131,8 +6291,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6232,8 +6393,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6333,8 +6497,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6434,8 +6601,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6535,109 +6705,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>40651700</v>
+        <v>40847100</v>
       </c>
       <c r="E72" s="3">
-        <v>39417300</v>
+        <v>35592300</v>
       </c>
       <c r="F72" s="3">
-        <v>37211600</v>
+        <v>36704500</v>
       </c>
       <c r="G72" s="3">
-        <v>36146300</v>
+        <v>37180800</v>
       </c>
       <c r="H72" s="3">
-        <v>35349400</v>
+        <v>34085100</v>
       </c>
       <c r="I72" s="3">
-        <v>34367600</v>
+        <v>34435100</v>
       </c>
       <c r="J72" s="3">
+        <v>36412900</v>
+      </c>
+      <c r="K72" s="3">
         <v>33403000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>28566600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>29304600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>27662000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>26560900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>26825200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>26541400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>25153800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>24743600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>26163700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>28238800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>29621800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>30109600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>30037200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>28668100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>29585900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>28566200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>22079200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>25998200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>26247000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>25531600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>24759700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>23601500</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>22619600</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>21765100</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>21151000</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6737,8 +6913,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6838,8 +7017,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6939,109 +7121,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>56244800</v>
+        <v>52065200</v>
       </c>
       <c r="E76" s="3">
-        <v>53547100</v>
+        <v>49244700</v>
       </c>
       <c r="F76" s="3">
-        <v>50414900</v>
+        <v>49861800</v>
       </c>
       <c r="G76" s="3">
-        <v>50136900</v>
+        <v>50373100</v>
       </c>
       <c r="H76" s="3">
-        <v>48167500</v>
+        <v>47278000</v>
       </c>
       <c r="I76" s="3">
-        <v>45211000</v>
+        <v>46921600</v>
       </c>
       <c r="J76" s="3">
+        <v>47901600</v>
+      </c>
+      <c r="K76" s="3">
         <v>43455000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>38568900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>38896000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>37218600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>34248700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>34165100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>35352000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>32404300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>30316100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>30647000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>33017300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>33633700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>39521800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>38703100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>38782900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>40969000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>39407500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>39762100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>36872200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>35931400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>37896800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>35850000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>34316500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>33104400</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>32312900</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>28320500</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7141,215 +7329,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
-        <v>1960400</v>
-      </c>
-      <c r="E81" s="3">
-        <v>2394700</v>
-      </c>
-      <c r="F81" s="3">
-        <v>1918000</v>
-      </c>
-      <c r="G81" s="3">
-        <v>1444200</v>
-      </c>
-      <c r="H81" s="3">
-        <v>1795200</v>
-      </c>
-      <c r="I81" s="3">
-        <v>2057900</v>
-      </c>
-      <c r="J81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K81" s="3">
         <v>2141900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1685000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1853500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1868900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1570700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1538400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1405800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>967900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>651700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>369800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>533600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>497200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>919400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1002800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1145300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>616500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1200700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>970400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1076400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>376500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1252300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1153100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1001200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>672400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>961100</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>539600</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7385,109 +7582,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>549200</v>
+        <v>455700</v>
       </c>
       <c r="E83" s="3">
-        <v>600900</v>
+        <v>479400</v>
       </c>
       <c r="F83" s="3">
-        <v>508100</v>
+        <v>194700</v>
       </c>
       <c r="G83" s="3">
-        <v>483200</v>
+        <v>525400</v>
       </c>
       <c r="H83" s="3">
-        <v>492100</v>
+        <v>491000</v>
       </c>
       <c r="I83" s="3">
-        <v>471200</v>
+        <v>485700</v>
       </c>
       <c r="J83" s="3">
+        <v>257800</v>
+      </c>
+      <c r="K83" s="3">
         <v>492000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>453200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>444900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>473800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>536800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>526500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>543100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>520500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>492200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>545800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>537500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>623100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>600400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>541700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>554500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>496000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>442500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>411100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>396100</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>413800</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>448800</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>449300</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>429100</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>410100</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>432800</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>438700</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7587,8 +7788,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7688,8 +7892,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7789,8 +7996,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7890,8 +8100,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7991,109 +8204,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>2026500</v>
+        <v>2166200</v>
       </c>
       <c r="E89" s="3">
-        <v>1298000</v>
+        <v>1774300</v>
       </c>
       <c r="F89" s="3">
-        <v>1527300</v>
+        <v>1208700</v>
       </c>
       <c r="G89" s="3">
-        <v>721900</v>
+        <v>1526000</v>
       </c>
       <c r="H89" s="3">
-        <v>2590200</v>
+        <v>667300</v>
       </c>
       <c r="I89" s="3">
-        <v>3178300</v>
+        <v>2537100</v>
       </c>
       <c r="J89" s="3">
+        <v>3367400</v>
+      </c>
+      <c r="K89" s="3">
         <v>2055600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>187800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1893500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2973900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>356300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>921800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1317900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1916000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>891400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1688800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1399300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1229000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>548400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1827000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1171400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>472800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1886300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>251200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1223700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1352500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>2182700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-372700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1833000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1624300</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1312000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>298600</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8129,109 +8348,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-96241000</v>
+        <v>-481100</v>
       </c>
       <c r="E91" s="3">
-        <v>-72428000</v>
+        <v>-598300</v>
       </c>
       <c r="F91" s="3">
-        <v>-80828000</v>
+        <v>-478800</v>
       </c>
       <c r="G91" s="3">
-        <v>-78404000</v>
+        <v>-573400</v>
       </c>
       <c r="H91" s="3">
-        <v>-63111000</v>
+        <v>-524900</v>
       </c>
       <c r="I91" s="3">
-        <v>-52536000</v>
+        <v>-436500</v>
       </c>
       <c r="J91" s="3">
+        <v>-395200</v>
+      </c>
+      <c r="K91" s="3">
         <v>-66573000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-54756000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-54200000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-44019000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-50278000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-44762000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-341500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-275500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-358300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-357300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-700100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-669200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-792800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-579100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-566500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-717000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-868800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-680800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-616300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>707600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-337700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-384300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-196300</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-458100</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-338400</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-537000</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8331,8 +8554,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8432,109 +8658,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-174400</v>
+        <v>-116000</v>
       </c>
       <c r="E94" s="3">
-        <v>-736400</v>
+        <v>-152700</v>
       </c>
       <c r="F94" s="3">
-        <v>-193900</v>
+        <v>-685700</v>
       </c>
       <c r="G94" s="3">
-        <v>-726100</v>
+        <v>-193700</v>
       </c>
       <c r="H94" s="3">
-        <v>-1379200</v>
+        <v>-684700</v>
       </c>
       <c r="I94" s="3">
-        <v>-368800</v>
+        <v>-1343500</v>
       </c>
       <c r="J94" s="3">
+        <v>-390700</v>
+      </c>
+      <c r="K94" s="3">
         <v>39800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-130100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-752200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>61100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-286000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-405500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-680000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-98800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-618100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-901100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-925800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>186300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-718500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-156200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1012200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-2595500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1897000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1369400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-914400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-579400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-717100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-761300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-186100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-967700</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-474900</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-603200</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8570,109 +8802,113 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-903700</v>
+        <v>0</v>
       </c>
       <c r="E96" s="3">
-        <v>0</v>
+        <v>791200</v>
       </c>
       <c r="F96" s="3">
-        <v>-909100</v>
+        <v>0</v>
       </c>
       <c r="G96" s="3">
-        <v>0</v>
+        <v>908400</v>
       </c>
       <c r="H96" s="3">
-        <v>-811700</v>
+        <v>0</v>
       </c>
       <c r="I96" s="3">
-        <v>0</v>
+        <v>790700</v>
       </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>-724400</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>-647400</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>-502400</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-551900</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
         <v>-492400</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
       <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
         <v>-582600</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
       <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
         <v>-633600</v>
       </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
       <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-636800</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
       <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-656300</v>
       </c>
-      <c r="AA96" s="3">
-        <v>0</v>
-      </c>
       <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-631900</v>
       </c>
-      <c r="AC96" s="3">
-        <v>0</v>
-      </c>
       <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-478400</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
       <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-478400</v>
       </c>
-      <c r="AG96" s="3">
-        <v>0</v>
-      </c>
       <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-397500</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8772,8 +9008,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8873,8 +9112,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8974,307 +9216,319 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-1115500</v>
+        <v>-2894600</v>
       </c>
       <c r="E100" s="3">
-        <v>-2386300</v>
+        <v>-976700</v>
       </c>
       <c r="F100" s="3">
-        <v>-1748100</v>
+        <v>-2222100</v>
       </c>
       <c r="G100" s="3">
-        <v>-650800</v>
+        <v>-1746700</v>
       </c>
       <c r="H100" s="3">
-        <v>-2407600</v>
+        <v>-613700</v>
       </c>
       <c r="I100" s="3">
-        <v>-1824900</v>
+        <v>-2345300</v>
       </c>
       <c r="J100" s="3">
+        <v>-1933500</v>
+      </c>
+      <c r="K100" s="3">
         <v>-494900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1136700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-874800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1439500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-322200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1286200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1266100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1451100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1099300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-343300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-752700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-130100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1862200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-68800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>202500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>2126800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-385900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>482800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-954700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1145700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1020400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-2791000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-939700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-1316100</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-841900</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>217200</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>238500</v>
+        <v>55100</v>
       </c>
       <c r="E101" s="3">
-        <v>238600</v>
+        <v>413000</v>
       </c>
       <c r="F101" s="3">
-        <v>-122700</v>
+        <v>42400</v>
       </c>
       <c r="G101" s="3">
-        <v>58400</v>
+        <v>-350500</v>
       </c>
       <c r="H101" s="3">
-        <v>424000</v>
+        <v>114700</v>
       </c>
       <c r="I101" s="3">
-        <v>40000</v>
+        <v>380700</v>
       </c>
       <c r="J101" s="3">
+        <v>382500</v>
+      </c>
+      <c r="K101" s="3">
         <v>-328200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>105900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>348700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>308400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>120700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-61400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-15900</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>233800</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-59100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>6600</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>131300</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-293800</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>148200</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-82300</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-72700</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>23700</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-142100</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>124000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>45000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-335900</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>3300</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>100100</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>10700</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-65200</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>603600</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-59700</v>
       </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>975200</v>
+        <v>-1244300</v>
       </c>
       <c r="E102" s="3">
-        <v>-1586200</v>
+        <v>853800</v>
       </c>
       <c r="F102" s="3">
-        <v>-537400</v>
+        <v>-1477000</v>
       </c>
       <c r="G102" s="3">
-        <v>-596500</v>
+        <v>-536900</v>
       </c>
       <c r="H102" s="3">
-        <v>-772600</v>
+        <v>-576000</v>
       </c>
       <c r="I102" s="3">
-        <v>1024600</v>
+        <v>-738700</v>
       </c>
       <c r="J102" s="3">
+        <v>1085600</v>
+      </c>
+      <c r="K102" s="3">
         <v>1272400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-973100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>615100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1903900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-131200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-831200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-644100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>600000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-885100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>451000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-148000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>991400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-1884100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>1519700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>289000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>27700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-404700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-643100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-600500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-708500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>448600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-3824900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>717900</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-724700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>598900</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-147200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MITSY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MITSY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="92">
   <si>
     <t>MITSY</t>
   </si>
@@ -656,138 +656,141 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="13" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="35" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="14" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="36" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -812,86 +815,89 @@
       <c r="J8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K8" s="3">
+      <c r="K8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L8" s="3">
         <v>25650200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>23627000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>25076400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>21036400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>21800100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>19886400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>19536500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>23476100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>14920200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>14487100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>15741000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>28986100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>16240900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>16340900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>14959400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>18687200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>16988500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>15394900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>14145800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>11201800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>11381200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>10959900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>10682200</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>10539300</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>10144100</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>8977900</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -916,86 +922,89 @@
       <c r="J9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K9" s="3">
+      <c r="K9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L9" s="3">
         <v>22907200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>21595000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>22963900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>18701800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>19997700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>18017600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>17565000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>21751400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>13451500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>13099400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>14122800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>27233000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>14307400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>14328700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>13042800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>16713400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>15012100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>13487900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>12160100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>9567400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>9519200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>9110700</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>8879700</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>8666700</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>8528400</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>7541800</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1020,86 +1029,89 @@
       <c r="J10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K10" s="3">
+      <c r="K10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L10" s="3">
         <v>2743000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2031900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2112500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2334500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1802400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1868700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1971500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1724700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1468700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1387600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1618200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1753200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1933500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2012200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1916600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1973800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1976400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1906900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1985700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1634400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1861900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1849100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1802500</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1872600</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1615700</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1436100</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1136,8 +1148,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1240,8 +1253,11 @@
       <c r="AJ12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1344,8 +1360,11 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1370,86 +1389,89 @@
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="3">
         <v>37400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>67300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>32100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>10800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>163500</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-1600</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>90700</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>262100</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>38700</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>2600</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>874000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>82100</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>8300</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>15500</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>225400</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>20700</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>3800</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>8900</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>59600</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>91800</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>67000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>11600</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>48200</v>
       </c>
-      <c r="AI14" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1474,8 +1496,8 @@
       <c r="J15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
+      <c r="K15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
@@ -1552,8 +1574,11 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1587,8 +1612,9 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1613,86 +1639,89 @@
       <c r="J17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K17" s="3">
+      <c r="K17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L17" s="3">
         <v>23948200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>22600500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>23836300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>19830800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>20835700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>19119900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>18538500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>22976200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>14945300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>14328800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>15201000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>29074600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>15671900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>15581200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>14210600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>18422900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>16308000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>14800500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>13271100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>11108400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>10721200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>10139700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>9954000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>9794000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>9291500</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>8516000</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1717,86 +1746,89 @@
       <c r="J18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K18" s="3">
+      <c r="K18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L18" s="3">
         <v>1701900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1026400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1240000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1205600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>964400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>766500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>998000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>500000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-25200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>158300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>540000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-88400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>569000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>759700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>748700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>264200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>680500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>594400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>874700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>93400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>660000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>820200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>728200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>745300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>852600</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>461900</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1833,8 +1865,9 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1859,86 +1892,89 @@
       <c r="J20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L20" s="3">
         <v>1211100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1290200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1215700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1076700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1107600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1367000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>990700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>836800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>762100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>586800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>461600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>822000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1024200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>799300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>1048100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>949200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>1042200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>982200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>815900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>682600</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>963900</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>765600</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>808400</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>451900</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>662000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>545900</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1963,86 +1999,89 @@
       <c r="J21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K21" s="3">
+      <c r="K21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L21" s="3">
         <v>3405000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2769800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2900600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2756100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2608800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2659900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2531800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1857200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1229100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1290900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1539200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1356700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2193700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>2100800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>2351400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1709400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>2165200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1987800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>2086700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1189800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>2072700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>2035100</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1965600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1607200</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1947400</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1446600</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2067,86 +2106,89 @@
       <c r="J22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K22" s="3">
+      <c r="K22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L22" s="3">
         <v>236200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>148400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>110500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>76000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>69100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>82400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>105800</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>77600</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>92500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>100800</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>131600</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>178400</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>205000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>212500</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>217600</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>194400</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>191600</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>191700</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>172300</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>149100</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>150300</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>156500</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>145100</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>140900</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>133700</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>118100</v>
       </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2171,86 +2213,89 @@
       <c r="J23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K23" s="3">
+      <c r="K23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L23" s="3">
         <v>2676800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2168200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2345200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2206300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2002900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2051000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1883000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1259100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>644500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>644300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>870000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>555100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1388200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1346500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1579200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1019000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1531100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1384900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1518300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>626900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1473600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1429300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1391500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1056300</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1380900</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>889700</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2275,86 +2320,89 @@
       <c r="J24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K24" s="3">
+      <c r="K24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L24" s="3">
         <v>502000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>460500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>401700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>299100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>402700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>482800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>413000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>260700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-32100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>250100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>301300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>88400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>409100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>280700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>343700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>397900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>289000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>367300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>372800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>201200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>158300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>234300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>338000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>320800</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>367600</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>316000</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2457,8 +2505,11 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2483,86 +2534,89 @@
       <c r="J26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K26" s="3">
+      <c r="K26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L26" s="3">
         <v>2174800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1707800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1943500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1907200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1600200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1568200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1470000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>998400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>676500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>394200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>568600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>466700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>979200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1065800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1235500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>621100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1242100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1017600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1145500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>425700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1315300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1195000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>1053500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>735500</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>1013300</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>573700</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2587,86 +2641,89 @@
       <c r="J27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K27" s="3">
+      <c r="K27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L27" s="3">
         <v>2141900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1685000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1853500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1868900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1570700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1538400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1405800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>967900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>651700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>369800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>533600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>497200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>919400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1002800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1145300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>616500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1200700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>970400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1076400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>376500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1252300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1153100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>1001200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>672400</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>961100</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>539600</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2769,8 +2826,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2795,8 +2855,8 @@
       <c r="J29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
+      <c r="K29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L29" s="3">
         <v>0</v>
@@ -2873,8 +2933,11 @@
       <c r="AJ29" s="3">
         <v>0</v>
       </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2977,8 +3040,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3081,8 +3147,11 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3107,86 +3176,89 @@
       <c r="J32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L32" s="3">
         <v>-1211100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1290200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1215700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1076700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1107600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1367000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-990700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-836800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-762100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-586800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-461600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-822000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1024200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-799300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-1048100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-949200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-1042200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-982200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-815900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-682600</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-963900</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-765600</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-808400</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-451900</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-662000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-545900</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3211,86 +3283,89 @@
       <c r="J33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K33" s="3">
+      <c r="K33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L33" s="3">
         <v>2141900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1685000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1853500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1868900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1570700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1538400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1405800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>967900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>651700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>369800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>533600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>497200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>919400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1002800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1145300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>616500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1200700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>970400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1076400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>376500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1252300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1153100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>1001200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>672400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>961100</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>539600</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3393,8 +3468,11 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3419,195 +3497,201 @@
       <c r="J35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K35" s="3">
+      <c r="K35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L35" s="3">
         <v>2141900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1685000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1853500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1868900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1570700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1538400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1405800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>967900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>651700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>369800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>533600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>497200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>919400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1002800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1145300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>616500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1200700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>970400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1076400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>376500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1252300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1153100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>1001200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>672400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>961100</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>539600</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3644,8 +3728,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3682,112 +3767,116 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6035200</v>
+      </c>
+      <c r="E41" s="3">
         <v>5983900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>6437400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>5938300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>7956800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>8016100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>8862000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>10457300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>8845300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>6805000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>8217000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>7489000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>5778600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>6202300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>7170000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>7537700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>7172600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>8563400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>8883000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>9327400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>8619900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>10596300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>9047000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>9188200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>8998400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>9253700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>9683800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>10227700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>10936200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>10487600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>14312400</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>13338900</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>14063500</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>13464600</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3798,11 +3887,11 @@
         <v>0</v>
       </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>29900</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
       <c r="H42" s="3">
         <v>0</v>
       </c>
@@ -3810,816 +3899,840 @@
         <v>0</v>
       </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>50300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>7188900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>8123200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>7698600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>6625800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>6088600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>5687100</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>4151400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>3048600</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>3152600</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>3119600</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>3626700</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>4959100</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>3002000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>2707200</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>2753000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>2445800</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>3255400</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>2869100</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>2702600</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>2205000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>3030500</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>2627800</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>2445500</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>2374300</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>3915400</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>3786600</v>
       </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>15344800</v>
+      </c>
+      <c r="E43" s="3">
         <v>15610800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>15335400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>17120500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>16334400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>14856300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>14613900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>17991700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>16929900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>15444400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>16786300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>15292800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>15852800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>13571000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>13780400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>12847000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>12632200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>11204300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>12454600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>14294200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>16566500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>14911000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>15916900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>17338600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>17779600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>16564800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>15649400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>15964800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>17290200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>16461900</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>14971500</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>15428500</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>15480700</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>13205700</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>6839100</v>
+      </c>
+      <c r="E44" s="3">
         <v>6684200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>6158700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>6384700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>6546400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>6130800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>6647900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>7075300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>7257600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>6519300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>6577600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>6305800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>6092800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>5348100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>5282900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>4361400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>4413800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>4318400</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>4554700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>4879500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>6283100</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>5890100</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>5901000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>5839800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>5950700</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>5828600</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>5150500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>4978300</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>5689100</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>5718500</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>5394500</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>5229200</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>5336700</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>4779400</v>
       </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>9580300</v>
+      </c>
+      <c r="E45" s="3">
         <v>9926400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>11358800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>8661800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>10355500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>9737900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>10486700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>7114500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3063800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2394200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2765400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2245300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2327600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2275500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2305600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2036200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2036500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2138300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2623100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2875800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2941600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>2909800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>3240200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>3592300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>3707100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>3593900</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>3510500</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>4828700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>4005100</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>3659200</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>3525900</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>3320100</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>3359700</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>2996000</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>37799400</v>
+      </c>
+      <c r="E46" s="3">
         <v>38205300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>39290200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>38135300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>41193200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>38741100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>40610400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>42689100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>43285600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>39286100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>42044900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>37958800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>36140400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>33084000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>32690400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>29831000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>29407700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>29344000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>32142100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>36336100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>37413100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>37014400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>36858100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>38404700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>39691200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>38110200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>36696800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>38204500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>40951100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>38955000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>40649900</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>39691000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>42156100</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>38232400</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>46014100</v>
+      </c>
+      <c r="E47" s="3">
         <v>48591000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>46012800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>47546900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>49006300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>46203000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>44651900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>45632700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>45576500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>42559700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>43167900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>41318100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>38904100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>40110200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>42558000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>38622100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>37234400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>38999900</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>42508800</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>43819300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>50414800</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>49513500</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>50532700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>53209900</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>48784500</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>49446400</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>45792300</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>44126500</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>45878300</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>44160100</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>42595400</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>41700800</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>39980100</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>35285000</v>
       </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>16381300</v>
+      </c>
+      <c r="E48" s="3">
         <v>16766200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>15999900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>15877100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>16660800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>16273300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>17114800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>17306400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>18096300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>17008700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>17712200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>16662900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>16691900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>17196100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>17942800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>17369900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>17576200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>18818600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>20573600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>20908000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>22359200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>21602500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>21397900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>20646900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>20363100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>19807500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>18394900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>17346400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>17820100</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>18003700</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>17903900</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>17769100</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>18403400</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>16888800</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3071600</v>
+      </c>
+      <c r="E49" s="3">
         <v>3268000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3155900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3029600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3154100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2975900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2995300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2086100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2005000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1888200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1898700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1680200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1568100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1529500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1604900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1336900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1365200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1507700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1644000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1720500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>2151300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>2186600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>2230100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1673000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1743600</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1607100</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1552500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1565800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1572800</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1615000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1568500</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>1496200</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>1434400</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>1274500</v>
       </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4722,8 +4835,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4826,112 +4942,118 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4376400</v>
+      </c>
+      <c r="E52" s="3">
         <v>4411800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>4789800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4761800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>4201200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4469200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4569800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>5022900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1576500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1578100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1578300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1470700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1415900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1479100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1529400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1577500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1215900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>984000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1107500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1229500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>850800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>851500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>819700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>864500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1064200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1091400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1002900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>969100</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1006800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1169300</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1357900</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1356900</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1432200</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1287300</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5034,112 +5156,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>110450000</v>
+      </c>
+      <c r="E54" s="3">
         <v>113744000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>111769500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>111728600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>116974300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>111437900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>112815100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>115703400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>110539800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>102320900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>106402000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>99090600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>94720400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>93398900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>96325500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>88737300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>86799500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>89654300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>97976000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>104013400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>113189100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>111168500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>111838500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>114798900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>111646700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>110062600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>103439500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>102212200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>107229100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>103903100</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>104075500</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>102014000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>103406200</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>92968100</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5176,8 +5304,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5214,632 +5343,651 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>11611300</v>
+      </c>
+      <c r="E57" s="3">
         <v>11222400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>11288100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>9498000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>12321600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>10818500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>11080800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>10059000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>12531200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>10965800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>12544700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>11547900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>11758900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>10074300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>10382200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>9311600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>8737600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>8288800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>8744100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>10012600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>11770300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>10845800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>11551100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>12707100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>13217100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>12028200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>11694800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>11429100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>12147200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>11328200</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>10649200</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>10676900</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>10787700</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>8887300</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>5575600</v>
+      </c>
+      <c r="E58" s="3">
         <v>5812800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>7401400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>6393500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>7399900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>7190800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>6481000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>9352200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>8859900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>8276900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>7751000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>4595500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>5029900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>5764700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>5962600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>5327600</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>5047300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>5228200</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>6306000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>6143800</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>6544700</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>7261900</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>8192800</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>7845800</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>7553600</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>6959600</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>6294800</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>6184300</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>5829800</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>5542100</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>6488500</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>6146100</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>7075800</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>6388700</v>
       </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>8202400</v>
+      </c>
+      <c r="E59" s="3">
         <v>8096000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>8963900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>8445800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>8028100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>8175600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>8720800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>7620400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>8159800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>10312300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>10810700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>9145900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>6802800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>6487000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>5634600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>4516000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>4513900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>4330200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>4931400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>7640400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>6186700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>5577100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>5804100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>5781200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>6905100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>6461800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>6059700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>6783400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>6711400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>5826600</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>5765000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>5564600</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>5821700</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>4722300</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>25389400</v>
+      </c>
+      <c r="E60" s="3">
         <v>25131200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>27653400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>25728300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>27749600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>26184900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>26282500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>28334600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>29550900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>29555000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>31106500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>25289300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>23591600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>22326000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>21979400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>19155200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>18298800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>17847200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>19981500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>23796800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>24501800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>23684800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>25548000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>26334000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>27675800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>25449500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>24049300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>24396900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>24688500</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>22697000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>22902800</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>22387600</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>23685200</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>19998200</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>26129600</v>
+      </c>
+      <c r="E61" s="3">
         <v>25551400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>23765800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>25182700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>27316400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>26820700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>28735500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>28565500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>27489000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>25059200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>27278200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>27790900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>28115400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>27947800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>29338200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>28326800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>30052900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>32828400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>35839200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>37259400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>38486000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>38586200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>37173100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>36605000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>33965600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>33739000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>32441500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>32027200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>34920400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>35699100</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>37405600</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>37431100</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>38250500</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>36521200</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>4639800</v>
+      </c>
+      <c r="E62" s="3">
         <v>4035000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>4657400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4226200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4199900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>4520300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>4351100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>4261800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>8578500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>7754600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>7707600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>7528900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>6977600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>7137200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>7774600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>7061100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>6336400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>6416800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>6975900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>7180400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>8188900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>7779100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>7906600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>8323600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>8124200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>8671300</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>7800000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>7656300</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>7269000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>7278500</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>7072300</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>6802600</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>6766700</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>5977300</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5942,8 +6090,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6046,8 +6197,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6150,112 +6304,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>61001900</v>
+      </c>
+      <c r="E66" s="3">
         <v>60132700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>61063700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>60358700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>65011800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>62688200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>64405100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>66316900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>67084800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>63752000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>67506000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>61872100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>60471700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>59233700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>60973500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>56333100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>56483400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>59007300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>64958700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>70379700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>73667400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>72465300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>73055600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>73829900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>72239100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>70300400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>66567400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>66280800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>69332300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>68053100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>69759100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>68909600</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>71093200</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>64647500</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6292,8 +6452,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6396,8 +6557,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6500,8 +6664,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6604,8 +6771,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6708,112 +6878,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>36646800</v>
+      </c>
+      <c r="E72" s="3">
         <v>40847100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>35592300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>36704500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>37180800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>34085100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>34435100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>36412900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>33403000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>28566600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>29304600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>27662000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>26560900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>26825200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>26541400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>25153800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>24743600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>26163700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>28238800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>29621800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>30109600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>30037200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>28668100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>29585900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>28566200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>22079200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>25998200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>26247000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>25531600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>24759700</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>23601500</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>22619600</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>21765100</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>21151000</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6916,8 +7092,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7020,8 +7199,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7124,112 +7306,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>48027900</v>
+      </c>
+      <c r="E76" s="3">
         <v>52065200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>49244700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>49861800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>50373100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>47278000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>46921600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>47901600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>43455000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>38568900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>38896000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>37218600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>34248700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>34165100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>35352000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>32404300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>30316100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>30647000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>33017300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>33633700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>39521800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>38703100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>38782900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>40969000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>39407500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>39762100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>36872200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>35931400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>37896800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>35850000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>34316500</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>33104400</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>32312900</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>28320500</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7332,117 +7520,123 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -7467,86 +7661,89 @@
       <c r="J81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K81" s="3">
+      <c r="K81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L81" s="3">
         <v>2141900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1685000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1853500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1868900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1570700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1538400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1405800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>967900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>651700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>369800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>533600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>497200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>919400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1002800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1145300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>616500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1200700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>970400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1076400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>376500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1252300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1153100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>1001200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>672400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>961100</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>539600</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7583,112 +7780,116 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>507700</v>
+      </c>
+      <c r="E83" s="3">
         <v>455700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>479400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>194700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>525400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>491000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>485700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>257800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>492000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>453200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>444900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>473800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>536800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>526500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>543100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>520500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>492200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>545800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>537500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>623100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>600400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>541700</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>554500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>496000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>442500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>411100</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>396100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>413800</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>448800</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>449300</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>429100</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>410100</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>432800</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>438700</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7791,8 +7992,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7895,8 +8099,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7999,8 +8206,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8103,8 +8313,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8207,112 +8420,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1129500</v>
+      </c>
+      <c r="E89" s="3">
         <v>2166200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1774300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1208700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1526000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>667300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2537100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>3367400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2055600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>187800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1893500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2973900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>356300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>921800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1317900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1916000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>891400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1688800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1399300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1229000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>548400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1827000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1171400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>472800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1886300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>251200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1223700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1352500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>2182700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-372700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1833000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1624300</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1312000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>298600</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8349,112 +8568,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-559200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-481100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-598300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-478800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-573400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-524900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-436500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-395200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-66573000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-54756000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-54200000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-44019000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-50278000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-44762000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-341500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-275500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-358300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-357300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-700100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-669200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-792800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-579100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-566500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-717000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-868800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-680800</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-616300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>707600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-337700</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-384300</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-196300</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-458100</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-338400</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-537000</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8557,8 +8780,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8661,112 +8887,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-192400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-116000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-152700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-685700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-193700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-684700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1343500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-390700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>39800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-130100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-752200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>61100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-286000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-405500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-680000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-98800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-618100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-901100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-925800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>186300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-718500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-156200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1012200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-2595500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1897000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1369400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-914400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-579400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-717100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-761300</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-186100</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-967700</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-474900</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-603200</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8803,112 +9035,116 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>934200</v>
       </c>
       <c r="E96" s="3">
+        <v>0</v>
+      </c>
+      <c r="F96" s="3">
         <v>791200</v>
       </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
       <c r="G96" s="3">
+        <v>0</v>
+      </c>
+      <c r="H96" s="3">
         <v>908400</v>
       </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
       <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
         <v>790700</v>
       </c>
-      <c r="J96" s="3">
-        <v>0</v>
-      </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>-724400</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>-647400</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>-502400</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>-551900</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-492400</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-582600</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-633600</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-636800</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-656300</v>
       </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-631900</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-478400</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
       <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-478400</v>
       </c>
-      <c r="AH96" s="3">
-        <v>0</v>
-      </c>
       <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-397500</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9011,8 +9247,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9115,8 +9354,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9219,316 +9461,328 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-521100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2894600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-976700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2222100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1746700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-613700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-2345300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1933500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-494900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1136700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-874800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1439500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-322200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1286200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1266100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1451100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1099300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-343300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-752700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-130100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1862200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-68800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>202500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>2126800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-385900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>482800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-954700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1145700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1020400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-2791000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-939700</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-1316100</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-841900</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>217200</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-122600</v>
+      </c>
+      <c r="E101" s="3">
         <v>55100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>413000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>42400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-350500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>114700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>380700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>382500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-328200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>105900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>348700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>308400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>120700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-61400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-15900</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>233800</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-59100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>6600</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>131300</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-293800</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>148200</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-82300</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-72700</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>23700</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-142100</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>124000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>45000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-335900</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>3300</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>100100</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>10700</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-65200</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>603600</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-59700</v>
       </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>582400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1244300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>853800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1477000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-536900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-576000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-738700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1085600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1272400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-973100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>615100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1903900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-131200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-831200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-644100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>600000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-885100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>451000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-148000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>991400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-1884100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>1519700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>289000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>27700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-404700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-643100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-600500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-708500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>448600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-3824900</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>717900</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-724700</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>598900</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-147200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MITSY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MITSY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="92">
   <si>
     <t>MITSY</t>
   </si>
@@ -656,141 +656,144 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="14" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="36" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="15" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="37" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -818,86 +821,89 @@
       <c r="K8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L8" s="3">
+      <c r="L8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M8" s="3">
         <v>25650200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>23627000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>25076400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>21036400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>21800100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>19886400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>19536500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>23476100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>14920200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>14487100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>15741000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>28986100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>16240900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>16340900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>14959400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>18687200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>16988500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>15394900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>14145800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>11201800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>11381200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>10959900</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>10682200</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>10539300</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>10144100</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>8977900</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -925,86 +931,89 @@
       <c r="K9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L9" s="3">
+      <c r="L9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M9" s="3">
         <v>22907200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>21595000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>22963900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>18701800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>19997700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>18017600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>17565000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>21751400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>13451500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>13099400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>14122800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>27233000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>14307400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>14328700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>13042800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>16713400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>15012100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>13487900</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>12160100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>9567400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>9519200</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>9110700</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>8879700</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>8666700</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>8528400</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>7541800</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1032,86 +1041,89 @@
       <c r="K10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L10" s="3">
+      <c r="L10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M10" s="3">
         <v>2743000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2031900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2112500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2334500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1802400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1868700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1971500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1724700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1468700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1387600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1618200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1753200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1933500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2012200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1916600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1973800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1976400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1906900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1985700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1634400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1861900</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1849100</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1802500</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1872600</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1615700</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>1436100</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1149,8 +1161,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1256,8 +1269,11 @@
       <c r="AK12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1363,8 +1379,11 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1392,86 +1411,89 @@
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="3">
         <v>37400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>67300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>1800</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>32100</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>10800</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>163500</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-1600</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>90700</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>262100</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>38700</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>2600</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>874000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>82100</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>8300</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>15500</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>225400</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>20700</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>3800</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>8900</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>59600</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>91800</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>67000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>11600</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>48200</v>
       </c>
-      <c r="AJ14" s="3">
-        <v>0</v>
-      </c>
       <c r="AK14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL14" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1499,8 +1521,8 @@
       <c r="K15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
+      <c r="L15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1577,8 +1599,11 @@
       <c r="AK15" s="3">
         <v>0</v>
       </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1613,8 +1638,9 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1642,86 +1668,89 @@
       <c r="K17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L17" s="3">
+      <c r="L17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M17" s="3">
         <v>23948200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>22600500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>23836300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>19830800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>20835700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>19119900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>18538500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>22976200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>14945300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>14328800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>15201000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>29074600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>15671900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>15581200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>14210600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>18422900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>16308000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>14800500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>13271100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>11108400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>10721200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>10139700</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>9954000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>9794000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>9291500</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>8516000</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1749,86 +1778,89 @@
       <c r="K18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L18" s="3">
+      <c r="L18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M18" s="3">
         <v>1701900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1026400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1240000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1205600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>964400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>766500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>998000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>500000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-25200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>158300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>540000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-88400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>569000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>759700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>748700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>264200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>680500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>594400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>874700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>93400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>660000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>820200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>728200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>745300</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>852600</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>461900</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1866,8 +1898,9 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1895,86 +1928,89 @@
       <c r="K20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M20" s="3">
         <v>1211100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1290200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1215700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1076700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1107600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1367000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>990700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>836800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>762100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>586800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>461600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>822000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>1024200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>799300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>1048100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>949200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>1042200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>982200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>815900</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>682600</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>963900</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>765600</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>808400</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>451900</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>662000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>545900</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2002,86 +2038,89 @@
       <c r="K21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L21" s="3">
+      <c r="L21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M21" s="3">
         <v>3405000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2769800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2900600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2756100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2608800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2659900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2531800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1857200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1229100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1290900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1539200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1356700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>2193700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>2100800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>2351400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1709400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>2165200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1987800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>2086700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1189800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>2072700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>2035100</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1965600</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1607200</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1947400</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1446600</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2109,86 +2148,89 @@
       <c r="K22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L22" s="3">
+      <c r="L22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M22" s="3">
         <v>236200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>148400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>110500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>76000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>69100</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>82400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>105800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>77600</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>92500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>100800</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>131600</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>178400</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>205000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>212500</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>217600</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>194400</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>191600</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>191700</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>172300</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>149100</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>150300</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>156500</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>145100</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>140900</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>133700</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>118100</v>
       </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2216,86 +2258,89 @@
       <c r="K23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L23" s="3">
+      <c r="L23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M23" s="3">
         <v>2676800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2168200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2345200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2206300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2002900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2051000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1883000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1259100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>644500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>644300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>870000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>555100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1388200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1346500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1579200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1019000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1531100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1384900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1518300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>626900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1473600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1429300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1391500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1056300</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>1380900</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>889700</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2323,86 +2368,89 @@
       <c r="K24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L24" s="3">
+      <c r="L24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M24" s="3">
         <v>502000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>460500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>401700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>299100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>402700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>482800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>413000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>260700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-32100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>250100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>301300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>88400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>409100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>280700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>343700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>397900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>289000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>367300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>372800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>201200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>158300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>234300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>338000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>320800</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>367600</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>316000</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2508,8 +2556,11 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2537,86 +2588,89 @@
       <c r="K26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L26" s="3">
+      <c r="L26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M26" s="3">
         <v>2174800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1707800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1943500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1907200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1600200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1568200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1470000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>998400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>676500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>394200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>568600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>466700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>979200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1065800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1235500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>621100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1242100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1017600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1145500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>425700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1315300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>1195000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1053500</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>735500</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>1013300</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>573700</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2644,86 +2698,89 @@
       <c r="K27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L27" s="3">
+      <c r="L27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M27" s="3">
         <v>2141900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1685000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1853500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1868900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1570700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1538400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1405800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>967900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>651700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>369800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>533600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>497200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>919400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1002800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1145300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>616500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1200700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>970400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1076400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>376500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1252300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>1153100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>1001200</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>672400</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>961100</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>539600</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2829,8 +2886,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2858,8 +2918,8 @@
       <c r="K29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L29" s="3">
-        <v>0</v>
+      <c r="L29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M29" s="3">
         <v>0</v>
@@ -2936,8 +2996,11 @@
       <c r="AK29" s="3">
         <v>0</v>
       </c>
+      <c r="AL29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3043,8 +3106,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3150,8 +3216,11 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3179,86 +3248,89 @@
       <c r="K32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M32" s="3">
         <v>-1211100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1290200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1215700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1076700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1107600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1367000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-990700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-836800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-762100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-586800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-461600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-822000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-1024200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-799300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-1048100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-949200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-1042200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-982200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-815900</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-682600</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-963900</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-765600</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-808400</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-451900</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-662000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-545900</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3286,86 +3358,89 @@
       <c r="K33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L33" s="3">
+      <c r="L33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M33" s="3">
         <v>2141900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1685000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1853500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1868900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1570700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1538400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1405800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>967900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>651700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>369800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>533600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>497200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>919400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1002800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1145300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>616500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1200700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>970400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1076400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>376500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1252300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>1153100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>1001200</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>672400</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>961100</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>539600</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3471,8 +3546,11 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3500,198 +3578,204 @@
       <c r="K35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L35" s="3">
+      <c r="L35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M35" s="3">
         <v>2141900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1685000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1853500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1868900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1570700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1538400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1405800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>967900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>651700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>369800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>533600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>497200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>919400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1002800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1145300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>616500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1200700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>970400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1076400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>376500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1252300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>1153100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>1001200</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>672400</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>961100</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>539600</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3729,8 +3813,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3768,115 +3853,119 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6526700</v>
+      </c>
+      <c r="E41" s="3">
         <v>6035200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>5983900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>6437400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>5938300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>7956800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>8016100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>8862000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>10457300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>8845300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>6805000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>8217000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>7489000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>5778600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>6202300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>7170000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>7537700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>7172600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>8563400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>8883000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>9327400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>8619900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>10596300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>9047000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>9188200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>8998400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>9253700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>9683800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>10227700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>10936200</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>10487600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>14312400</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>13338900</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>14063500</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>13464600</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3890,11 +3979,11 @@
         <v>0</v>
       </c>
       <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>29900</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
       <c r="I42" s="3">
         <v>0</v>
       </c>
@@ -3902,837 +3991,861 @@
         <v>0</v>
       </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>50300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>7188900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>8123200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>7698600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>6625800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>6088600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>5687100</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>4151400</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>3048600</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>3152600</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>3119600</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>3626700</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>4959100</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>3002000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>2707200</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>2753000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>2445800</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>3255400</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>2869100</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>2702600</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>2205000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>3030500</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>2627800</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>2445500</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>2374300</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>3915400</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>3786600</v>
       </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>15014400</v>
+      </c>
+      <c r="E43" s="3">
         <v>15344800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>15610800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>15335400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>17120500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>16334400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>14856300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>14613900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>17991700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>16929900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>15444400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>16786300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>15292800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>15852800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>13571000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>13780400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>12847000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>12632200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>11204300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>12454600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>14294200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>16566500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>14911000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>15916900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>17338600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>17779600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>16564800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>15649400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>15964800</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>17290200</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>16461900</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>14971500</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>15428500</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>15480700</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>13205700</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>6413800</v>
+      </c>
+      <c r="E44" s="3">
         <v>6839100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>6684200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>6158700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>6384700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>6546400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>6130800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>6647900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>7075300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>7257600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>6519300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>6577600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>6305800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>6092800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>5348100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>5282900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>4361400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>4413800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>4318400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>4554700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>4879500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>6283100</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>5890100</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>5901000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>5839800</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>5950700</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>5828600</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>5150500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>4978300</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>5689100</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>5718500</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>5394500</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>5229200</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>5336700</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>4779400</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>10021900</v>
+      </c>
+      <c r="E45" s="3">
         <v>9580300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>9926400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>11358800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>8661800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>10355500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>9737900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>10486700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>7114500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3063800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2394200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2765400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2245300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2327600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2275500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2305600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2036200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2036500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2138300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2623100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2875800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>2941600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>2909800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>3240200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>3592300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>3707100</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>3593900</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>3510500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>4828700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>4005100</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>3659200</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>3525900</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>3320100</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>3359700</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>2996000</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>37976700</v>
+      </c>
+      <c r="E46" s="3">
         <v>37799400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>38205300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>39290200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>38135300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>41193200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>38741100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>40610400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>42689100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>43285600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>39286100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>42044900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>37958800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>36140400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>33084000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>32690400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>29831000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>29407700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>29344000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>32142100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>36336100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>37413100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>37014400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>36858100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>38404700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>39691200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>38110200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>36696800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>38204500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>40951100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>38955000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>40649900</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>39691000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>42156100</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>38232400</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>47840900</v>
+      </c>
+      <c r="E47" s="3">
         <v>46014100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>48591000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>46012800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>47546900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>49006300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>46203000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>44651900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>45632700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>45576500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>42559700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>43167900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>41318100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>38904100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>40110200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>42558000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>38622100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>37234400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>38999900</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>42508800</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>43819300</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>50414800</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>49513500</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>50532700</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>53209900</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>48784500</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>49446400</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>45792300</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>44126500</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>45878300</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>44160100</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>42595400</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>41700800</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>39980100</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>35285000</v>
       </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>16491400</v>
+      </c>
+      <c r="E48" s="3">
         <v>16381300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>16766200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>15999900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>15877100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>16660800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>16273300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>17114800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>17306400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>18096300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>17008700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>17712200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>16662900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>16691900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>17196100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>17942800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>17369900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>17576200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>18818600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>20573600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>20908000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>22359200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>21602500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>21397900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>20646900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>20363100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>19807500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>18394900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>17346400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>17820100</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>18003700</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>17903900</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>17769100</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>18403400</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>16888800</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3375300</v>
+      </c>
+      <c r="E49" s="3">
         <v>3071600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3268000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3155900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3029600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3154100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2975900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2995300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2086100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2005000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1888200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1898700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1680200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1568100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1529500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1604900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1336900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1365200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1507700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1644000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1720500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>2151300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>2186600</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>2230100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1673000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1743600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1607100</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1552500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1565800</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1572800</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1615000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>1568500</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>1496200</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>1434400</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>1274500</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4838,8 +4951,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4945,115 +5061,121 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3899800</v>
+      </c>
+      <c r="E52" s="3">
         <v>4376400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>4411800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4789800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>4761800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4201200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4469200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4569800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>5022900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1576500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1578100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1578300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1470700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1415900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1479100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1529400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1577500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1215900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>984000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1107500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1229500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>850800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>851500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>819700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>864500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1064200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1091400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1002900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>969100</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1006800</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1169300</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1357900</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1356900</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1432200</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>1287300</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5159,115 +5281,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>112265300</v>
+      </c>
+      <c r="E54" s="3">
         <v>110450000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>113744000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>111769500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>111728600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>116974300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>111437900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>112815100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>115703400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>110539800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>102320900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>106402000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>99090600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>94720400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>93398900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>96325500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>88737300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>86799500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>89654300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>97976000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>104013400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>113189100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>111168500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>111838500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>114798900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>111646700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>110062600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>103439500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>102212200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>107229100</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>103903100</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>104075500</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>102014000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>103406200</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>92968100</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5305,8 +5433,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5344,650 +5473,669 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>11189900</v>
+      </c>
+      <c r="E57" s="3">
         <v>11611300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>11222400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>11288100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>9498000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>12321600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>10818500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>11080800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>10059000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>12531200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>10965800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>12544700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>11547900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>11758900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>10074300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>10382200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>9311600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>8737600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>8288800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>8744100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>10012600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>11770300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>10845800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>11551100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>12707100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>13217100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>12028200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>11694800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>11429100</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>12147200</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>11328200</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>10649200</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>10676900</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>10787700</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>8887300</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>5299500</v>
+      </c>
+      <c r="E58" s="3">
         <v>5575600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>5812800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>7401400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>6393500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>7399900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>7190800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>6481000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>9352200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>8859900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>8276900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>7751000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>4595500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>5029900</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>5764700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>5962600</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>5327600</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>5047300</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>5228200</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>6306000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>6143800</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>6544700</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>7261900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>8192800</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>7845800</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>7553600</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>6959600</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>6294800</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>6184300</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>5829800</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>5542100</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>6488500</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>6146100</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>7075800</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>6388700</v>
       </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>7912800</v>
+      </c>
+      <c r="E59" s="3">
         <v>8202400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>8096000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>8963900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>8445800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>8028100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>8175600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>8720800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>7620400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>8159800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>10312300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>10810700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>9145900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>6802800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>6487000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>5634600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>4516000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>4513900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>4330200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>4931400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>7640400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>6186700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>5577100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>5804100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>5781200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>6905100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>6461800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>6059700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>6783400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>6711400</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>5826600</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>5765000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>5564600</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>5821700</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>4722300</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>24402200</v>
+      </c>
+      <c r="E60" s="3">
         <v>25389400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>25131200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>27653400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>25728300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>27749600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>26184900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>26282500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>28334600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>29550900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>29555000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>31106500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>25289300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>23591600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>22326000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>21979400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>19155200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>18298800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>17847200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>19981500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>23796800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>24501800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>23684800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>25548000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>26334000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>27675800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>25449500</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>24049300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>24396900</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>24688500</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>22697000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>22902800</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>22387600</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>23685200</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>19998200</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>27029800</v>
+      </c>
+      <c r="E61" s="3">
         <v>26129600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>25551400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>23765800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>25182700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>27316400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>26820700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>28735500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>28565500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>27489000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>25059200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>27278200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>27790900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>28115400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>27947800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>29338200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>28326800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>30052900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>32828400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>35839200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>37259400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>38486000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>38586200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>37173100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>36605000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>33965600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>33739000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>32441500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>32027200</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>34920400</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>35699100</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>37405600</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>37431100</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>38250500</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>36521200</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>4156000</v>
+      </c>
+      <c r="E62" s="3">
         <v>4639800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>4035000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4657400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4226200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>4199900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>4520300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>4351100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>4261800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>8578500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>7754600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>7707600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>7528900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>6977600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>7137200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>7774600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>7061100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>6336400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>6416800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>6975900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>7180400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>8188900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>7779100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>7906600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>8323600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>8124200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>8671300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>7800000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>7656300</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>7269000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>7278500</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>7072300</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>6802600</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>6766700</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>5977300</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6093,8 +6241,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6200,8 +6351,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6307,115 +6461,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>60427400</v>
+      </c>
+      <c r="E66" s="3">
         <v>61001900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>60132700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>61063700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>60358700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>65011800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>62688200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>64405100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>66316900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>67084800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>63752000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>67506000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>61872100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>60471700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>59233700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>60973500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>56333100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>56483400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>59007300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>64958700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>70379700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>73667400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>72465300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>73055600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>73829900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>72239100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>70300400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>66567400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>66280800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>69332300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>68053100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>69759100</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>68909600</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>71093200</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>64647500</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6453,8 +6613,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6560,8 +6721,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6667,8 +6831,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6774,8 +6941,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6881,115 +7051,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>38738800</v>
+      </c>
+      <c r="E72" s="3">
         <v>36646800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>40847100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>35592300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>36704500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>37180800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>34085100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>34435100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>36412900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>33403000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>28566600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>29304600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>27662000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>26560900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>26825200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>26541400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>25153800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>24743600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>26163700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>28238800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>29621800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>30109600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>30037200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>28668100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>29585900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>28566200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>22079200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>25998200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>26247000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>25531600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>24759700</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>23601500</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>22619600</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>21765100</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>21151000</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7095,8 +7271,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7202,8 +7381,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7309,115 +7491,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>50395400</v>
+      </c>
+      <c r="E76" s="3">
         <v>48027900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>52065200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>49244700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>49861800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>50373100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>47278000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>46921600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>47901600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>43455000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>38568900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>38896000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>37218600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>34248700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>34165100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>35352000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>32404300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>30316100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>30647000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>33017300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>33633700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>39521800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>38703100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>38782900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>40969000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>39407500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>39762100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>36872200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>35931400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>37896800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>35850000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>34316500</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>33104400</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>32312900</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>28320500</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7523,120 +7711,126 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -7664,86 +7858,89 @@
       <c r="K81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L81" s="3">
+      <c r="L81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M81" s="3">
         <v>2141900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1685000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1853500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1868900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1570700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1538400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1405800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>967900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>651700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>369800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>533600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>497200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>919400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1002800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1145300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>616500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1200700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>970400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1076400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>376500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1252300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>1153100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>1001200</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>672400</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>961100</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>539600</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7781,115 +7978,119 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>263400</v>
+      </c>
+      <c r="E83" s="3">
         <v>507700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>455700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>479400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>194700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>525400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>491000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>485700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>257800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>492000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>453200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>444900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>473800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>536800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>526500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>543100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>520500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>492200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>545800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>537500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>623100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>600400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>541700</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>554500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>496000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>442500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>411100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>396100</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>413800</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>448800</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>449300</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>429100</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>410100</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>432800</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>438700</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7995,8 +8196,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8102,8 +8306,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8209,8 +8416,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8316,8 +8526,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8423,115 +8636,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1630600</v>
+      </c>
+      <c r="E89" s="3">
         <v>1129500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2166200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1774300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1208700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1526000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>667300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2537100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3367400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2055600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>187800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1893500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2973900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>356300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>921800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1317900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1916000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>891400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1688800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1399300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1229000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>548400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1827000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1171400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>472800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1886300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>251200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1223700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1352500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>2182700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-372700</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1833000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1624300</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1312000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>298600</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8569,115 +8788,119 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-621500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-559200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-481100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-598300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-478800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-573400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-524900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-436500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-395200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-66573000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-54756000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-54200000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-44019000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-50278000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-44762000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-341500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-275500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-358300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-357300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-700100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-669200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-792800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-579100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-566500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-717000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-868800</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-680800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-616300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>707600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-337700</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-384300</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-196300</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-458100</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-338400</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-537000</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8783,8 +9006,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8890,115 +9116,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-604800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-192400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-116000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-152700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-685700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-193700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-684700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1343500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-390700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>39800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-130100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-752200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>61100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-286000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-405500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-680000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-98800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-618100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-901100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-925800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>186300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-718500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-156200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1012200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-2595500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1897000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1369400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-914400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-579400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-717100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-761300</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-186100</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-967700</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-474900</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-603200</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9036,115 +9268,119 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>0</v>
+      </c>
+      <c r="E96" s="3">
         <v>934200</v>
       </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
       <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3">
         <v>791200</v>
       </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
       <c r="H96" s="3">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3">
         <v>908400</v>
       </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>790700</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>-724400</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>-647400</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-502400</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
         <v>-551900</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
       <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
         <v>-492400</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
       <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
         <v>-582600</v>
       </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
       <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-633600</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
       <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-636800</v>
       </c>
-      <c r="AA96" s="3">
-        <v>0</v>
-      </c>
       <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-656300</v>
       </c>
-      <c r="AC96" s="3">
-        <v>0</v>
-      </c>
       <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-631900</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
       <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-478400</v>
       </c>
-      <c r="AG96" s="3">
-        <v>0</v>
-      </c>
       <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-478400</v>
       </c>
-      <c r="AI96" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK96" s="3">
         <v>-397500</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9250,8 +9486,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9357,8 +9596,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9464,325 +9706,337 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-640200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-521100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2894600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-976700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2222100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1746700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-613700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2345300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1933500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-494900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1136700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-874800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1439500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-322200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1286200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1266100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1451100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1099300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-343300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-752700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-130100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1862200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-68800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>202500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>2126800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-385900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>482800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-954700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1145700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-1020400</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-2791000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-939700</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-1316100</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-841900</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>217200</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>222200</v>
+      </c>
+      <c r="E101" s="3">
         <v>-122600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>55100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>413000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>42400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-350500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>114700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>380700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>382500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-328200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>105900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>348700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>308400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>120700</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-61400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-15900</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>233800</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-59100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>6600</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>131300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-293800</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>148200</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-82300</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-72700</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>23700</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-142100</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>124000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>45000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-335900</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>3300</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>100100</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>10700</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-65200</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>603600</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-59700</v>
       </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>190300</v>
+      </c>
+      <c r="E102" s="3">
         <v>582400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1244300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>853800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1477000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-536900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-576000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-738700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1085600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1272400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-973100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>615100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1903900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-131200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-831200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-644100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>600000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-885100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>451000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-148000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>991400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-1884100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>1519700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>289000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>27700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-404700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-643100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-600500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-708500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>448600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-3824900</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>717900</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-724700</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>598900</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-147200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MITSY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MITSY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="92">
   <si>
     <t>MITSY</t>
   </si>
@@ -656,144 +656,152 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="37" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="16" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="19" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="38" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -824,86 +832,89 @@
       <c r="L8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M8" s="3">
+      <c r="M8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N8" s="3">
         <v>25650200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>23627000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>25076400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>21036400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>21800100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>19886400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>19536500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>23476100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>14920200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>14487100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>15741000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>28986100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>16240900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>16340900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>14959400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>18687200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>16988500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>15394900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>14145800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>11201800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>11381200</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>10959900</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>10682200</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>10539300</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>10144100</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>8977900</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -934,86 +945,89 @@
       <c r="L9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M9" s="3">
+      <c r="M9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N9" s="3">
         <v>22907200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>21595000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>22963900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>18701800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>19997700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>18017600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>17565000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>21751400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>13451500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>13099400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>14122800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>27233000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>14307400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>14328700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>13042800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>16713400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>15012100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>13487900</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>12160100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>9567400</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>9519200</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>9110700</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>8879700</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>8666700</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>8528400</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>7541800</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1044,86 +1058,89 @@
       <c r="L10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M10" s="3">
+      <c r="M10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N10" s="3">
         <v>2743000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2031900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2112500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2334500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1802400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1868700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1971500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1724700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1468700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1387600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1618200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1753200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1933500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2012200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1916600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1973800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1976400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1906900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1985700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1634400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1861900</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1849100</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1802500</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1872600</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>1615700</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>1436100</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1162,8 +1179,9 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1272,8 +1290,11 @@
       <c r="AL12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1382,8 +1403,11 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1414,86 +1438,89 @@
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="3">
         <v>37400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>67300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>1800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>32100</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>10800</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>163500</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-1600</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>90700</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>262100</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>38700</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>2600</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>874000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>82100</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>8300</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>15500</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>225400</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>20700</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>3800</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>8900</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>59600</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>91800</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>67000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>11600</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>48200</v>
       </c>
-      <c r="AK14" s="3">
-        <v>0</v>
-      </c>
       <c r="AL14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM14" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1524,8 +1551,8 @@
       <c r="L15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
+      <c r="M15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
@@ -1602,8 +1629,11 @@
       <c r="AL15" s="3">
         <v>0</v>
       </c>
+      <c r="AM15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1639,8 +1669,9 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1671,86 +1702,89 @@
       <c r="L17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M17" s="3">
+      <c r="M17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N17" s="3">
         <v>23948200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>22600500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>23836300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>19830800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>20835700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>19119900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>18538500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>22976200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>14945300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>14328800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>15201000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>29074600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>15671900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>15581200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>14210600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>18422900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>16308000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>14800500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>13271100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>11108400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>10721200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>10139700</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>9954000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>9794000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>9291500</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>8516000</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1781,86 +1815,89 @@
       <c r="L18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M18" s="3">
+      <c r="M18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N18" s="3">
         <v>1701900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1026400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1240000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1205600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>964400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>766500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>998000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>500000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-25200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>158300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>540000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-88400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>569000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>759700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>748700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>264200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>680500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>594400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>874700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>93400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>660000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>820200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>728200</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>745300</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>852600</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>461900</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1899,8 +1936,9 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1931,86 +1969,89 @@
       <c r="L20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N20" s="3">
         <v>1211100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1290200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1215700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1076700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1107600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>1367000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>990700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>836800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>762100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>586800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>461600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>822000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>1024200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>799300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>1048100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>949200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>1042200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>982200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>815900</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>682600</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>963900</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>765600</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>808400</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>451900</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>662000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>545900</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2041,86 +2082,89 @@
       <c r="L21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N21" s="3">
         <v>3405000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2769800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2900600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2756100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2608800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2659900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2531800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1857200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1229100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1290900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1539200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1356700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>2193700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>2100800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>2351400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1709400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>2165200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1987800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>2086700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1189800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>2072700</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>2035100</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1965600</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1607200</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1947400</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1446600</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2151,86 +2195,89 @@
       <c r="L22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M22" s="3">
+      <c r="M22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N22" s="3">
         <v>236200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>148400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>110500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>76000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>69100</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>82400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>105800</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>77600</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>92500</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>100800</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>131600</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>178400</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>205000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>212500</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>217600</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>194400</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>191600</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>191700</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>172300</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>149100</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>150300</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>156500</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>145100</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>140900</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>133700</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>118100</v>
       </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2261,86 +2308,89 @@
       <c r="L23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M23" s="3">
+      <c r="M23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N23" s="3">
         <v>2676800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2168200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2345200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2206300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2002900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2051000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1883000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1259100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>644500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>644300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>870000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>555100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1388200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1346500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1579200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1019000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1531100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1384900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1518300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>626900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1473600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1429300</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1391500</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>1056300</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>1380900</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>889700</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2371,86 +2421,89 @@
       <c r="L24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M24" s="3">
+      <c r="M24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N24" s="3">
         <v>502000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>460500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>401700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>299100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>402700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>482800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>413000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>260700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-32100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>250100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>301300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>88400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>409100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>280700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>343700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>397900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>289000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>367300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>372800</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>201200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>158300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>234300</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>338000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>320800</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>367600</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>316000</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2559,8 +2612,11 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2591,86 +2647,89 @@
       <c r="L26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M26" s="3">
+      <c r="M26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N26" s="3">
         <v>2174800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1707800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1943500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1907200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1600200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1568200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1470000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>998400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>676500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>394200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>568600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>466700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>979200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1065800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1235500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>621100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1242100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1017600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1145500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>425700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>1315300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1195000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>1053500</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>735500</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>1013300</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>573700</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2701,86 +2760,89 @@
       <c r="L27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M27" s="3">
+      <c r="M27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N27" s="3">
         <v>2141900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1685000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1853500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1868900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1570700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1538400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1405800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>967900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>651700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>369800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>533600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>497200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>919400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1002800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1145300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>616500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1200700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>970400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1076400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>376500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>1252300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>1153100</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>1001200</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>672400</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>961100</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>539600</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2889,8 +2951,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2921,8 +2986,8 @@
       <c r="L29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
+      <c r="M29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N29" s="3">
         <v>0</v>
@@ -2999,8 +3064,11 @@
       <c r="AL29" s="3">
         <v>0</v>
       </c>
+      <c r="AM29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3109,8 +3177,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3219,8 +3290,11 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3251,86 +3325,89 @@
       <c r="L32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N32" s="3">
         <v>-1211100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1290200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1215700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1076700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1107600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-1367000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-990700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-836800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-762100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-586800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-461600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-822000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-1024200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-799300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-1048100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-949200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-1042200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-982200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-815900</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-682600</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-963900</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-765600</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-808400</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-451900</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-662000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-545900</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3361,86 +3438,89 @@
       <c r="L33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M33" s="3">
+      <c r="M33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N33" s="3">
         <v>2141900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1685000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1853500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1868900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1570700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1538400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1405800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>967900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>651700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>369800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>533600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>497200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>919400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1002800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1145300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>616500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1200700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>970400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1076400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>376500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>1252300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>1153100</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>1001200</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>672400</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>961100</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>539600</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3549,8 +3629,11 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3581,201 +3664,207 @@
       <c r="L35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M35" s="3">
+      <c r="M35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N35" s="3">
         <v>2141900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1685000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1853500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1868900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1570700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1538400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1405800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>967900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>651700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>369800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>533600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>497200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>919400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1002800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1145300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>616500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1200700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>970400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1076400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>376500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>1252300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>1153100</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>1001200</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>672400</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>961100</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>539600</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3814,8 +3903,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3854,118 +3944,122 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3">
+      <c r="D41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="3">
         <v>6526700</v>
       </c>
-      <c r="E41" s="3">
-        <v>6035200</v>
-      </c>
-      <c r="F41" s="3">
+      <c r="F41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G41" s="3">
         <v>5983900</v>
       </c>
-      <c r="G41" s="3">
-        <v>6437400</v>
-      </c>
-      <c r="H41" s="3">
+      <c r="H41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I41" s="3">
         <v>5938300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>7956800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>8016100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>8862000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>10457300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>8845300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>6805000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>8217000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>7489000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>5778600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>6202300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>7170000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>7537700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>7172600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>8563400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>8883000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>9327400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>8619900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>10596300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>9047000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>9188200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>8998400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>9253700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>9683800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>10227700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>10936200</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>10487600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>14312400</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>13338900</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>14063500</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>13464600</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3973,7 +4067,7 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>16000</v>
       </c>
       <c r="F42" s="3">
         <v>0</v>
@@ -3982,11 +4076,11 @@
         <v>0</v>
       </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>29900</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
         <v>0</v>
       </c>
@@ -3994,858 +4088,882 @@
         <v>0</v>
       </c>
       <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
         <v>50300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>7188900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>8123200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>7698600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>6625800</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>6088600</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>5687100</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>4151400</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>3048600</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>3152600</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>3119600</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>3626700</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>4959100</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>3002000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>2707200</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>2753000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>2445800</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>3255400</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>2869100</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>2702600</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>2205000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>3030500</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>2627800</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>2445500</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>2374300</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>3915400</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>3786600</v>
       </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>15014400</v>
+      <c r="D43" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E43" s="3">
-        <v>15344800</v>
-      </c>
-      <c r="F43" s="3">
+        <v>16053000</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G43" s="3">
         <v>15610800</v>
       </c>
-      <c r="G43" s="3">
-        <v>15335400</v>
-      </c>
-      <c r="H43" s="3">
+      <c r="H43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I43" s="3">
         <v>17120500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>16334400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>14856300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>14613900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>17991700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>16929900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>15444400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>16786300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>15292800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>15852800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>13571000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>13780400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>12847000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>12632200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>11204300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>12454600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>14294200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>16566500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>14911000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>15916900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>17338600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>17779600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>16564800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>15649400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>15964800</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>17290200</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>16461900</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>14971500</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>15428500</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>15480700</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>13205700</v>
       </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
+      <c r="D44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="3">
         <v>6413800</v>
       </c>
-      <c r="E44" s="3">
-        <v>6839100</v>
-      </c>
-      <c r="F44" s="3">
+      <c r="F44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G44" s="3">
         <v>6684200</v>
       </c>
-      <c r="G44" s="3">
-        <v>6158700</v>
-      </c>
-      <c r="H44" s="3">
+      <c r="H44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I44" s="3">
         <v>6384700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>6546400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>6130800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>6647900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>7075300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>7257600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>6519300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>6577600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>6305800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>6092800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>5348100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>5282900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>4361400</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>4413800</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>4318400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>4554700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>4879500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>6283100</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>5890100</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>5901000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>5839800</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>5950700</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>5828600</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>5150500</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>4978300</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>5689100</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>5718500</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>5394500</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>5229200</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>5336700</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>4779400</v>
       </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>10021900</v>
+      <c r="D45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E45" s="3">
-        <v>9580300</v>
-      </c>
-      <c r="F45" s="3">
+        <v>8967300</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G45" s="3">
         <v>9926400</v>
       </c>
-      <c r="G45" s="3">
-        <v>11358800</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I45" s="3">
         <v>8661800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>10355500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>9737900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>10486700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>7114500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3063800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2394200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2765400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2245300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2327600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2275500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2305600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2036200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2036500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2138300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2623100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>2875800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>2941600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>2909800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>3240200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>3592300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>3707100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>3593900</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>3510500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>4828700</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>4005100</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>3659200</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>3525900</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>3320100</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>3359700</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>2996000</v>
       </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3">
+      <c r="D46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E46" s="3">
         <v>37976700</v>
       </c>
-      <c r="E46" s="3">
-        <v>37799400</v>
-      </c>
-      <c r="F46" s="3">
+      <c r="F46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G46" s="3">
         <v>38205300</v>
       </c>
-      <c r="G46" s="3">
-        <v>39290200</v>
-      </c>
-      <c r="H46" s="3">
+      <c r="H46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I46" s="3">
         <v>38135300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>41193200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>38741100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>40610400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>42689100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>43285600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>39286100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>42044900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>37958800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>36140400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>33084000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>32690400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>29831000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>29407700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>29344000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>32142100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>36336100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>37413100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>37014400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>36858100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>38404700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>39691200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>38110200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>36696800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>38204500</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>40951100</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>38955000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>40649900</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>39691000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>42156100</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>38232400</v>
       </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>47840900</v>
+      <c r="D47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E47" s="3">
-        <v>46014100</v>
-      </c>
-      <c r="F47" s="3">
+        <v>47854300</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3">
         <v>48591000</v>
       </c>
-      <c r="G47" s="3">
-        <v>46012800</v>
-      </c>
-      <c r="H47" s="3">
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3">
         <v>47546900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>49006300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>46203000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>44651900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>45632700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>45576500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>42559700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>43167900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>41318100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>38904100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>40110200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>42558000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>38622100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>37234400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>38999900</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>42508800</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>43819300</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>50414800</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>49513500</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>50532700</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>53209900</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>48784500</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>49446400</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>45792300</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>44126500</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>45878300</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>44160100</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>42595400</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>41700800</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>39980100</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>35285000</v>
       </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" s="3">
         <v>16491400</v>
       </c>
-      <c r="E48" s="3">
-        <v>16381300</v>
-      </c>
-      <c r="F48" s="3">
+      <c r="F48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G48" s="3">
         <v>16766200</v>
       </c>
-      <c r="G48" s="3">
-        <v>15999900</v>
-      </c>
-      <c r="H48" s="3">
+      <c r="H48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I48" s="3">
         <v>15877100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>16660800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>16273300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>17114800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>17306400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>18096300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>17008700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>17712200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>16662900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>16691900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>17196100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>17942800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>17369900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>17576200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>18818600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>20573600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>20908000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>22359200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>21602500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>21397900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>20646900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>20363100</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>19807500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>18394900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>17346400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>17820100</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>18003700</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>17903900</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>17769100</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>18403400</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>16888800</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3">
+      <c r="D49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="3">
         <v>3375300</v>
       </c>
-      <c r="E49" s="3">
-        <v>3071600</v>
-      </c>
-      <c r="F49" s="3">
+      <c r="F49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G49" s="3">
         <v>3268000</v>
       </c>
-      <c r="G49" s="3">
-        <v>3155900</v>
-      </c>
-      <c r="H49" s="3">
+      <c r="H49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I49" s="3">
         <v>3029600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3154100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2975900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2995300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2086100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2005000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1888200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1898700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1680200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1568100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1529500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1604900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1336900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1365200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1507700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1644000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1720500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>2151300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>2186600</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>2230100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1673000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1743600</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1607100</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1552500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1565800</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1572800</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>1615000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>1568500</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>1496200</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>1434400</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>1274500</v>
       </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4954,8 +5072,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5064,118 +5185,124 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>3899800</v>
+      <c r="D52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E52" s="3">
-        <v>4376400</v>
-      </c>
-      <c r="F52" s="3">
+        <v>4122800</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G52" s="3">
         <v>4411800</v>
       </c>
-      <c r="G52" s="3">
-        <v>4789800</v>
-      </c>
-      <c r="H52" s="3">
+      <c r="H52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I52" s="3">
         <v>4761800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4201200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4469200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4569800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>5022900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1576500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1578100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1578300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1470700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1415900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1479100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1529400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1577500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1215900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>984000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1107500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1229500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>850800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>851500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>819700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>864500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1064200</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1091400</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1002900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>969100</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1006800</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1169300</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1357900</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1356900</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>1432200</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>1287300</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5284,118 +5411,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3">
+      <c r="D54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="3">
         <v>112265300</v>
       </c>
-      <c r="E54" s="3">
-        <v>110450000</v>
-      </c>
-      <c r="F54" s="3">
+      <c r="F54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G54" s="3">
         <v>113744000</v>
       </c>
-      <c r="G54" s="3">
-        <v>111769500</v>
-      </c>
-      <c r="H54" s="3">
+      <c r="H54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I54" s="3">
         <v>111728600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>116974300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>111437900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>112815100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>115703400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>110539800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>102320900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>106402000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>99090600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>94720400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>93398900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>96325500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>88737300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>86799500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>89654300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>97976000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>104013400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>113189100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>111168500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>111838500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>114798900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>111646700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>110062600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>103439500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>102212200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>107229100</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>103903100</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>104075500</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>102014000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>103406200</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>92968100</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5434,8 +5567,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5474,668 +5608,687 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
-        <v>11189900</v>
+      <c r="D57" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E57" s="3">
-        <v>11611300</v>
-      </c>
-      <c r="F57" s="3">
+        <v>9866300</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G57" s="3">
         <v>11222400</v>
       </c>
-      <c r="G57" s="3">
-        <v>11288100</v>
-      </c>
-      <c r="H57" s="3">
+      <c r="H57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I57" s="3">
         <v>9498000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>12321600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>10818500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>11080800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>10059000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>12531200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>10965800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>12544700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>11547900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>11758900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>10074300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>10382200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>9311600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>8737600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>8288800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>8744100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>10012600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>11770300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>10845800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>11551100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>12707100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>13217100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>12028200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>11694800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>11429100</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>12147200</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>11328200</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>10649200</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>10676900</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>10787700</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>8887300</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
+      <c r="D58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="3">
         <v>5299500</v>
       </c>
-      <c r="E58" s="3">
-        <v>5575600</v>
-      </c>
-      <c r="F58" s="3">
+      <c r="F58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G58" s="3">
         <v>5812800</v>
       </c>
-      <c r="G58" s="3">
-        <v>7401400</v>
-      </c>
-      <c r="H58" s="3">
+      <c r="H58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I58" s="3">
         <v>6393500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>7399900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>7190800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>6481000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>9352200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>8859900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>8276900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>7751000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>4595500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>5029900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>5764700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>5962600</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>5327600</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>5047300</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>5228200</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>6306000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>6143800</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>6544700</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>7261900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>8192800</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>7845800</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>7553600</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>6959600</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>6294800</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>6184300</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>5829800</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>5542100</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>6488500</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>6146100</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>7075800</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>6388700</v>
       </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="3">
         <v>7912800</v>
       </c>
-      <c r="E59" s="3">
-        <v>8202400</v>
-      </c>
-      <c r="F59" s="3">
+      <c r="F59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G59" s="3">
         <v>8096000</v>
       </c>
-      <c r="G59" s="3">
-        <v>8963900</v>
-      </c>
-      <c r="H59" s="3">
+      <c r="H59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I59" s="3">
         <v>8445800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>8028100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>8175600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>8720800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>7620400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>8159800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>10312300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>10810700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>9145900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>6802800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>6487000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>5634600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>4516000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>4513900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>4330200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>4931400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>7640400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>6186700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>5577100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>5804100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>5781200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>6905100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>6461800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>6059700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>6783400</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>6711400</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>5826600</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>5765000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>5564600</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>5821700</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>4722300</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3">
+      <c r="D60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="3">
         <v>24402200</v>
       </c>
-      <c r="E60" s="3">
-        <v>25389400</v>
-      </c>
-      <c r="F60" s="3">
+      <c r="F60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G60" s="3">
         <v>25131200</v>
       </c>
-      <c r="G60" s="3">
-        <v>27653400</v>
-      </c>
-      <c r="H60" s="3">
+      <c r="H60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I60" s="3">
         <v>25728300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>27749600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>26184900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>26282500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>28334600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>29550900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>29555000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>31106500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>25289300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>23591600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>22326000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>21979400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>19155200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>18298800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>17847200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>19981500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>23796800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>24501800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>23684800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>25548000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>26334000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>27675800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>25449500</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>24049300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>24396900</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>24688500</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>22697000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>22902800</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>22387600</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>23685200</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>19998200</v>
       </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3">
         <v>27029800</v>
       </c>
-      <c r="E61" s="3">
-        <v>26129600</v>
-      </c>
       <c r="F61" s="3">
+        <v>0</v>
+      </c>
+      <c r="G61" s="3">
         <v>25551400</v>
       </c>
-      <c r="G61" s="3">
-        <v>23765800</v>
-      </c>
       <c r="H61" s="3">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
         <v>25182700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>27316400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>26820700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>28735500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>28565500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>27489000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>25059200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>27278200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>27790900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>28115400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>27947800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>29338200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>28326800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>30052900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>32828400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>35839200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>37259400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>38486000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>38586200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>37173100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>36605000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>33965600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>33739000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>32441500</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>32027200</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>34920400</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>35699100</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>37405600</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>37431100</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>38250500</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>36521200</v>
       </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E62" s="3">
         <v>4156000</v>
       </c>
-      <c r="E62" s="3">
-        <v>4639800</v>
-      </c>
-      <c r="F62" s="3">
+      <c r="F62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G62" s="3">
         <v>4035000</v>
       </c>
-      <c r="G62" s="3">
-        <v>4657400</v>
-      </c>
-      <c r="H62" s="3">
+      <c r="H62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I62" s="3">
         <v>4226200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>4199900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>4520300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>4351100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>4261800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>8578500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>7754600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>7707600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>7528900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>6977600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>7137200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>7774600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>7061100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>6336400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>6416800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>6975900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>7180400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>8188900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>7779100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>7906600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>8323600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>8124200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>8671300</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>7800000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>7656300</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>7269000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>7278500</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>7072300</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>6802600</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>6766700</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>5977300</v>
       </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6244,8 +6397,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6354,8 +6510,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6464,118 +6623,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3">
+      <c r="D66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E66" s="3">
         <v>60427400</v>
       </c>
-      <c r="E66" s="3">
-        <v>61001900</v>
-      </c>
-      <c r="F66" s="3">
+      <c r="F66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G66" s="3">
         <v>60132700</v>
       </c>
-      <c r="G66" s="3">
-        <v>61063700</v>
-      </c>
-      <c r="H66" s="3">
+      <c r="H66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I66" s="3">
         <v>60358700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>65011800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>62688200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>64405100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>66316900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>67084800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>63752000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>67506000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>61872100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>60471700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>59233700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>60973500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>56333100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>56483400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>59007300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>64958700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>70379700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>73667400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>72465300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>73055600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>73829900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>72239100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>70300400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>66567400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>66280800</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>69332300</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>68053100</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>69759100</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>68909600</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>71093200</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>64647500</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6614,8 +6779,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6724,8 +6890,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6834,8 +7003,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6944,8 +7116,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7054,118 +7229,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E72" s="3">
         <v>38738800</v>
       </c>
-      <c r="E72" s="3">
-        <v>36646800</v>
-      </c>
-      <c r="F72" s="3">
+      <c r="F72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G72" s="3">
         <v>40847100</v>
       </c>
-      <c r="G72" s="3">
-        <v>35592300</v>
-      </c>
-      <c r="H72" s="3">
+      <c r="H72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I72" s="3">
         <v>36704500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>37180800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>34085100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>34435100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>36412900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>33403000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>28566600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>29304600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>27662000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>26560900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>26825200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>26541400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>25153800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>24743600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>26163700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>28238800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>29621800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>30109600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>30037200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>28668100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>29585900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>28566200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>22079200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>25998200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>26247000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>25531600</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>24759700</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>23601500</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>22619600</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>21765100</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>21151000</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7274,8 +7455,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7384,8 +7568,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7494,118 +7681,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3">
+      <c r="D76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E76" s="3">
         <v>50395400</v>
       </c>
-      <c r="E76" s="3">
-        <v>48027900</v>
-      </c>
-      <c r="F76" s="3">
+      <c r="F76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G76" s="3">
         <v>52065200</v>
       </c>
-      <c r="G76" s="3">
-        <v>49244700</v>
-      </c>
-      <c r="H76" s="3">
+      <c r="H76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I76" s="3">
         <v>49861800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>50373100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>47278000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>46921600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>47901600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>43455000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>38568900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>38896000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>37218600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>34248700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>34165100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>35352000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>32404300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>30316100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>30647000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>33017300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>33633700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>39521800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>38703100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>38782900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>40969000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>39407500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>39762100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>36872200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>35931400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>37896800</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>35850000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>34316500</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>33104400</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>32312900</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>28320500</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7714,123 +7907,129 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -7861,86 +8060,89 @@
       <c r="L81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M81" s="3">
+      <c r="M81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N81" s="3">
         <v>2141900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1685000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1853500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1868900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1570700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1538400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1405800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>967900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>651700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>369800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>533600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>497200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>919400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1002800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1145300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>616500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1200700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>970400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1076400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>376500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>1252300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>1153100</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>1001200</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>672400</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>961100</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>539600</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7979,118 +8181,122 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E83" s="3">
         <v>263400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>507700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>455700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>479400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>194700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>525400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>491000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>485700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>257800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>492000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>453200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>444900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>473800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>536800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>526500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>543100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>520500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>492200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>545800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>537500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>623100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>600400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>541700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>554500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>496000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>442500</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>411100</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>396100</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>413800</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>448800</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>449300</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>429100</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>410100</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>432800</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>438700</v>
       </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8199,8 +8405,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8309,8 +8518,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8419,8 +8631,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8529,8 +8744,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8639,118 +8857,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E89" s="3">
         <v>1630600</v>
       </c>
-      <c r="E89" s="3">
-        <v>1129500</v>
-      </c>
-      <c r="F89" s="3">
+      <c r="F89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G89" s="3">
         <v>2166200</v>
       </c>
-      <c r="G89" s="3">
-        <v>1774300</v>
-      </c>
-      <c r="H89" s="3">
+      <c r="H89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I89" s="3">
         <v>1208700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1526000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>667300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2537100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3367400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2055600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>187800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1893500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>2973900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>356300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>921800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1317900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1916000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>891400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1688800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1399300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1229000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>548400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1827000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1171400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>472800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1886300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>251200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1223700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1352500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>2182700</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-372700</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1833000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1624300</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>1312000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>298600</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8789,118 +9013,122 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E91" s="3">
         <v>-621500</v>
       </c>
-      <c r="E91" s="3">
-        <v>-559200</v>
-      </c>
-      <c r="F91" s="3">
+      <c r="F91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G91" s="3">
         <v>-481100</v>
       </c>
-      <c r="G91" s="3">
-        <v>-598300</v>
-      </c>
-      <c r="H91" s="3">
+      <c r="H91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I91" s="3">
         <v>-478800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-573400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-524900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-436500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-395200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-66573000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-54756000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-54200000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-44019000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-50278000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-44762000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-341500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-275500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-358300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-357300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-700100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-669200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-792800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-579100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-566500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-717000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-868800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-680800</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-616300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>707600</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-337700</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-384300</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-196300</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-458100</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-338400</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-537000</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9009,8 +9237,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9119,118 +9350,124 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E94" s="3">
         <v>-604800</v>
       </c>
-      <c r="E94" s="3">
-        <v>-192400</v>
-      </c>
-      <c r="F94" s="3">
+      <c r="F94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G94" s="3">
         <v>-116000</v>
       </c>
-      <c r="G94" s="3">
-        <v>-152700</v>
-      </c>
-      <c r="H94" s="3">
+      <c r="H94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I94" s="3">
         <v>-685700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-193700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-684700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1343500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-390700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>39800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-130100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-752200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>61100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-286000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-405500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-680000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-98800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-618100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-901100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-925800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>186300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-718500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-156200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1012200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-2595500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1897000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1369400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-914400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-579400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-717100</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-761300</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-186100</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-967700</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-474900</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-603200</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9269,118 +9506,122 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E96" s="3">
-        <v>934200</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G96" s="3">
-        <v>791200</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
         <v>908400</v>
       </c>
-      <c r="J96" s="3">
-        <v>0</v>
-      </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>790700</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>-724400</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>-647400</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>-502400</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-551900</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-492400</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-582600</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-633600</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-636800</v>
       </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-656300</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-631900</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
       <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-478400</v>
       </c>
-      <c r="AH96" s="3">
-        <v>0</v>
-      </c>
       <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-478400</v>
       </c>
-      <c r="AJ96" s="3">
-        <v>0</v>
-      </c>
       <c r="AK96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL96" s="3">
         <v>-397500</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9489,8 +9730,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9599,8 +9843,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9709,334 +9956,346 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E100" s="3">
         <v>-640200</v>
       </c>
-      <c r="E100" s="3">
-        <v>-521100</v>
-      </c>
-      <c r="F100" s="3">
+      <c r="F100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G100" s="3">
         <v>-2894600</v>
       </c>
-      <c r="G100" s="3">
-        <v>-976700</v>
-      </c>
-      <c r="H100" s="3">
+      <c r="H100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I100" s="3">
         <v>-2222100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1746700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-613700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2345300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1933500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-494900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1136700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-874800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1439500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-322200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1286200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1266100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1451100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1099300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-343300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-752700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-130100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1862200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-68800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>202500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>2126800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-385900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>482800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-954700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-1145700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-1020400</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-2791000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-939700</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-1316100</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-841900</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>217200</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3">
         <v>222200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-122600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>55100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>413000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>42400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-350500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>114700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>380700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>382500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-328200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>105900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>348700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>308400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>120700</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-61400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-15900</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>233800</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-59100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>6600</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>131300</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-293800</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>148200</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-82300</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-72700</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>23700</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-142100</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>124000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>45000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-335900</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>3300</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>100100</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>10700</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-65200</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>603600</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-59700</v>
       </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>190300</v>
       </c>
-      <c r="E102" s="3">
-        <v>582400</v>
-      </c>
       <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
         <v>-1244300</v>
       </c>
-      <c r="G102" s="3">
-        <v>853800</v>
-      </c>
       <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
         <v>-1477000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-536900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-576000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-738700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1085600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1272400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-973100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>615100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1903900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-131200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-831200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-644100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>600000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-885100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>451000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-148000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>991400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-1884100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>1519700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>289000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>27700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-404700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-643100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-600500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-708500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>448600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-3824900</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>717900</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-724700</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>598900</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-147200</v>
       </c>
     </row>
